--- a/Hem catalogue.xlsx
+++ b/Hem catalogue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ee11846ce882123f/Desktop/hem-catalogue-app_final-1/hem-catalogue-app-1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="95" documentId="8_{B8F50426-6742-42C2-B694-AD00EF5BFA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E01EFCD0-0640-427A-B422-D7AE3384B01A}"/>
+  <xr:revisionPtr revIDLastSave="96" documentId="8_{B8F50426-6742-42C2-B694-AD00EF5BFA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3A3C9D2-17B7-4710-BDCD-9B6671758F67}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5395" uniqueCount="925">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5395" uniqueCount="926">
   <si>
     <t>Category</t>
   </si>
@@ -2822,6 +2822,9 @@
   </si>
   <si>
     <t>Mama and Baby Tall Hexa</t>
+  </si>
+  <si>
+    <t>Mama and Baby square</t>
   </si>
 </sst>
 </file>
@@ -3952,10 +3955,6 @@
 </externalLink>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -10224,7 +10223,7 @@
         <v>24</v>
       </c>
       <c r="C399" s="3" t="s">
-        <v>514</v>
+        <v>925</v>
       </c>
       <c r="D399" s="14" t="s">
         <v>514</v>

--- a/Hem catalogue.xlsx
+++ b/Hem catalogue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ee11846ce882123f/Desktop/hem-catalogue-app_final-1/hem-catalogue-app-1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="108" documentId="8_{B8F50426-6742-42C2-B694-AD00EF5BFA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6DC7F34-83E2-470C-A0A9-2EF5E4A8603B}"/>
+  <xr:revisionPtr revIDLastSave="117" documentId="8_{B8F50426-6742-42C2-B694-AD00EF5BFA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F476F854-C3AF-4D75-A4A7-91D4AB377549}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5395" uniqueCount="926">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5395" uniqueCount="928">
   <si>
     <t>Category</t>
   </si>
@@ -2825,6 +2825,12 @@
   </si>
   <si>
     <t>Mama and Baby square</t>
+  </si>
+  <si>
+    <t>sd</t>
+  </si>
+  <si>
+    <t>Lavender and White Sage Room Spray</t>
   </si>
 </sst>
 </file>
@@ -11666,7 +11672,7 @@
         <v>24</v>
       </c>
       <c r="C503" s="3" t="s">
-        <v>579</v>
+        <v>825</v>
       </c>
       <c r="D503" s="11" t="s">
         <v>825</v>
@@ -12752,7 +12758,7 @@
       </c>
       <c r="B579" s="2"/>
       <c r="C579" s="3" t="s">
-        <v>623</v>
+        <v>926</v>
       </c>
       <c r="D579" s="11" t="s">
         <v>885</v>
@@ -13470,7 +13476,7 @@
         <v>24</v>
       </c>
       <c r="C631" s="3" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="D631" s="11"/>
       <c r="E631" s="2"/>
@@ -13513,9 +13519,8 @@
         <v>24</v>
       </c>
       <c r="C634" s="3" t="s">
-        <v>703</v>
-      </c>
-      <c r="D634" s="11"/>
+        <v>706</v>
+      </c>
       <c r="E634" s="2"/>
     </row>
     <row r="635" spans="1:5" x14ac:dyDescent="0.45">
@@ -14483,7 +14488,7 @@
       </c>
       <c r="B710" s="2"/>
       <c r="C710" s="3" t="s">
-        <v>779</v>
+        <v>927</v>
       </c>
       <c r="D710" s="11" t="s">
         <v>898</v>

--- a/Hem catalogue.xlsx
+++ b/Hem catalogue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ee11846ce882123f/Desktop/hem-catalogue-app_final-1/hem-catalogue-app-1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="117" documentId="8_{B8F50426-6742-42C2-B694-AD00EF5BFA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F476F854-C3AF-4D75-A4A7-91D4AB377549}"/>
+  <xr:revisionPtr revIDLastSave="124" documentId="8_{B8F50426-6742-42C2-B694-AD00EF5BFA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{165920DF-25A0-419A-9A7A-B4804D75F872}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2827,10 +2827,10 @@
     <t>Mama and Baby square</t>
   </si>
   <si>
-    <t>sd</t>
-  </si>
-  <si>
     <t>Lavender and White Sage Room Spray</t>
+  </si>
+  <si>
+    <t>Mama and Baby Back flow Cones</t>
   </si>
 </sst>
 </file>
@@ -10803,17 +10803,13 @@
         <v>48</v>
       </c>
       <c r="B439" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C439" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="D439" s="17" t="s">
-        <v>916</v>
-      </c>
-      <c r="F439" s="14" t="e">
-        <f>_xlfn.XLOOKUP(#REF!,'[1]Hem Catalogue'!$C$545:$C$643,'[1]Hem Catalogue'!$D$545:$D$643,"")</f>
-        <v>#REF!</v>
+        <v>23</v>
+      </c>
+      <c r="C439" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="D439" s="14" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.45">
@@ -10821,17 +10817,13 @@
         <v>48</v>
       </c>
       <c r="B440" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C440" s="5" t="s">
-        <v>563</v>
-      </c>
-      <c r="D440" s="17" t="s">
-        <v>914</v>
-      </c>
-      <c r="F440" s="14" t="e">
-        <f>_xlfn.XLOOKUP(#REF!,'[1]Hem Catalogue'!$C$545:$C$643,'[1]Hem Catalogue'!$D$545:$D$643,"")</f>
-        <v>#REF!</v>
+        <v>23</v>
+      </c>
+      <c r="C440" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="D440" s="14" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.45">
@@ -10839,17 +10831,13 @@
         <v>48</v>
       </c>
       <c r="B441" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C441" s="2" t="s">
-        <v>807</v>
-      </c>
-      <c r="D441" s="17" t="s">
-        <v>915</v>
-      </c>
-      <c r="F441" s="14" t="e">
-        <f>_xlfn.XLOOKUP(#REF!,'[1]Hem Catalogue'!$C$545:$C$643,'[1]Hem Catalogue'!$D$545:$D$643,"")</f>
-        <v>#REF!</v>
+        <v>23</v>
+      </c>
+      <c r="C441" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="D441" s="14" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.45">
@@ -10860,10 +10848,10 @@
         <v>23</v>
       </c>
       <c r="C442" s="3" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D442" s="14" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.45">
@@ -10874,10 +10862,10 @@
         <v>23</v>
       </c>
       <c r="C443" s="3" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="D443" s="14" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.45">
@@ -10888,10 +10876,10 @@
         <v>23</v>
       </c>
       <c r="C444" s="3" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="D444" s="14" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.45">
@@ -10902,10 +10890,10 @@
         <v>23</v>
       </c>
       <c r="C445" s="3" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="D445" s="14" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.45">
@@ -10913,13 +10901,17 @@
         <v>48</v>
       </c>
       <c r="B446" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C446" s="3" t="s">
-        <v>530</v>
-      </c>
-      <c r="D446" s="14" t="s">
-        <v>530</v>
+        <v>24</v>
+      </c>
+      <c r="C446" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="D446" s="17" t="s">
+        <v>916</v>
+      </c>
+      <c r="F446" s="14" t="e">
+        <f>_xlfn.XLOOKUP(#REF!,'[1]Hem Catalogue'!$C$545:$C$643,'[1]Hem Catalogue'!$D$545:$D$643,"")</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.45">
@@ -10927,13 +10919,17 @@
         <v>48</v>
       </c>
       <c r="B447" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C447" s="3" t="s">
-        <v>531</v>
-      </c>
-      <c r="D447" s="14" t="s">
-        <v>531</v>
+        <v>24</v>
+      </c>
+      <c r="C447" s="5" t="s">
+        <v>563</v>
+      </c>
+      <c r="D447" s="17" t="s">
+        <v>914</v>
+      </c>
+      <c r="F447" s="14" t="e">
+        <f>_xlfn.XLOOKUP(#REF!,'[1]Hem Catalogue'!$C$545:$C$643,'[1]Hem Catalogue'!$D$545:$D$643,"")</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.45">
@@ -10941,13 +10937,17 @@
         <v>48</v>
       </c>
       <c r="B448" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C448" s="3" t="s">
-        <v>532</v>
-      </c>
-      <c r="D448" s="14" t="s">
-        <v>532</v>
+        <v>24</v>
+      </c>
+      <c r="C448" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="D448" s="17" t="s">
+        <v>915</v>
+      </c>
+      <c r="F448" s="14" t="e">
+        <f>_xlfn.XLOOKUP(#REF!,'[1]Hem Catalogue'!$C$545:$C$643,'[1]Hem Catalogue'!$D$545:$D$643,"")</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.45">
@@ -12600,7 +12600,7 @@
       </c>
       <c r="B567" s="2"/>
       <c r="C567" s="3" t="s">
-        <v>601</v>
+        <v>927</v>
       </c>
       <c r="D567" s="2" t="s">
         <v>601</v>
@@ -12757,8 +12757,8 @@
         <v>616</v>
       </c>
       <c r="B579" s="2"/>
-      <c r="C579" s="3" t="s">
-        <v>926</v>
+      <c r="C579" s="11" t="s">
+        <v>885</v>
       </c>
       <c r="D579" s="11" t="s">
         <v>885</v>
@@ -14488,7 +14488,7 @@
       </c>
       <c r="B710" s="2"/>
       <c r="C710" s="3" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="D710" s="11" t="s">
         <v>898</v>

--- a/Hem catalogue.xlsx
+++ b/Hem catalogue.xlsx
@@ -1,27 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hemcorporation-my.sharepoint.com/personal/analytics_hemcorporation_onmicrosoft_com/Documents/jitesh/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Jitesh\Desktop\hem-catalogue-app_final-1\hem-catalogue-app-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F5B423D1-35D6-4C70-BBF2-4D40E6AE70F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{637A14A9-03BF-4B14-BE5D-93A8CBC102AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hem catalogue" sheetId="3" r:id="rId1"/>
-    <sheet name="Sheet3" sheetId="5" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="2" state="hidden" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId4"/>
+    <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hem catalogue'!$A$1:$G$731</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hem catalogue'!$A$1:$G$721</definedName>
   </definedNames>
   <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
@@ -44,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5395" uniqueCount="928">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5365" uniqueCount="922">
   <si>
     <t>Category</t>
   </si>
@@ -2764,30 +2763,9 @@
     <t>Yog Chakra Air Freshner Spray</t>
   </si>
   <si>
-    <t>Black Current Ceramic Reed Diffuser 40 Ml</t>
-  </si>
-  <si>
-    <t>Lavender Ceramic Reed Diffuser 40 Ml</t>
-  </si>
-  <si>
-    <t>Lemongrass Ceramic Reed Diffuser 40 Ml</t>
-  </si>
-  <si>
-    <t>Black Current Reed Diffuser 100 Ml</t>
-  </si>
-  <si>
-    <t>Lavender Reed Diffuser 100 Ml</t>
-  </si>
-  <si>
-    <t>Lemongrass Reed Diffuser 100 Ml</t>
-  </si>
-  <si>
     <t>Hem Precious Chandan Soap</t>
   </si>
   <si>
-    <t>MASALA GIFT PACK</t>
-  </si>
-  <si>
     <t xml:space="preserve">7 CHAKRA </t>
   </si>
   <si>
@@ -2797,9 +2775,6 @@
     <t>Table Top Square 4</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Call Money Square</t>
   </si>
   <si>
@@ -2830,7 +2805,13 @@
     <t>Lavender and White Sage Room Spray</t>
   </si>
   <si>
-    <t>Mama and Baby Back flow Cones</t>
+    <t xml:space="preserve"> GIFT PACK</t>
+  </si>
+  <si>
+    <t>Hexa Gift Pack</t>
+  </si>
+  <si>
+    <t>7 Chakras Stone</t>
   </si>
 </sst>
 </file>
@@ -2890,7 +2871,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2930,12 +2911,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCAEDFB"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -3029,7 +3004,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -3087,18 +3062,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -3106,24 +3072,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3155,6 +3115,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Hem Catalogue"/>
@@ -3961,10 +3922,6 @@
 </externalLink>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -4282,7 +4239,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBBB3535-4F14-43E5-BD0D-3890A33AED12}">
-  <dimension ref="A1:G731"/>
+  <dimension ref="A1:G728"/>
   <sheetFormatPr defaultColWidth="48.7265625" defaultRowHeight="18.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="63.6328125" style="14" bestFit="1" customWidth="1"/>
@@ -4393,7 +4350,7 @@
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="D7" s="16" t="s">
         <v>840</v>
@@ -4408,7 +4365,7 @@
         <v>24</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>918</v>
+        <v>910</v>
       </c>
       <c r="D8" s="16" t="s">
         <v>841</v>
@@ -4453,7 +4410,7 @@
         <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
       <c r="D11" s="16" t="s">
         <v>126</v>
@@ -6491,7 +6448,7 @@
         <v>24</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>921</v>
+        <v>913</v>
       </c>
       <c r="D147" s="17" t="s">
         <v>227</v>
@@ -8377,70 +8334,69 @@
       <c r="A273" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B273" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="C273" s="3" t="s">
-        <v>470</v>
+      <c r="B273" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="C273" s="2" t="s">
+        <v>805</v>
       </c>
       <c r="D273" s="16"/>
       <c r="E273" s="2"/>
     </row>
-    <row r="274" spans="1:5" s="30" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A274" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B274" s="7" t="s">
-        <v>472</v>
-      </c>
-      <c r="C274" s="7" t="s">
-        <v>472</v>
-      </c>
-      <c r="D274" s="10" t="s">
-        <v>886</v>
-      </c>
-      <c r="E274" s="10"/>
-    </row>
-    <row r="275" spans="1:5" s="30" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A275" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B275" s="6" t="s">
-        <v>471</v>
-      </c>
-      <c r="C275" s="7" t="s">
-        <v>471</v>
-      </c>
-      <c r="D275" s="10" t="s">
-        <v>816</v>
-      </c>
-      <c r="E275" s="10"/>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A274" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B274" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C274" s="3" t="s">
+        <v>914</v>
+      </c>
+      <c r="D274" s="18" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A275" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B275" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C275" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D275" s="17" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A276" s="2" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>805</v>
-      </c>
-      <c r="C276" s="2" t="s">
-        <v>805</v>
-      </c>
-      <c r="D276" s="16"/>
-      <c r="E276" s="2"/>
+        <v>24</v>
+      </c>
+      <c r="C276" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D276" s="17" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A277" s="3" t="s">
+      <c r="A277" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B277" s="3" t="s">
+      <c r="B277" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C277" s="3" t="s">
-        <v>922</v>
-      </c>
-      <c r="D277" s="18" t="s">
-        <v>386</v>
+        <v>28</v>
+      </c>
+      <c r="D277" s="17" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.45">
@@ -8451,10 +8407,10 @@
         <v>24</v>
       </c>
       <c r="C278" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D278" s="17" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.45">
@@ -8465,10 +8421,10 @@
         <v>24</v>
       </c>
       <c r="C279" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D279" s="17" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.45">
@@ -8479,10 +8435,10 @@
         <v>24</v>
       </c>
       <c r="C280" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D280" s="17" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.45">
@@ -8493,10 +8449,10 @@
         <v>24</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D281" s="17" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.45">
@@ -8507,10 +8463,10 @@
         <v>24</v>
       </c>
       <c r="C282" s="3" t="s">
-        <v>30</v>
+        <v>359</v>
       </c>
       <c r="D282" s="17" t="s">
-        <v>30</v>
+        <v>359</v>
       </c>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.45">
@@ -8521,10 +8477,10 @@
         <v>24</v>
       </c>
       <c r="C283" s="3" t="s">
-        <v>31</v>
+        <v>360</v>
       </c>
       <c r="D283" s="17" t="s">
-        <v>31</v>
+        <v>360</v>
       </c>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.45">
@@ -8535,10 +8491,10 @@
         <v>24</v>
       </c>
       <c r="C284" s="3" t="s">
-        <v>32</v>
+        <v>361</v>
       </c>
       <c r="D284" s="17" t="s">
-        <v>32</v>
+        <v>361</v>
       </c>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.45">
@@ -8549,10 +8505,10 @@
         <v>24</v>
       </c>
       <c r="C285" s="3" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="D285" s="17" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.45">
@@ -8563,10 +8519,10 @@
         <v>24</v>
       </c>
       <c r="C286" s="3" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D286" s="17" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.45">
@@ -8577,10 +8533,10 @@
         <v>24</v>
       </c>
       <c r="C287" s="3" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D287" s="17" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.45">
@@ -8591,10 +8547,10 @@
         <v>24</v>
       </c>
       <c r="C288" s="3" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="D288" s="17" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.45">
@@ -8605,10 +8561,10 @@
         <v>24</v>
       </c>
       <c r="C289" s="3" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="D289" s="17" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.45">
@@ -8619,10 +8575,10 @@
         <v>24</v>
       </c>
       <c r="C290" s="3" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="D290" s="17" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.45">
@@ -8633,10 +8589,10 @@
         <v>24</v>
       </c>
       <c r="C291" s="3" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="D291" s="17" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.45">
@@ -8647,10 +8603,10 @@
         <v>24</v>
       </c>
       <c r="C292" s="3" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="D292" s="17" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.45">
@@ -8661,10 +8617,10 @@
         <v>24</v>
       </c>
       <c r="C293" s="3" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D293" s="17" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.45">
@@ -8675,10 +8631,10 @@
         <v>24</v>
       </c>
       <c r="C294" s="3" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="D294" s="17" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.45">
@@ -8689,10 +8645,10 @@
         <v>24</v>
       </c>
       <c r="C295" s="3" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="D295" s="17" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.45">
@@ -8703,10 +8659,10 @@
         <v>24</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D296" s="17" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.45">
@@ -8717,10 +8673,10 @@
         <v>24</v>
       </c>
       <c r="C297" s="3" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D297" s="17" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.45">
@@ -8731,10 +8687,10 @@
         <v>24</v>
       </c>
       <c r="C298" s="3" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="D298" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.45">
@@ -8745,10 +8701,10 @@
         <v>24</v>
       </c>
       <c r="C299" s="3" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="D299" s="17" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.45">
@@ -8759,10 +8715,10 @@
         <v>24</v>
       </c>
       <c r="C300" s="3" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D300" s="17" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.45">
@@ -8773,10 +8729,10 @@
         <v>24</v>
       </c>
       <c r="C301" s="3" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D301" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.45">
@@ -8787,10 +8743,10 @@
         <v>24</v>
       </c>
       <c r="C302" s="3" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D302" s="17" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.45">
@@ -8801,10 +8757,10 @@
         <v>24</v>
       </c>
       <c r="C303" s="3" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D303" s="17" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.45">
@@ -8815,10 +8771,10 @@
         <v>24</v>
       </c>
       <c r="C304" s="3" t="s">
-        <v>378</v>
+        <v>915</v>
       </c>
       <c r="D304" s="17" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.45">
@@ -8829,10 +8785,10 @@
         <v>24</v>
       </c>
       <c r="C305" s="3" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="D305" s="17" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.45">
@@ -8843,10 +8799,10 @@
         <v>24</v>
       </c>
       <c r="C306" s="3" t="s">
-        <v>380</v>
+        <v>916</v>
       </c>
       <c r="D306" s="17" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.45">
@@ -8857,10 +8813,10 @@
         <v>24</v>
       </c>
       <c r="C307" s="3" t="s">
-        <v>923</v>
+        <v>384</v>
       </c>
       <c r="D307" s="17" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.45">
@@ -8871,10 +8827,10 @@
         <v>24</v>
       </c>
       <c r="C308" s="3" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D308" s="17" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.45">
@@ -8885,10 +8841,10 @@
         <v>24</v>
       </c>
       <c r="C309" s="3" t="s">
-        <v>924</v>
+        <v>387</v>
       </c>
       <c r="D309" s="17" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.45">
@@ -8899,10 +8855,10 @@
         <v>24</v>
       </c>
       <c r="C310" s="3" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="D310" s="17" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.45">
@@ -8913,10 +8869,10 @@
         <v>24</v>
       </c>
       <c r="C311" s="3" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="D311" s="17" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.45">
@@ -8927,10 +8883,10 @@
         <v>24</v>
       </c>
       <c r="C312" s="3" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="D312" s="17" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.45">
@@ -8941,10 +8897,10 @@
         <v>24</v>
       </c>
       <c r="C313" s="3" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="D313" s="17" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.45">
@@ -8955,10 +8911,10 @@
         <v>24</v>
       </c>
       <c r="C314" s="3" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="D314" s="17" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.45">
@@ -8969,10 +8925,10 @@
         <v>24</v>
       </c>
       <c r="C315" s="3" t="s">
-        <v>390</v>
+        <v>33</v>
       </c>
       <c r="D315" s="17" t="s">
-        <v>390</v>
+        <v>33</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.45">
@@ -8983,10 +8939,10 @@
         <v>24</v>
       </c>
       <c r="C316" s="3" t="s">
-        <v>391</v>
+        <v>39</v>
       </c>
       <c r="D316" s="17" t="s">
-        <v>391</v>
+        <v>39</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.45">
@@ -8997,10 +8953,10 @@
         <v>24</v>
       </c>
       <c r="C317" s="3" t="s">
-        <v>392</v>
+        <v>40</v>
       </c>
       <c r="D317" s="17" t="s">
-        <v>392</v>
+        <v>40</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.45">
@@ -9011,10 +8967,10 @@
         <v>24</v>
       </c>
       <c r="C318" s="3" t="s">
-        <v>33</v>
+        <v>396</v>
       </c>
       <c r="D318" s="17" t="s">
-        <v>33</v>
+        <v>396</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.45">
@@ -9025,10 +8981,10 @@
         <v>24</v>
       </c>
       <c r="C319" s="3" t="s">
-        <v>39</v>
+        <v>397</v>
       </c>
       <c r="D319" s="17" t="s">
-        <v>39</v>
+        <v>397</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.45">
@@ -9039,10 +8995,10 @@
         <v>24</v>
       </c>
       <c r="C320" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D320" s="17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.45">
@@ -9053,10 +9009,10 @@
         <v>24</v>
       </c>
       <c r="C321" s="3" t="s">
-        <v>396</v>
+        <v>42</v>
       </c>
       <c r="D321" s="17" t="s">
-        <v>396</v>
+        <v>42</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.45">
@@ -9067,10 +9023,10 @@
         <v>24</v>
       </c>
       <c r="C322" s="3" t="s">
-        <v>397</v>
+        <v>43</v>
       </c>
       <c r="D322" s="17" t="s">
-        <v>397</v>
+        <v>43</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.45">
@@ -9081,10 +9037,10 @@
         <v>24</v>
       </c>
       <c r="C323" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D323" s="17" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.45">
@@ -9095,10 +9051,10 @@
         <v>24</v>
       </c>
       <c r="C324" s="3" t="s">
-        <v>42</v>
+        <v>398</v>
       </c>
       <c r="D324" s="17" t="s">
-        <v>42</v>
+        <v>398</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.45">
@@ -9109,10 +9065,10 @@
         <v>24</v>
       </c>
       <c r="C325" s="3" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="D325" s="17" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.45">
@@ -9123,10 +9079,10 @@
         <v>24</v>
       </c>
       <c r="C326" s="3" t="s">
-        <v>44</v>
+        <v>400</v>
       </c>
       <c r="D326" s="17" t="s">
-        <v>44</v>
+        <v>400</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.45">
@@ -9137,10 +9093,10 @@
         <v>24</v>
       </c>
       <c r="C327" s="3" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D327" s="17" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.45">
@@ -9151,10 +9107,10 @@
         <v>24</v>
       </c>
       <c r="C328" s="3" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D328" s="17" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.45">
@@ -9165,10 +9121,10 @@
         <v>24</v>
       </c>
       <c r="C329" s="3" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="D329" s="17" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.45">
@@ -9179,10 +9135,10 @@
         <v>24</v>
       </c>
       <c r="C330" s="3" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="D330" s="17" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.45">
@@ -9193,10 +9149,10 @@
         <v>24</v>
       </c>
       <c r="C331" s="3" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="D331" s="17" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.45">
@@ -9207,10 +9163,10 @@
         <v>24</v>
       </c>
       <c r="C332" s="3" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D332" s="17" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.45">
@@ -9221,10 +9177,10 @@
         <v>24</v>
       </c>
       <c r="C333" s="3" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="D333" s="17" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.45">
@@ -9235,10 +9191,10 @@
         <v>24</v>
       </c>
       <c r="C334" s="3" t="s">
-        <v>405</v>
+        <v>45</v>
       </c>
       <c r="D334" s="17" t="s">
-        <v>405</v>
+        <v>45</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.45">
@@ -9249,10 +9205,10 @@
         <v>24</v>
       </c>
       <c r="C335" s="3" t="s">
-        <v>406</v>
+        <v>46</v>
       </c>
       <c r="D335" s="17" t="s">
-        <v>406</v>
+        <v>46</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.45">
@@ -9260,13 +9216,13 @@
         <v>25</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C336" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="D336" s="17" t="s">
-        <v>407</v>
+        <v>393</v>
+      </c>
+      <c r="D336" s="16" t="s">
+        <v>888</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.45">
@@ -9274,13 +9230,13 @@
         <v>25</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C337" s="3" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D337" s="17" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.45">
@@ -9288,13 +9244,13 @@
         <v>25</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>46</v>
+        <v>394</v>
       </c>
       <c r="D338" s="17" t="s">
-        <v>46</v>
+        <v>394</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.45">
@@ -9305,10 +9261,10 @@
         <v>23</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="D339" s="16" t="s">
-        <v>888</v>
+        <v>395</v>
+      </c>
+      <c r="D339" s="17" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.45">
@@ -9319,10 +9275,10 @@
         <v>23</v>
       </c>
       <c r="C340" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D340" s="17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.45">
@@ -9333,10 +9289,10 @@
         <v>23</v>
       </c>
       <c r="C341" s="3" t="s">
-        <v>394</v>
+        <v>36</v>
       </c>
       <c r="D341" s="17" t="s">
-        <v>394</v>
+        <v>36</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.45">
@@ -9347,10 +9303,10 @@
         <v>23</v>
       </c>
       <c r="C342" s="3" t="s">
-        <v>395</v>
+        <v>37</v>
       </c>
       <c r="D342" s="17" t="s">
-        <v>395</v>
+        <v>37</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.45">
@@ -9361,192 +9317,198 @@
         <v>23</v>
       </c>
       <c r="C343" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D343" s="17" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A344" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B344" s="2" t="s">
-        <v>23</v>
+        <v>48</v>
+      </c>
+      <c r="B344" s="33" t="s">
+        <v>24</v>
       </c>
       <c r="C344" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D344" s="17" t="s">
-        <v>36</v>
+        <v>49</v>
+      </c>
+      <c r="D344" s="14" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A345" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B345" s="2" t="s">
-        <v>23</v>
+        <v>48</v>
+      </c>
+      <c r="B345" s="33" t="s">
+        <v>24</v>
       </c>
       <c r="C345" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D345" s="17" t="s">
-        <v>37</v>
+        <v>50</v>
+      </c>
+      <c r="D345" s="14" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A346" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B346" s="2" t="s">
-        <v>23</v>
+        <v>48</v>
+      </c>
+      <c r="B346" s="33" t="s">
+        <v>24</v>
       </c>
       <c r="C346" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D346" s="17" t="s">
-        <v>38</v>
+        <v>51</v>
+      </c>
+      <c r="D346" s="14" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A347" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B347" s="38" t="s">
+      <c r="B347" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C347" s="3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D347" s="14" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A348" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B348" s="38" t="s">
+      <c r="B348" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C348" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D348" s="14" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A349" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B349" s="38" t="s">
+      <c r="B349" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C349" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D349" s="14" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A350" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B350" s="38" t="s">
+      <c r="B350" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C350" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D350" s="14" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A351" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B351" s="38" t="s">
+      <c r="B351" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C351" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D351" s="14" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A352" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B352" s="38" t="s">
+      <c r="B352" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C352" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D352" s="14" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.45">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A353" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B353" s="38" t="s">
+      <c r="B353" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C353" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D353" s="14" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.45">
+        <v>58</v>
+      </c>
+      <c r="E353" s="19"/>
+      <c r="F353" s="14"/>
+    </row>
+    <row r="354" spans="1:6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A354" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B354" s="38" t="s">
+      <c r="B354" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C354" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D354" s="14" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.45">
+        <v>59</v>
+      </c>
+      <c r="E354" s="19"/>
+      <c r="F354" s="14"/>
+    </row>
+    <row r="355" spans="1:6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A355" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B355" s="38" t="s">
+      <c r="B355" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C355" s="3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D355" s="14" t="s">
-        <v>57</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="E355" s="19"/>
+      <c r="F355" s="14"/>
     </row>
     <row r="356" spans="1:6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A356" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B356" s="38" t="s">
+      <c r="B356" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C356" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D356" s="14" t="s">
-        <v>58</v>
+        <v>909</v>
       </c>
       <c r="E356" s="19"/>
       <c r="F356" s="14"/>
@@ -9555,14 +9517,14 @@
       <c r="A357" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B357" s="38" t="s">
+      <c r="B357" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C357" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D357" s="14" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E357" s="19"/>
       <c r="F357" s="14"/>
@@ -9571,14 +9533,14 @@
       <c r="A358" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B358" s="38" t="s">
+      <c r="B358" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C358" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D358" s="14" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E358" s="19"/>
       <c r="F358" s="14"/>
@@ -9587,14 +9549,14 @@
       <c r="A359" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B359" s="38" t="s">
+      <c r="B359" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C359" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D359" s="14" t="s">
-        <v>917</v>
+        <v>64</v>
       </c>
       <c r="E359" s="19"/>
       <c r="F359" s="14"/>
@@ -9603,14 +9565,14 @@
       <c r="A360" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B360" s="38" t="s">
+      <c r="B360" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C360" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D360" s="14" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E360" s="19"/>
       <c r="F360" s="14"/>
@@ -9619,14 +9581,14 @@
       <c r="A361" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B361" s="38" t="s">
+      <c r="B361" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C361" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D361" s="14" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E361" s="19"/>
       <c r="F361" s="14"/>
@@ -9635,14 +9597,14 @@
       <c r="A362" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B362" s="38" t="s">
+      <c r="B362" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C362" s="3" t="s">
-        <v>64</v>
+        <v>480</v>
       </c>
       <c r="D362" s="14" t="s">
-        <v>64</v>
+        <v>480</v>
       </c>
       <c r="E362" s="19"/>
       <c r="F362" s="14"/>
@@ -9651,14 +9613,14 @@
       <c r="A363" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B363" s="38" t="s">
+      <c r="B363" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C363" s="3" t="s">
-        <v>65</v>
+        <v>481</v>
       </c>
       <c r="D363" s="14" t="s">
-        <v>65</v>
+        <v>481</v>
       </c>
       <c r="E363" s="19"/>
       <c r="F363" s="14"/>
@@ -9667,14 +9629,14 @@
       <c r="A364" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B364" s="38" t="s">
+      <c r="B364" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C364" s="3" t="s">
-        <v>66</v>
+        <v>482</v>
       </c>
       <c r="D364" s="14" t="s">
-        <v>66</v>
+        <v>482</v>
       </c>
       <c r="E364" s="19"/>
       <c r="F364" s="14"/>
@@ -9683,14 +9645,14 @@
       <c r="A365" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B365" s="38" t="s">
+      <c r="B365" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C365" s="3" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="D365" s="14" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="E365" s="19"/>
       <c r="F365" s="14"/>
@@ -9699,14 +9661,14 @@
       <c r="A366" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B366" s="38" t="s">
+      <c r="B366" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C366" s="3" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D366" s="14" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="E366" s="19"/>
       <c r="F366" s="14"/>
@@ -9715,14 +9677,14 @@
       <c r="A367" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B367" s="38" t="s">
+      <c r="B367" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C367" s="3" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="D367" s="14" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="E367" s="19"/>
       <c r="F367" s="14"/>
@@ -9731,14 +9693,14 @@
       <c r="A368" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B368" s="38" t="s">
+      <c r="B368" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C368" s="3" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="D368" s="14" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="E368" s="19"/>
       <c r="F368" s="14"/>
@@ -9747,14 +9709,14 @@
       <c r="A369" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B369" s="38" t="s">
+      <c r="B369" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C369" s="3" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="D369" s="14" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="E369" s="19"/>
       <c r="F369" s="14"/>
@@ -9763,14 +9725,14 @@
       <c r="A370" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B370" s="38" t="s">
+      <c r="B370" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C370" s="3" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D370" s="14" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="E370" s="19"/>
       <c r="F370" s="14"/>
@@ -9779,14 +9741,14 @@
       <c r="A371" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B371" s="38" t="s">
+      <c r="B371" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C371" s="3" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="D371" s="14" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E371" s="19"/>
       <c r="F371" s="14"/>
@@ -9795,14 +9757,14 @@
       <c r="A372" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B372" s="38" t="s">
+      <c r="B372" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C372" s="3" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="D372" s="14" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="E372" s="19"/>
       <c r="F372" s="14"/>
@@ -9811,14 +9773,14 @@
       <c r="A373" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B373" s="38" t="s">
+      <c r="B373" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C373" s="3" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="D373" s="14" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="E373" s="19"/>
       <c r="F373" s="14"/>
@@ -9827,14 +9789,14 @@
       <c r="A374" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B374" s="38" t="s">
+      <c r="B374" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C374" s="3" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D374" s="14" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="E374" s="19"/>
       <c r="F374" s="14"/>
@@ -9843,14 +9805,14 @@
       <c r="A375" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B375" s="38" t="s">
+      <c r="B375" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C375" s="3" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="D375" s="14" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E375" s="19"/>
       <c r="F375" s="14"/>
@@ -9859,14 +9821,14 @@
       <c r="A376" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B376" s="38" t="s">
+      <c r="B376" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C376" s="3" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="D376" s="14" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E376" s="19"/>
       <c r="F376" s="14"/>
@@ -9875,14 +9837,14 @@
       <c r="A377" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B377" s="38" t="s">
+      <c r="B377" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C377" s="3" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="D377" s="14" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="E377" s="19"/>
       <c r="F377" s="14"/>
@@ -9891,14 +9853,14 @@
       <c r="A378" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B378" s="38" t="s">
+      <c r="B378" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C378" s="3" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="D378" s="14" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E378" s="19"/>
       <c r="F378" s="14"/>
@@ -9907,14 +9869,14 @@
       <c r="A379" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B379" s="38" t="s">
+      <c r="B379" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C379" s="3" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D379" s="14" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E379" s="19"/>
       <c r="F379" s="14"/>
@@ -9923,14 +9885,14 @@
       <c r="A380" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B380" s="38" t="s">
+      <c r="B380" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C380" s="3" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="D380" s="14" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="E380" s="19"/>
       <c r="F380" s="14"/>
@@ -9939,14 +9901,14 @@
       <c r="A381" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B381" s="38" t="s">
+      <c r="B381" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C381" s="3" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D381" s="14" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="E381" s="19"/>
       <c r="F381" s="14"/>
@@ -9955,14 +9917,14 @@
       <c r="A382" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B382" s="38" t="s">
+      <c r="B382" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C382" s="3" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="D382" s="14" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="E382" s="19"/>
       <c r="F382" s="14"/>
@@ -9971,14 +9933,14 @@
       <c r="A383" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B383" s="38" t="s">
+      <c r="B383" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C383" s="3" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="D383" s="14" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="E383" s="19"/>
       <c r="F383" s="14"/>
@@ -9987,14 +9949,14 @@
       <c r="A384" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B384" s="38" t="s">
+      <c r="B384" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C384" s="3" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="D384" s="14" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="E384" s="19"/>
       <c r="F384" s="14"/>
@@ -10003,14 +9965,14 @@
       <c r="A385" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B385" s="38" t="s">
+      <c r="B385" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C385" s="3" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="D385" s="14" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="E385" s="19"/>
       <c r="F385" s="14"/>
@@ -10019,14 +9981,14 @@
       <c r="A386" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B386" s="38" t="s">
+      <c r="B386" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C386" s="3" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="D386" s="14" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="E386" s="19"/>
       <c r="F386" s="14"/>
@@ -10035,14 +9997,14 @@
       <c r="A387" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B387" s="38" t="s">
+      <c r="B387" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C387" s="3" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="D387" s="14" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="E387" s="19"/>
       <c r="F387" s="14"/>
@@ -10051,14 +10013,14 @@
       <c r="A388" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B388" s="38" t="s">
+      <c r="B388" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C388" s="3" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="D388" s="14" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="E388" s="19"/>
       <c r="F388" s="14"/>
@@ -10067,14 +10029,14 @@
       <c r="A389" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B389" s="38" t="s">
+      <c r="B389" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C389" s="3" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="D389" s="14" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E389" s="19"/>
       <c r="F389" s="14"/>
@@ -10083,14 +10045,14 @@
       <c r="A390" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B390" s="38" t="s">
+      <c r="B390" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C390" s="3" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="D390" s="14" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="E390" s="19"/>
       <c r="F390" s="14"/>
@@ -10099,14 +10061,14 @@
       <c r="A391" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B391" s="38" t="s">
+      <c r="B391" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C391" s="3" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="D391" s="14" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="E391" s="19"/>
       <c r="F391" s="14"/>
@@ -10115,14 +10077,14 @@
       <c r="A392" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B392" s="38" t="s">
+      <c r="B392" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C392" s="3" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D392" s="14" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="E392" s="19"/>
       <c r="F392" s="14"/>
@@ -10131,14 +10093,14 @@
       <c r="A393" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B393" s="38" t="s">
+      <c r="B393" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C393" s="3" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="D393" s="14" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="E393" s="19"/>
       <c r="F393" s="14"/>
@@ -10147,113 +10109,113 @@
       <c r="A394" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B394" s="38" t="s">
+      <c r="B394" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C394" s="3" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D394" s="14" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="E394" s="19"/>
       <c r="F394" s="14"/>
+      <c r="G394" s="21"/>
     </row>
     <row r="395" spans="1:7" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A395" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B395" s="38" t="s">
+      <c r="B395" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C395" s="3" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D395" s="14" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E395" s="19"/>
       <c r="F395" s="14"/>
+      <c r="G395" s="21"/>
     </row>
     <row r="396" spans="1:7" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A396" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B396" s="38" t="s">
+      <c r="B396" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C396" s="3" t="s">
-        <v>511</v>
+        <v>917</v>
       </c>
       <c r="D396" s="14" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="E396" s="19"/>
       <c r="F396" s="14"/>
+      <c r="G396" s="21"/>
     </row>
     <row r="397" spans="1:7" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A397" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B397" s="38" t="s">
+      <c r="B397" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C397" s="3" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="D397" s="14" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="E397" s="19"/>
       <c r="F397" s="14"/>
-      <c r="G397" s="23"/>
     </row>
     <row r="398" spans="1:7" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A398" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B398" s="38" t="s">
+      <c r="B398" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C398" s="3" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="D398" s="14" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="E398" s="19"/>
       <c r="F398" s="14"/>
-      <c r="G398" s="23"/>
     </row>
     <row r="399" spans="1:7" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A399" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B399" s="38" t="s">
+      <c r="B399" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C399" s="3" t="s">
-        <v>925</v>
+        <v>517</v>
       </c>
       <c r="D399" s="14" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="E399" s="19"/>
       <c r="F399" s="14"/>
-      <c r="G399" s="23"/>
     </row>
     <row r="400" spans="1:7" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A400" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B400" s="38" t="s">
+      <c r="B400" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C400" s="3" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="D400" s="14" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E400" s="19"/>
       <c r="F400" s="14"/>
@@ -10262,148 +10224,142 @@
       <c r="A401" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B401" s="38" t="s">
+      <c r="B401" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C401" s="3" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D401" s="14" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="E401" s="19"/>
       <c r="F401" s="14"/>
     </row>
-    <row r="402" spans="1:6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="402" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A402" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B402" s="38" t="s">
+      <c r="B402" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C402" s="3" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="D402" s="14" t="s">
-        <v>517</v>
-      </c>
-      <c r="E402" s="19"/>
-      <c r="F402" s="14"/>
-    </row>
-    <row r="403" spans="1:6" customFormat="1" x14ac:dyDescent="0.45">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="403" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A403" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B403" s="38" t="s">
+      <c r="B403" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C403" s="3" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="D403" s="14" t="s">
-        <v>518</v>
-      </c>
-      <c r="E403" s="19"/>
-      <c r="F403" s="14"/>
-    </row>
-    <row r="404" spans="1:6" customFormat="1" x14ac:dyDescent="0.45">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="404" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A404" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B404" s="38" t="s">
+      <c r="B404" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C404" s="3" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="D404" s="14" t="s">
-        <v>519</v>
-      </c>
-      <c r="E404" s="19"/>
-      <c r="F404" s="14"/>
+        <v>522</v>
+      </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A405" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B405" s="38" t="s">
+      <c r="B405" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C405" s="3" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D405" s="14" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A406" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B406" s="38" t="s">
+      <c r="B406" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C406" s="3" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="D406" s="14" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A407" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B407" s="38" t="s">
+      <c r="B407" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C407" s="3" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="D407" s="14" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A408" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B408" s="38" t="s">
+      <c r="B408" s="14" t="s">
         <v>24</v>
       </c>
       <c r="C408" s="3" t="s">
-        <v>523</v>
+        <v>533</v>
       </c>
       <c r="D408" s="14" t="s">
-        <v>523</v>
+        <v>533</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A409" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B409" s="38" t="s">
+      <c r="B409" s="14" t="s">
         <v>24</v>
       </c>
       <c r="C409" s="3" t="s">
-        <v>524</v>
+        <v>534</v>
       </c>
       <c r="D409" s="14" t="s">
-        <v>524</v>
+        <v>534</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A410" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B410" s="38" t="s">
+      <c r="B410" s="14" t="s">
         <v>24</v>
       </c>
       <c r="C410" s="3" t="s">
-        <v>525</v>
+        <v>535</v>
       </c>
       <c r="D410" s="14" t="s">
-        <v>525</v>
+        <v>535</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.45">
@@ -10414,10 +10370,10 @@
         <v>24</v>
       </c>
       <c r="C411" s="3" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="D411" s="14" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.45">
@@ -10428,10 +10384,10 @@
         <v>24</v>
       </c>
       <c r="C412" s="3" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="D412" s="14" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.45">
@@ -10442,10 +10398,10 @@
         <v>24</v>
       </c>
       <c r="C413" s="3" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="D413" s="14" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.45">
@@ -10456,10 +10412,10 @@
         <v>24</v>
       </c>
       <c r="C414" s="3" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="D414" s="14" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.45">
@@ -10470,10 +10426,10 @@
         <v>24</v>
       </c>
       <c r="C415" s="3" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="D415" s="14" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.45">
@@ -10484,10 +10440,10 @@
         <v>24</v>
       </c>
       <c r="C416" s="3" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="D416" s="14" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.45">
@@ -10498,10 +10454,10 @@
         <v>24</v>
       </c>
       <c r="C417" s="3" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="D417" s="14" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.45">
@@ -10512,10 +10468,10 @@
         <v>24</v>
       </c>
       <c r="C418" s="3" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D418" s="14" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.45">
@@ -10526,10 +10482,10 @@
         <v>24</v>
       </c>
       <c r="C419" s="3" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="D419" s="14" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.45">
@@ -10540,10 +10496,10 @@
         <v>24</v>
       </c>
       <c r="C420" s="3" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D420" s="14" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.45">
@@ -10554,10 +10510,10 @@
         <v>24</v>
       </c>
       <c r="C421" s="3" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="D421" s="14" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.45">
@@ -10568,10 +10524,10 @@
         <v>24</v>
       </c>
       <c r="C422" s="3" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="D422" s="14" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.45">
@@ -10582,10 +10538,10 @@
         <v>24</v>
       </c>
       <c r="C423" s="3" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="D423" s="14" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.45">
@@ -10596,10 +10552,10 @@
         <v>24</v>
       </c>
       <c r="C424" s="3" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="D424" s="14" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.45">
@@ -10610,10 +10566,10 @@
         <v>24</v>
       </c>
       <c r="C425" s="3" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="D425" s="14" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.45">
@@ -10624,10 +10580,10 @@
         <v>24</v>
       </c>
       <c r="C426" s="3" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="D426" s="14" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.45">
@@ -10638,10 +10594,10 @@
         <v>24</v>
       </c>
       <c r="C427" s="3" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="D427" s="14" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.45">
@@ -10652,10 +10608,10 @@
         <v>24</v>
       </c>
       <c r="C428" s="3" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D428" s="14" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.45">
@@ -10666,10 +10622,10 @@
         <v>24</v>
       </c>
       <c r="C429" s="3" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="D429" s="14" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.45">
@@ -10680,10 +10636,10 @@
         <v>24</v>
       </c>
       <c r="C430" s="3" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="D430" s="14" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.45">
@@ -10694,10 +10650,10 @@
         <v>24</v>
       </c>
       <c r="C431" s="3" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D431" s="14" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.45">
@@ -10708,10 +10664,10 @@
         <v>24</v>
       </c>
       <c r="C432" s="3" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="D432" s="14" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.45">
@@ -10722,10 +10678,10 @@
         <v>24</v>
       </c>
       <c r="C433" s="3" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="D433" s="14" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.45">
@@ -10736,10 +10692,10 @@
         <v>24</v>
       </c>
       <c r="C434" s="3" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="D434" s="14" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.45">
@@ -10750,24 +10706,10 @@
         <v>24</v>
       </c>
       <c r="C435" s="3" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="D435" s="14" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A436" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B436" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C436" s="3" t="s">
-        <v>558</v>
-      </c>
-      <c r="D436" s="14" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.45">
@@ -10777,11 +10719,15 @@
       <c r="B437" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C437" s="3" t="s">
-        <v>559</v>
-      </c>
-      <c r="D437" s="14" t="s">
-        <v>559</v>
+      <c r="C437" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="D437" s="17" t="s">
+        <v>908</v>
+      </c>
+      <c r="F437" s="14" t="e">
+        <f>_xlfn.XLOOKUP(#REF!,'[1]Hem Catalogue'!$C$545:$C$643,'[1]Hem Catalogue'!$D$545:$D$643,"")</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.45">
@@ -10789,13 +10735,13 @@
         <v>48</v>
       </c>
       <c r="B438" s="14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C438" s="3" t="s">
-        <v>560</v>
+        <v>526</v>
       </c>
       <c r="D438" s="14" t="s">
-        <v>560</v>
+        <v>526</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.45">
@@ -10806,10 +10752,10 @@
         <v>23</v>
       </c>
       <c r="C439" s="3" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D439" s="14" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.45">
@@ -10820,10 +10766,10 @@
         <v>23</v>
       </c>
       <c r="C440" s="3" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D440" s="14" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.45">
@@ -10834,10 +10780,10 @@
         <v>23</v>
       </c>
       <c r="C441" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D441" s="14" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.45">
@@ -10848,10 +10794,10 @@
         <v>23</v>
       </c>
       <c r="C442" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D442" s="14" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.45">
@@ -10862,10 +10808,10 @@
         <v>23</v>
       </c>
       <c r="C443" s="3" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D443" s="14" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.45">
@@ -10876,79 +10822,67 @@
         <v>23</v>
       </c>
       <c r="C444" s="3" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D444" s="14" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A445" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B445" s="14" t="s">
-        <v>23</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="B445"/>
       <c r="C445" s="3" t="s">
-        <v>532</v>
-      </c>
-      <c r="D445" s="14" t="s">
-        <v>532</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="D445" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="E445" s="2"/>
+      <c r="F445"/>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A446" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B446" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C446" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="D446" s="17" t="s">
-        <v>916</v>
-      </c>
-      <c r="F446" s="14" t="e">
-        <f>_xlfn.XLOOKUP(#REF!,'[1]Hem Catalogue'!$C$545:$C$643,'[1]Hem Catalogue'!$D$545:$D$643,"")</f>
-        <v>#REF!</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="B446"/>
+      <c r="C446" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="D446" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="E446" s="2"/>
+      <c r="F446"/>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A447" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B447" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C447" s="5" t="s">
-        <v>563</v>
-      </c>
-      <c r="D447" s="17" t="s">
-        <v>914</v>
-      </c>
-      <c r="F447" s="14" t="e">
-        <f>_xlfn.XLOOKUP(#REF!,'[1]Hem Catalogue'!$C$545:$C$643,'[1]Hem Catalogue'!$D$545:$D$643,"")</f>
-        <v>#REF!</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="B447"/>
+      <c r="C447" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="D447" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E447" s="2"/>
+      <c r="F447"/>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A448" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B448" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C448" s="2" t="s">
-        <v>807</v>
-      </c>
-      <c r="D448" s="17" t="s">
-        <v>915</v>
-      </c>
-      <c r="F448" s="14" t="e">
-        <f>_xlfn.XLOOKUP(#REF!,'[1]Hem Catalogue'!$C$545:$C$643,'[1]Hem Catalogue'!$D$545:$D$643,"")</f>
-        <v>#REF!</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="B448"/>
+      <c r="C448" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="D448" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="E448" s="2"/>
+      <c r="F448"/>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A449" s="2" t="s">
@@ -10956,83 +10890,81 @@
       </c>
       <c r="B449"/>
       <c r="C449" s="3" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="E449" s="2"/>
       <c r="F449"/>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A450" s="2" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="B450"/>
       <c r="C450" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="D450" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="E450" s="2"/>
+        <v>418</v>
+      </c>
+      <c r="D450" s="11" t="s">
+        <v>848</v>
+      </c>
+      <c r="E450"/>
       <c r="F450"/>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A451" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="B451"/>
+        <v>416</v>
+      </c>
+      <c r="B451" s="2"/>
       <c r="C451" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="D451" s="2" t="s">
-        <v>411</v>
+        <v>454</v>
+      </c>
+      <c r="D451" s="11" t="s">
+        <v>847</v>
       </c>
       <c r="E451" s="2"/>
       <c r="F451"/>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A452" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="B452"/>
+        <v>416</v>
+      </c>
+      <c r="B452" s="2"/>
       <c r="C452" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="D452" s="2" t="s">
-        <v>412</v>
+        <v>419</v>
+      </c>
+      <c r="D452" s="11" t="s">
+        <v>849</v>
       </c>
       <c r="E452" s="2"/>
       <c r="F452"/>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A453" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="B453"/>
+        <v>416</v>
+      </c>
+      <c r="B453" s="2"/>
       <c r="C453" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="D453" s="2" t="s">
-        <v>413</v>
+        <v>420</v>
+      </c>
+      <c r="D453" s="11" t="s">
+        <v>850</v>
       </c>
       <c r="E453" s="2"/>
-      <c r="F453"/>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A454" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="B454"/>
+      <c r="B454" s="2"/>
       <c r="C454" s="3" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="D454" s="11" t="s">
-        <v>848</v>
-      </c>
-      <c r="E454"/>
-      <c r="F454"/>
+        <v>851</v>
+      </c>
+      <c r="E454" s="2"/>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A455" s="2" t="s">
@@ -11040,13 +10972,12 @@
       </c>
       <c r="B455" s="2"/>
       <c r="C455" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D455" s="11" t="s">
-        <v>847</v>
+        <v>852</v>
       </c>
       <c r="E455" s="2"/>
-      <c r="F455"/>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A456" s="2" t="s">
@@ -11054,13 +10985,12 @@
       </c>
       <c r="B456" s="2"/>
       <c r="C456" s="3" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="D456" s="11" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="E456" s="2"/>
-      <c r="F456"/>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A457" s="2" t="s">
@@ -11068,10 +10998,10 @@
       </c>
       <c r="B457" s="2"/>
       <c r="C457" s="3" t="s">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="D457" s="11" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="E457" s="2"/>
     </row>
@@ -11081,10 +11011,10 @@
       </c>
       <c r="B458" s="2"/>
       <c r="C458" s="3" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="D458" s="11" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="E458" s="2"/>
     </row>
@@ -11094,10 +11024,10 @@
       </c>
       <c r="B459" s="2"/>
       <c r="C459" s="3" t="s">
-        <v>455</v>
+        <v>426</v>
       </c>
       <c r="D459" s="11" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="E459" s="2"/>
     </row>
@@ -11107,10 +11037,10 @@
       </c>
       <c r="B460" s="2"/>
       <c r="C460" s="3" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D460" s="11" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="E460" s="2"/>
     </row>
@@ -11120,10 +11050,10 @@
       </c>
       <c r="B461" s="2"/>
       <c r="C461" s="3" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D461" s="11" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="E461" s="2"/>
     </row>
@@ -11133,10 +11063,10 @@
       </c>
       <c r="B462" s="2"/>
       <c r="C462" s="3" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="D462" s="11" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="E462" s="2"/>
     </row>
@@ -11146,10 +11076,10 @@
       </c>
       <c r="B463" s="2"/>
       <c r="C463" s="3" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D463" s="11" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="E463" s="2"/>
     </row>
@@ -11159,10 +11089,10 @@
       </c>
       <c r="B464" s="2"/>
       <c r="C464" s="3" t="s">
-        <v>427</v>
+        <v>452</v>
       </c>
       <c r="D464" s="11" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="E464" s="2"/>
     </row>
@@ -11172,10 +11102,10 @@
       </c>
       <c r="B465" s="2"/>
       <c r="C465" s="3" t="s">
-        <v>428</v>
+        <v>451</v>
       </c>
       <c r="D465" s="11" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="E465" s="2"/>
     </row>
@@ -11185,10 +11115,10 @@
       </c>
       <c r="B466" s="2"/>
       <c r="C466" s="3" t="s">
-        <v>430</v>
+        <v>458</v>
       </c>
       <c r="D466" s="11" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="E466" s="2"/>
     </row>
@@ -11198,10 +11128,10 @@
       </c>
       <c r="B467" s="2"/>
       <c r="C467" s="3" t="s">
-        <v>429</v>
+        <v>444</v>
       </c>
       <c r="D467" s="11" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="E467" s="2"/>
     </row>
@@ -11211,10 +11141,10 @@
       </c>
       <c r="B468" s="2"/>
       <c r="C468" s="3" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="D468" s="11" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="E468" s="2"/>
     </row>
@@ -11224,10 +11154,10 @@
       </c>
       <c r="B469" s="2"/>
       <c r="C469" s="3" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="D469" s="11" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="E469" s="2"/>
     </row>
@@ -11237,88 +11167,88 @@
       </c>
       <c r="B470" s="2"/>
       <c r="C470" s="3" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="D470" s="11" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="E470" s="2"/>
     </row>
-    <row r="471" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="471" spans="1:5" s="25" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A471" s="2" t="s">
         <v>416</v>
       </c>
       <c r="B471" s="2"/>
       <c r="C471" s="3" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="D471" s="11" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="E471" s="2"/>
     </row>
-    <row r="472" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="472" spans="1:5" s="28" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A472" s="2" t="s">
         <v>416</v>
       </c>
       <c r="B472" s="2"/>
       <c r="C472" s="3" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D472" s="11" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="E472" s="2"/>
     </row>
-    <row r="473" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="473" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A473" s="2" t="s">
         <v>416</v>
       </c>
       <c r="B473" s="2"/>
       <c r="C473" s="3" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="D473" s="11" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="E473" s="2"/>
     </row>
-    <row r="474" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="474" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A474" s="2" t="s">
         <v>416</v>
       </c>
       <c r="B474" s="2"/>
       <c r="C474" s="3" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="D474" s="11" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="E474" s="2"/>
     </row>
-    <row r="475" spans="1:5" s="30" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A475" s="2" t="s">
         <v>416</v>
       </c>
       <c r="B475" s="2"/>
       <c r="C475" s="3" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="D475" s="11" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="E475" s="2"/>
     </row>
-    <row r="476" spans="1:5" s="33" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A476" s="2" t="s">
         <v>416</v>
       </c>
       <c r="B476" s="2"/>
       <c r="C476" s="3" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="D476" s="11" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="E476" s="2"/>
     </row>
@@ -11328,10 +11258,10 @@
       </c>
       <c r="B477" s="2"/>
       <c r="C477" s="3" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D477" s="11" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="E477" s="2"/>
     </row>
@@ -11341,10 +11271,10 @@
       </c>
       <c r="B478" s="2"/>
       <c r="C478" s="3" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="D478" s="11" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="E478" s="2"/>
     </row>
@@ -11354,10 +11284,10 @@
       </c>
       <c r="B479" s="2"/>
       <c r="C479" s="3" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="D479" s="11" t="s">
-        <v>872</v>
+        <v>456</v>
       </c>
       <c r="E479" s="2"/>
     </row>
@@ -11367,10 +11297,10 @@
       </c>
       <c r="B480" s="2"/>
       <c r="C480" s="3" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="D480" s="11" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="E480" s="2"/>
     </row>
@@ -11380,23 +11310,23 @@
       </c>
       <c r="B481" s="2"/>
       <c r="C481" s="3" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D481" s="11" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="E481" s="2"/>
     </row>
-    <row r="482" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:5" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A482" s="2" t="s">
         <v>416</v>
       </c>
       <c r="B482" s="2"/>
       <c r="C482" s="3" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D482" s="11" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="E482" s="2"/>
     </row>
@@ -11406,10 +11336,10 @@
       </c>
       <c r="B483" s="2"/>
       <c r="C483" s="3" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="D483" s="11" t="s">
-        <v>456</v>
+        <v>879</v>
       </c>
       <c r="E483" s="2"/>
     </row>
@@ -11419,10 +11349,10 @@
       </c>
       <c r="B484" s="2"/>
       <c r="C484" s="3" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D484" s="11" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="E484" s="2"/>
     </row>
@@ -11432,23 +11362,23 @@
       </c>
       <c r="B485" s="2"/>
       <c r="C485" s="3" t="s">
-        <v>438</v>
+        <v>457</v>
       </c>
       <c r="D485" s="11" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="E485" s="2"/>
     </row>
-    <row r="486" spans="1:5" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A486" s="2" t="s">
         <v>416</v>
       </c>
       <c r="B486" s="2"/>
       <c r="C486" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="D486" s="11" t="s">
-        <v>878</v>
+        <v>422</v>
+      </c>
+      <c r="D486" s="2" t="s">
+        <v>422</v>
       </c>
       <c r="E486" s="2"/>
     </row>
@@ -11458,10 +11388,10 @@
       </c>
       <c r="B487" s="2"/>
       <c r="C487" s="3" t="s">
-        <v>439</v>
-      </c>
-      <c r="D487" s="11" t="s">
-        <v>879</v>
+        <v>423</v>
+      </c>
+      <c r="D487" s="2" t="s">
+        <v>423</v>
       </c>
       <c r="E487" s="2"/>
     </row>
@@ -11471,10 +11401,10 @@
       </c>
       <c r="B488" s="2"/>
       <c r="C488" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="D488" s="11" t="s">
-        <v>880</v>
+        <v>450</v>
+      </c>
+      <c r="D488" s="2" t="s">
+        <v>450</v>
       </c>
       <c r="E488" s="2"/>
     </row>
@@ -11484,10 +11414,10 @@
       </c>
       <c r="B489" s="2"/>
       <c r="C489" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="D489" s="11" t="s">
-        <v>881</v>
+        <v>453</v>
+      </c>
+      <c r="D489" s="2" t="s">
+        <v>453</v>
       </c>
       <c r="E489" s="2"/>
     </row>
@@ -11497,170 +11427,135 @@
       </c>
       <c r="B490" s="2"/>
       <c r="C490" s="3" t="s">
-        <v>422</v>
+        <v>456</v>
       </c>
       <c r="D490" s="2" t="s">
-        <v>422</v>
+        <v>456</v>
       </c>
       <c r="E490" s="2"/>
     </row>
-    <row r="491" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A491" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="B491" s="2"/>
-      <c r="C491" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="D491" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="E491" s="2"/>
-    </row>
-    <row r="492" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A492" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="B492" s="2"/>
-      <c r="C492" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="D492" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="E492" s="2"/>
-    </row>
-    <row r="493" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A493" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="B493" s="2"/>
-      <c r="C493" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="D493" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="E493" s="2"/>
-    </row>
     <row r="494" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A494" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="B494" s="2"/>
+      <c r="A494" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="B494" s="32"/>
       <c r="C494" s="3" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="D494" s="2" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="E494" s="2"/>
     </row>
     <row r="495" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A495" s="5" t="s">
-        <v>912</v>
-      </c>
-      <c r="B495" s="20" t="s">
-        <v>469</v>
-      </c>
-      <c r="C495" s="21" t="s">
-        <v>474</v>
-      </c>
-      <c r="D495" s="22"/>
-      <c r="E495" s="20"/>
+        <v>459</v>
+      </c>
+      <c r="B495" s="32"/>
+      <c r="C495" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="D495" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E495" s="2"/>
     </row>
     <row r="496" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A496" s="24" t="s">
-        <v>912</v>
-      </c>
-      <c r="B496" s="20" t="s">
-        <v>468</v>
-      </c>
-      <c r="C496" s="25" t="s">
-        <v>468</v>
-      </c>
-      <c r="D496" s="26" t="s">
-        <v>889</v>
-      </c>
-      <c r="E496" s="27"/>
+      <c r="A496" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="B496" s="32"/>
+      <c r="C496" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="D496" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="E496" s="2"/>
     </row>
     <row r="497" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A497" s="24" t="s">
-        <v>912</v>
-      </c>
-      <c r="B497" s="28" t="s">
-        <v>466</v>
-      </c>
-      <c r="C497" s="29" t="s">
-        <v>466</v>
-      </c>
-      <c r="D497" s="26" t="s">
-        <v>887</v>
-      </c>
-      <c r="E497" s="27"/>
+      <c r="A497" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="B497" s="32"/>
+      <c r="C497" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="D497" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="E497" s="2"/>
     </row>
     <row r="498" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A498" s="5" t="s">
         <v>459</v>
       </c>
-      <c r="B498" s="37"/>
+      <c r="B498" s="32"/>
       <c r="C498" s="3" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="D498" s="2" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E498" s="2"/>
     </row>
     <row r="499" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A499" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="B499" s="37"/>
+        <v>565</v>
+      </c>
+      <c r="B499" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="C499" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="D499" s="2" t="s">
-        <v>462</v>
+        <v>825</v>
+      </c>
+      <c r="D499" s="11" t="s">
+        <v>825</v>
       </c>
       <c r="E499" s="2"/>
     </row>
     <row r="500" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A500" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="B500" s="37"/>
+        <v>565</v>
+      </c>
+      <c r="B500" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="C500" s="3" t="s">
-        <v>463</v>
+        <v>67</v>
       </c>
       <c r="D500" s="2" t="s">
-        <v>463</v>
+        <v>67</v>
       </c>
       <c r="E500" s="2"/>
     </row>
     <row r="501" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A501" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="B501" s="37"/>
+        <v>565</v>
+      </c>
+      <c r="B501" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="C501" s="3" t="s">
-        <v>464</v>
+        <v>68</v>
       </c>
       <c r="D501" s="2" t="s">
-        <v>464</v>
+        <v>68</v>
       </c>
       <c r="E501" s="2"/>
     </row>
     <row r="502" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A502" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="B502" s="37"/>
+        <v>565</v>
+      </c>
+      <c r="B502" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="C502" s="3" t="s">
-        <v>465</v>
+        <v>69</v>
       </c>
       <c r="D502" s="2" t="s">
-        <v>465</v>
+        <v>69</v>
       </c>
       <c r="E502" s="2"/>
     </row>
@@ -11672,10 +11567,10 @@
         <v>24</v>
       </c>
       <c r="C503" s="3" t="s">
-        <v>825</v>
-      </c>
-      <c r="D503" s="11" t="s">
-        <v>825</v>
+        <v>70</v>
+      </c>
+      <c r="D503" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="E503" s="2"/>
     </row>
@@ -11687,10 +11582,10 @@
         <v>24</v>
       </c>
       <c r="C504" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D504" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E504" s="2"/>
     </row>
@@ -11702,10 +11597,10 @@
         <v>24</v>
       </c>
       <c r="C505" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D505" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E505" s="2"/>
     </row>
@@ -11717,10 +11612,10 @@
         <v>24</v>
       </c>
       <c r="C506" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D506" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E506" s="2"/>
     </row>
@@ -11732,10 +11627,10 @@
         <v>24</v>
       </c>
       <c r="C507" s="3" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D507" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E507" s="2"/>
     </row>
@@ -11747,10 +11642,10 @@
         <v>24</v>
       </c>
       <c r="C508" s="3" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D508" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E508" s="2"/>
     </row>
@@ -11762,10 +11657,10 @@
         <v>24</v>
       </c>
       <c r="C509" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D509" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E509" s="2"/>
     </row>
@@ -11777,10 +11672,10 @@
         <v>24</v>
       </c>
       <c r="C510" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D510" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E510" s="2"/>
     </row>
@@ -11792,10 +11687,10 @@
         <v>24</v>
       </c>
       <c r="C511" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D511" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E511" s="2"/>
     </row>
@@ -11807,10 +11702,10 @@
         <v>24</v>
       </c>
       <c r="C512" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D512" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E512" s="2"/>
     </row>
@@ -11822,10 +11717,10 @@
         <v>24</v>
       </c>
       <c r="C513" s="3" t="s">
-        <v>76</v>
+        <v>566</v>
       </c>
       <c r="D513" s="2" t="s">
-        <v>76</v>
+        <v>566</v>
       </c>
       <c r="E513" s="2"/>
     </row>
@@ -11837,10 +11732,10 @@
         <v>24</v>
       </c>
       <c r="C514" s="3" t="s">
-        <v>77</v>
+        <v>567</v>
       </c>
       <c r="D514" s="2" t="s">
-        <v>77</v>
+        <v>567</v>
       </c>
       <c r="E514" s="2"/>
     </row>
@@ -11852,10 +11747,10 @@
         <v>24</v>
       </c>
       <c r="C515" s="3" t="s">
-        <v>78</v>
+        <v>568</v>
       </c>
       <c r="D515" s="2" t="s">
-        <v>78</v>
+        <v>568</v>
       </c>
       <c r="E515" s="2"/>
     </row>
@@ -11867,10 +11762,10 @@
         <v>24</v>
       </c>
       <c r="C516" s="3" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="D516" s="2" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="E516" s="2"/>
     </row>
@@ -11882,10 +11777,10 @@
         <v>24</v>
       </c>
       <c r="C517" s="3" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="D517" s="2" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="E517" s="2"/>
     </row>
@@ -11897,10 +11792,10 @@
         <v>24</v>
       </c>
       <c r="C518" s="3" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="D518" s="2" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="E518" s="2"/>
     </row>
@@ -11912,10 +11807,10 @@
         <v>24</v>
       </c>
       <c r="C519" s="3" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="D519" s="2" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="E519" s="2"/>
     </row>
@@ -11927,10 +11822,10 @@
         <v>24</v>
       </c>
       <c r="C520" s="3" t="s">
-        <v>101</v>
+        <v>572</v>
       </c>
       <c r="D520" s="2" t="s">
-        <v>101</v>
+        <v>572</v>
       </c>
       <c r="E520" s="2"/>
     </row>
@@ -11942,10 +11837,10 @@
         <v>24</v>
       </c>
       <c r="C521" s="3" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="D521" s="2" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="E521" s="2"/>
     </row>
@@ -11957,10 +11852,10 @@
         <v>24</v>
       </c>
       <c r="C522" s="3" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="D522" s="2" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="E522" s="2"/>
     </row>
@@ -11972,10 +11867,10 @@
         <v>24</v>
       </c>
       <c r="C523" s="3" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="D523" s="2" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="E523" s="2"/>
     </row>
@@ -11987,10 +11882,10 @@
         <v>24</v>
       </c>
       <c r="C524" s="3" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="D524" s="2" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="E524" s="2"/>
     </row>
@@ -12002,10 +11897,10 @@
         <v>24</v>
       </c>
       <c r="C525" s="3" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="D525" s="2" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="E525" s="2"/>
     </row>
@@ -12017,10 +11912,10 @@
         <v>24</v>
       </c>
       <c r="C526" s="3" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="D526" s="2" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="E526" s="2"/>
     </row>
@@ -12029,28 +11924,28 @@
         <v>565</v>
       </c>
       <c r="B527" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C527" s="3" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="D527" s="2" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="E527" s="2"/>
     </row>
-    <row r="528" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A528" s="5" t="s">
         <v>565</v>
       </c>
       <c r="B528" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C528" s="3" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="D528" s="2" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="E528" s="2"/>
     </row>
@@ -12059,13 +11954,13 @@
         <v>565</v>
       </c>
       <c r="B529" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C529" s="3" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="D529" s="2" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="E529" s="2"/>
     </row>
@@ -12074,13 +11969,13 @@
         <v>565</v>
       </c>
       <c r="B530" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C530" s="3" t="s">
-        <v>578</v>
+        <v>100</v>
       </c>
       <c r="D530" s="2" t="s">
-        <v>578</v>
+        <v>100</v>
       </c>
       <c r="E530" s="2"/>
     </row>
@@ -12092,14 +11987,14 @@
         <v>23</v>
       </c>
       <c r="C531" s="3" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="D531" s="2" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="E531" s="2"/>
     </row>
-    <row r="532" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="532" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A532" s="5" t="s">
         <v>565</v>
       </c>
@@ -12107,10 +12002,10 @@
         <v>23</v>
       </c>
       <c r="C532" s="3" t="s">
-        <v>581</v>
+        <v>102</v>
       </c>
       <c r="D532" s="2" t="s">
-        <v>581</v>
+        <v>102</v>
       </c>
       <c r="E532" s="2"/>
     </row>
@@ -12122,10 +12017,10 @@
         <v>23</v>
       </c>
       <c r="C533" s="3" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="D533" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E533" s="2"/>
     </row>
@@ -12134,13 +12029,13 @@
         <v>565</v>
       </c>
       <c r="B534" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C534" s="3" t="s">
-        <v>100</v>
+        <v>585</v>
       </c>
       <c r="D534" s="2" t="s">
-        <v>100</v>
+        <v>585</v>
       </c>
       <c r="E534" s="2"/>
     </row>
@@ -12149,13 +12044,13 @@
         <v>565</v>
       </c>
       <c r="B535" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C535" s="3" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="D535" s="2" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="E535" s="2"/>
     </row>
@@ -12164,13 +12059,13 @@
         <v>565</v>
       </c>
       <c r="B536" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C536" s="3" t="s">
-        <v>102</v>
+        <v>587</v>
       </c>
       <c r="D536" s="2" t="s">
-        <v>102</v>
+        <v>587</v>
       </c>
       <c r="E536" s="2"/>
     </row>
@@ -12179,13 +12074,13 @@
         <v>565</v>
       </c>
       <c r="B537" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C537" s="3" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="D537" s="2" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="E537" s="2"/>
     </row>
@@ -12197,10 +12092,10 @@
         <v>24</v>
       </c>
       <c r="C538" s="3" t="s">
-        <v>585</v>
+        <v>104</v>
       </c>
       <c r="D538" s="2" t="s">
-        <v>585</v>
+        <v>104</v>
       </c>
       <c r="E538" s="2"/>
     </row>
@@ -12212,10 +12107,10 @@
         <v>24</v>
       </c>
       <c r="C539" s="3" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="D539" s="2" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E539" s="2"/>
     </row>
@@ -12227,10 +12122,10 @@
         <v>24</v>
       </c>
       <c r="C540" s="3" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="D540" s="2" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="E540" s="2"/>
     </row>
@@ -12242,10 +12137,10 @@
         <v>24</v>
       </c>
       <c r="C541" s="3" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="D541" s="2" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="E541" s="2"/>
     </row>
@@ -12257,10 +12152,10 @@
         <v>24</v>
       </c>
       <c r="C542" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D542" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E542" s="2"/>
     </row>
@@ -12272,10 +12167,10 @@
         <v>24</v>
       </c>
       <c r="C543" s="3" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="D543" s="2" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="E543" s="2"/>
     </row>
@@ -12287,10 +12182,10 @@
         <v>24</v>
       </c>
       <c r="C544" s="3" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="D544" s="2" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="E544" s="2"/>
     </row>
@@ -12299,13 +12194,13 @@
         <v>565</v>
       </c>
       <c r="B545" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C545" s="3" t="s">
-        <v>591</v>
+        <v>811</v>
+      </c>
+      <c r="C545" s="5" t="s">
+        <v>811</v>
       </c>
       <c r="D545" s="2" t="s">
-        <v>591</v>
+        <v>811</v>
       </c>
       <c r="E545" s="2"/>
     </row>
@@ -12313,14 +12208,14 @@
       <c r="A546" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="B546" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C546" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D546" s="2" t="s">
-        <v>103</v>
+      <c r="B546" s="9" t="s">
+        <v>595</v>
+      </c>
+      <c r="C546" s="9" t="s">
+        <v>595</v>
+      </c>
+      <c r="D546" s="11" t="s">
+        <v>819</v>
       </c>
       <c r="E546" s="2"/>
     </row>
@@ -12328,113 +12223,105 @@
       <c r="A547" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="B547" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C547" s="3" t="s">
-        <v>592</v>
-      </c>
-      <c r="D547" s="2" t="s">
-        <v>592</v>
+      <c r="B547" s="9" t="s">
+        <v>596</v>
+      </c>
+      <c r="C547" s="9" t="s">
+        <v>596</v>
+      </c>
+      <c r="D547" s="11" t="s">
+        <v>820</v>
       </c>
       <c r="E547" s="2"/>
     </row>
     <row r="548" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A548" s="5" t="s">
-        <v>565</v>
-      </c>
-      <c r="B548" s="5" t="s">
-        <v>24</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="B548" s="2"/>
       <c r="C548" s="3" t="s">
-        <v>593</v>
-      </c>
-      <c r="D548" s="2" t="s">
-        <v>593</v>
+        <v>84</v>
+      </c>
+      <c r="D548" s="11" t="s">
+        <v>882</v>
       </c>
       <c r="E548" s="2"/>
     </row>
     <row r="549" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A549" s="5" t="s">
-        <v>565</v>
-      </c>
-      <c r="B549" s="5" t="s">
-        <v>811</v>
-      </c>
-      <c r="C549" s="5" t="s">
-        <v>811</v>
-      </c>
-      <c r="D549" s="2" t="s">
-        <v>811</v>
+        <v>85</v>
+      </c>
+      <c r="B549" s="2"/>
+      <c r="C549" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D549" s="11" t="s">
+        <v>883</v>
       </c>
       <c r="E549" s="2"/>
     </row>
     <row r="550" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A550" s="5" t="s">
-        <v>565</v>
-      </c>
-      <c r="B550" s="9" t="s">
-        <v>595</v>
-      </c>
-      <c r="C550" s="9" t="s">
-        <v>595</v>
+        <v>85</v>
+      </c>
+      <c r="B550" s="2"/>
+      <c r="C550" s="3" t="s">
+        <v>83</v>
       </c>
       <c r="D550" s="11" t="s">
-        <v>819</v>
+        <v>884</v>
       </c>
       <c r="E550" s="2"/>
     </row>
     <row r="551" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A551" s="5" t="s">
-        <v>565</v>
-      </c>
-      <c r="B551" s="9" t="s">
-        <v>596</v>
-      </c>
-      <c r="C551" s="9" t="s">
-        <v>596</v>
-      </c>
-      <c r="D551" s="11" t="s">
-        <v>820</v>
+        <v>86</v>
+      </c>
+      <c r="B551" s="2"/>
+      <c r="C551" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D551" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="E551" s="2"/>
     </row>
     <row r="552" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A552" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B552" s="2"/>
       <c r="C552" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D552" s="11" t="s">
-        <v>882</v>
+        <v>88</v>
+      </c>
+      <c r="D552" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="E552" s="2"/>
     </row>
     <row r="553" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A553" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B553" s="2"/>
       <c r="C553" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D553" s="11" t="s">
-        <v>883</v>
+        <v>89</v>
+      </c>
+      <c r="D553" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="E553" s="2"/>
     </row>
-    <row r="554" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:5" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A554" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B554" s="2"/>
       <c r="C554" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D554" s="11" t="s">
-        <v>884</v>
+        <v>90</v>
+      </c>
+      <c r="D554" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="E554" s="2"/>
     </row>
@@ -12444,10 +12331,10 @@
       </c>
       <c r="B555" s="2"/>
       <c r="C555" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D555" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E555" s="2"/>
     </row>
@@ -12457,10 +12344,10 @@
       </c>
       <c r="B556" s="2"/>
       <c r="C556" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D556" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E556" s="2"/>
     </row>
@@ -12470,23 +12357,23 @@
       </c>
       <c r="B557" s="2"/>
       <c r="C557" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D557" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E557" s="2"/>
     </row>
-    <row r="558" spans="1:5" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A558" s="5" t="s">
         <v>86</v>
       </c>
       <c r="B558" s="2"/>
       <c r="C558" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D558" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E558" s="2"/>
     </row>
@@ -12496,10 +12383,10 @@
       </c>
       <c r="B559" s="2"/>
       <c r="C559" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D559" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E559" s="2"/>
     </row>
@@ -12509,10 +12396,10 @@
       </c>
       <c r="B560" s="2"/>
       <c r="C560" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D560" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E560" s="2"/>
     </row>
@@ -12522,10 +12409,10 @@
       </c>
       <c r="B561" s="2"/>
       <c r="C561" s="3" t="s">
-        <v>93</v>
+        <v>599</v>
       </c>
       <c r="D561" s="2" t="s">
-        <v>93</v>
+        <v>599</v>
       </c>
       <c r="E561" s="2"/>
     </row>
@@ -12535,10 +12422,10 @@
       </c>
       <c r="B562" s="2"/>
       <c r="C562" s="3" t="s">
-        <v>94</v>
+        <v>600</v>
       </c>
       <c r="D562" s="2" t="s">
-        <v>94</v>
+        <v>600</v>
       </c>
       <c r="E562" s="2"/>
     </row>
@@ -12548,10 +12435,10 @@
       </c>
       <c r="B563" s="2"/>
       <c r="C563" s="3" t="s">
-        <v>95</v>
+        <v>601</v>
       </c>
       <c r="D563" s="2" t="s">
-        <v>95</v>
+        <v>601</v>
       </c>
       <c r="E563" s="2"/>
     </row>
@@ -12561,10 +12448,10 @@
       </c>
       <c r="B564" s="2"/>
       <c r="C564" s="3" t="s">
-        <v>96</v>
+        <v>602</v>
       </c>
       <c r="D564" s="2" t="s">
-        <v>96</v>
+        <v>602</v>
       </c>
       <c r="E564" s="2"/>
     </row>
@@ -12574,10 +12461,10 @@
       </c>
       <c r="B565" s="2"/>
       <c r="C565" s="3" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="D565" s="2" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="E565" s="2"/>
     </row>
@@ -12587,10 +12474,10 @@
       </c>
       <c r="B566" s="2"/>
       <c r="C566" s="3" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="D566" s="2" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="E566" s="2"/>
     </row>
@@ -12600,10 +12487,10 @@
       </c>
       <c r="B567" s="2"/>
       <c r="C567" s="3" t="s">
-        <v>927</v>
+        <v>605</v>
       </c>
       <c r="D567" s="2" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="E567" s="2"/>
     </row>
@@ -12613,194 +12500,194 @@
       </c>
       <c r="B568" s="2"/>
       <c r="C568" s="3" t="s">
-        <v>602</v>
-      </c>
-      <c r="D568" s="2" t="s">
-        <v>602</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="D568" s="11"/>
       <c r="E568" s="2"/>
     </row>
     <row r="569" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A569" s="5" t="s">
+      <c r="A569" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="B569" s="2"/>
-      <c r="C569" s="3" t="s">
-        <v>603</v>
-      </c>
-      <c r="D569" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="E569" s="2"/>
+      <c r="B569" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="C569" s="7" t="s">
+        <v>606</v>
+      </c>
+      <c r="D569" s="10" t="s">
+        <v>817</v>
+      </c>
+      <c r="E569" s="10"/>
     </row>
     <row r="570" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A570" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B570" s="2"/>
+      <c r="A570" s="26" t="s">
+        <v>906</v>
+      </c>
+      <c r="B570" s="26" t="s">
+        <v>612</v>
+      </c>
       <c r="C570" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="D570" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="E570" s="2"/>
+        <v>921</v>
+      </c>
+      <c r="D570" s="27" t="s">
+        <v>818</v>
+      </c>
+      <c r="E570" s="27"/>
     </row>
     <row r="571" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A571" s="5" t="s">
-        <v>86</v>
+      <c r="A571" s="2" t="s">
+        <v>614</v>
       </c>
       <c r="B571" s="2"/>
       <c r="C571" s="3" t="s">
-        <v>605</v>
+        <v>617</v>
       </c>
       <c r="D571" s="2" t="s">
-        <v>605</v>
+        <v>617</v>
       </c>
       <c r="E571" s="2"/>
     </row>
     <row r="572" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A572" s="5" t="s">
-        <v>86</v>
+      <c r="A572" s="2" t="s">
+        <v>614</v>
       </c>
       <c r="B572" s="2"/>
       <c r="C572" s="3" t="s">
-        <v>607</v>
-      </c>
-      <c r="D572" s="11"/>
+        <v>618</v>
+      </c>
+      <c r="D572" s="2" t="s">
+        <v>618</v>
+      </c>
       <c r="E572" s="2"/>
     </row>
     <row r="573" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A573" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="B573" s="6" t="s">
-        <v>608</v>
-      </c>
-      <c r="C573" s="7" t="s">
-        <v>606</v>
-      </c>
-      <c r="D573" s="10" t="s">
-        <v>817</v>
-      </c>
-      <c r="E573" s="10"/>
+      <c r="A573" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="B573" s="2"/>
+      <c r="C573" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="D573" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="E573" s="2"/>
     </row>
     <row r="574" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A574" s="31" t="s">
-        <v>913</v>
-      </c>
-      <c r="B574" s="31" t="s">
-        <v>612</v>
-      </c>
-      <c r="C574" s="31" t="s">
-        <v>612</v>
-      </c>
-      <c r="D574" s="32" t="s">
-        <v>818</v>
-      </c>
-      <c r="E574" s="32"/>
+      <c r="A574" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="B574" s="2"/>
+      <c r="C574" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="D574" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="E574" s="2"/>
     </row>
     <row r="575" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A575" s="2" t="s">
-        <v>614</v>
+      <c r="A575" s="5" t="s">
+        <v>616</v>
       </c>
       <c r="B575" s="2"/>
-      <c r="C575" s="3" t="s">
-        <v>617</v>
-      </c>
-      <c r="D575" s="2" t="s">
-        <v>617</v>
+      <c r="C575" s="11" t="s">
+        <v>885</v>
+      </c>
+      <c r="D575" s="11" t="s">
+        <v>885</v>
       </c>
       <c r="E575" s="2"/>
     </row>
     <row r="576" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A576" s="2" t="s">
-        <v>614</v>
+      <c r="A576" s="5" t="s">
+        <v>616</v>
       </c>
       <c r="B576" s="2"/>
       <c r="C576" s="3" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="D576" s="2" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="E576" s="2"/>
     </row>
     <row r="577" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A577" s="2" t="s">
-        <v>614</v>
+      <c r="A577" s="5" t="s">
+        <v>616</v>
       </c>
       <c r="B577" s="2"/>
       <c r="C577" s="3" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="D577" s="2" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="E577" s="2"/>
     </row>
     <row r="578" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A578" s="2" t="s">
-        <v>614</v>
+      <c r="A578" s="5" t="s">
+        <v>616</v>
       </c>
       <c r="B578" s="2"/>
       <c r="C578" s="3" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="D578" s="2" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="E578" s="2"/>
     </row>
-    <row r="579" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A579" s="5" t="s">
         <v>616</v>
       </c>
       <c r="B579" s="2"/>
-      <c r="C579" s="11" t="s">
-        <v>885</v>
-      </c>
-      <c r="D579" s="11" t="s">
-        <v>885</v>
+      <c r="C579" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="D579" s="2" t="s">
+        <v>625</v>
       </c>
       <c r="E579" s="2"/>
     </row>
-    <row r="580" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A580" s="5" t="s">
         <v>616</v>
       </c>
       <c r="B580" s="2"/>
       <c r="C580" s="3" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="D580" s="2" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="E580" s="2"/>
     </row>
-    <row r="581" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A581" s="5" t="s">
         <v>616</v>
       </c>
       <c r="B581" s="2"/>
       <c r="C581" s="3" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="D581" s="2" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="E581" s="2"/>
     </row>
-    <row r="582" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A582" s="5" t="s">
         <v>616</v>
       </c>
       <c r="B582" s="2"/>
       <c r="C582" s="3" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D582" s="2" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="E582" s="2"/>
     </row>
@@ -12810,10 +12697,10 @@
       </c>
       <c r="B583" s="2"/>
       <c r="C583" s="3" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D583" s="2" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="E583" s="2"/>
     </row>
@@ -12823,10 +12710,10 @@
       </c>
       <c r="B584" s="2"/>
       <c r="C584" s="3" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="D584" s="2" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="E584" s="2"/>
     </row>
@@ -12836,10 +12723,10 @@
       </c>
       <c r="B585" s="2"/>
       <c r="C585" s="3" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="D585" s="2" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="E585" s="2"/>
     </row>
@@ -12849,10 +12736,10 @@
       </c>
       <c r="B586" s="2"/>
       <c r="C586" s="3" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D586" s="2" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="E586" s="2"/>
     </row>
@@ -12862,10 +12749,10 @@
       </c>
       <c r="B587" s="2"/>
       <c r="C587" s="3" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="D587" s="2" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="E587" s="2"/>
     </row>
@@ -12875,10 +12762,10 @@
       </c>
       <c r="B588" s="2"/>
       <c r="C588" s="3" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="D588" s="2" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="E588" s="2"/>
     </row>
@@ -12888,10 +12775,10 @@
       </c>
       <c r="B589" s="2"/>
       <c r="C589" s="3" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="D589" s="2" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="E589" s="2"/>
     </row>
@@ -12901,10 +12788,10 @@
       </c>
       <c r="B590" s="2"/>
       <c r="C590" s="3" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="D590" s="2" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="E590" s="2"/>
     </row>
@@ -12914,10 +12801,10 @@
       </c>
       <c r="B591" s="2"/>
       <c r="C591" s="3" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="D591" s="2" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="E591" s="2"/>
     </row>
@@ -12927,10 +12814,10 @@
       </c>
       <c r="B592" s="2"/>
       <c r="C592" s="3" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="D592" s="2" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="E592" s="2"/>
     </row>
@@ -12940,10 +12827,10 @@
       </c>
       <c r="B593" s="2"/>
       <c r="C593" s="3" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="D593" s="2" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="E593" s="2"/>
     </row>
@@ -12953,10 +12840,10 @@
       </c>
       <c r="B594" s="2"/>
       <c r="C594" s="3" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="D594" s="2" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="E594" s="2"/>
     </row>
@@ -12966,10 +12853,10 @@
       </c>
       <c r="B595" s="2"/>
       <c r="C595" s="3" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D595" s="2" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="E595" s="2"/>
     </row>
@@ -12979,10 +12866,10 @@
       </c>
       <c r="B596" s="2"/>
       <c r="C596" s="3" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="D596" s="2" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="E596" s="2"/>
     </row>
@@ -12992,10 +12879,10 @@
       </c>
       <c r="B597" s="2"/>
       <c r="C597" s="3" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="D597" s="2" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E597" s="2"/>
     </row>
@@ -13005,10 +12892,10 @@
       </c>
       <c r="B598" s="2"/>
       <c r="C598" s="3" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="D598" s="2" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="E598" s="2"/>
     </row>
@@ -13018,10 +12905,10 @@
       </c>
       <c r="B599" s="2"/>
       <c r="C599" s="3" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="D599" s="2" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="E599" s="2"/>
     </row>
@@ -13031,10 +12918,10 @@
       </c>
       <c r="B600" s="2"/>
       <c r="C600" s="3" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="D600" s="2" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="E600" s="2"/>
     </row>
@@ -13042,64 +12929,72 @@
       <c r="A601" s="5" t="s">
         <v>616</v>
       </c>
-      <c r="B601" s="2"/>
+      <c r="B601"/>
       <c r="C601" s="3" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="D601" s="2" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E601" s="2"/>
     </row>
     <row r="602" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A602" s="5" t="s">
-        <v>616</v>
-      </c>
-      <c r="B602" s="2"/>
+        <v>649</v>
+      </c>
+      <c r="B602" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="C602" s="3" t="s">
-        <v>644</v>
-      </c>
-      <c r="D602" s="2" t="s">
-        <v>644</v>
+        <v>650</v>
+      </c>
+      <c r="D602" s="11" t="s">
+        <v>650</v>
       </c>
       <c r="E602" s="2"/>
     </row>
     <row r="603" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A603" s="5" t="s">
-        <v>616</v>
-      </c>
-      <c r="B603" s="2"/>
+        <v>649</v>
+      </c>
+      <c r="B603" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="C603" s="3" t="s">
-        <v>645</v>
-      </c>
-      <c r="D603" s="2" t="s">
-        <v>645</v>
+        <v>651</v>
+      </c>
+      <c r="D603" s="11" t="s">
+        <v>651</v>
       </c>
       <c r="E603" s="2"/>
     </row>
     <row r="604" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A604" s="5" t="s">
-        <v>616</v>
-      </c>
-      <c r="B604" s="2"/>
+        <v>649</v>
+      </c>
+      <c r="B604" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="C604" s="3" t="s">
-        <v>646</v>
-      </c>
-      <c r="D604" s="2" t="s">
-        <v>646</v>
+        <v>652</v>
+      </c>
+      <c r="D604" s="11" t="s">
+        <v>652</v>
       </c>
       <c r="E604" s="2"/>
     </row>
     <row r="605" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A605" s="5" t="s">
-        <v>616</v>
-      </c>
-      <c r="B605"/>
+        <v>649</v>
+      </c>
+      <c r="B605" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="C605" s="3" t="s">
-        <v>647</v>
-      </c>
-      <c r="D605" s="2" t="s">
-        <v>647</v>
+        <v>653</v>
+      </c>
+      <c r="D605" s="11" t="s">
+        <v>653</v>
       </c>
       <c r="E605" s="2"/>
     </row>
@@ -13108,13 +13003,13 @@
         <v>649</v>
       </c>
       <c r="B606" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C606" s="3" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="D606" s="11" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="E606" s="2"/>
     </row>
@@ -13126,10 +13021,10 @@
         <v>23</v>
       </c>
       <c r="C607" s="3" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="D607" s="11" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="E607" s="2"/>
     </row>
@@ -13141,10 +13036,10 @@
         <v>23</v>
       </c>
       <c r="C608" s="3" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="D608" s="11" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="E608" s="2"/>
     </row>
@@ -13156,10 +13051,10 @@
         <v>23</v>
       </c>
       <c r="C609" s="3" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="D609" s="11" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="E609" s="2"/>
     </row>
@@ -13171,10 +13066,10 @@
         <v>23</v>
       </c>
       <c r="C610" s="3" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="D610" s="11" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="E610" s="2"/>
     </row>
@@ -13186,10 +13081,10 @@
         <v>23</v>
       </c>
       <c r="C611" s="3" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="D611" s="11" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="E611" s="2"/>
     </row>
@@ -13201,10 +13096,10 @@
         <v>23</v>
       </c>
       <c r="C612" s="3" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="D612" s="11" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="E612" s="2"/>
     </row>
@@ -13216,10 +13111,10 @@
         <v>23</v>
       </c>
       <c r="C613" s="3" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="D613" s="11" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="E613" s="2"/>
     </row>
@@ -13231,10 +13126,10 @@
         <v>23</v>
       </c>
       <c r="C614" s="3" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="D614" s="11" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="E614" s="2"/>
     </row>
@@ -13245,73 +13140,73 @@
       <c r="B615" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C615" s="3" t="s">
-        <v>659</v>
-      </c>
-      <c r="D615" s="11" t="s">
-        <v>659</v>
-      </c>
-      <c r="E615" s="2"/>
+      <c r="C615" s="5" t="s">
+        <v>663</v>
+      </c>
+      <c r="D615" s="5" t="s">
+        <v>663</v>
+      </c>
+      <c r="E615" s="5"/>
     </row>
     <row r="616" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A616" s="5" t="s">
-        <v>649</v>
-      </c>
-      <c r="B616" s="5" t="s">
+        <v>665</v>
+      </c>
+      <c r="B616" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C616" s="3" t="s">
-        <v>660</v>
-      </c>
-      <c r="D616" s="11" t="s">
-        <v>660</v>
+        <v>667</v>
+      </c>
+      <c r="D616" s="2" t="s">
+        <v>667</v>
       </c>
       <c r="E616" s="2"/>
     </row>
     <row r="617" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A617" s="5" t="s">
-        <v>649</v>
-      </c>
-      <c r="B617" s="5" t="s">
+        <v>665</v>
+      </c>
+      <c r="B617" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C617" s="3" t="s">
-        <v>661</v>
-      </c>
-      <c r="D617" s="11" t="s">
-        <v>661</v>
+        <v>668</v>
+      </c>
+      <c r="D617" s="2" t="s">
+        <v>668</v>
       </c>
       <c r="E617" s="2"/>
     </row>
     <row r="618" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A618" s="5" t="s">
-        <v>649</v>
-      </c>
-      <c r="B618" s="5" t="s">
+        <v>665</v>
+      </c>
+      <c r="B618" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C618" s="3" t="s">
-        <v>662</v>
-      </c>
-      <c r="D618" s="11" t="s">
-        <v>662</v>
+        <v>669</v>
+      </c>
+      <c r="D618" s="2" t="s">
+        <v>669</v>
       </c>
       <c r="E618" s="2"/>
     </row>
     <row r="619" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A619" s="5" t="s">
-        <v>649</v>
-      </c>
-      <c r="B619" s="5" t="s">
+        <v>665</v>
+      </c>
+      <c r="B619" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C619" s="5" t="s">
-        <v>663</v>
-      </c>
-      <c r="D619" s="5" t="s">
-        <v>663</v>
-      </c>
-      <c r="E619" s="5"/>
+      <c r="C619" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="D619" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="E619" s="2"/>
     </row>
     <row r="620" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A620" s="5" t="s">
@@ -13321,10 +13216,10 @@
         <v>23</v>
       </c>
       <c r="C620" s="3" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="D620" s="2" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="E620" s="2"/>
     </row>
@@ -13336,10 +13231,10 @@
         <v>23</v>
       </c>
       <c r="C621" s="3" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="D621" s="2" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="E621" s="2"/>
     </row>
@@ -13348,125 +13243,120 @@
         <v>665</v>
       </c>
       <c r="B622" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C622" s="3" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="D622" s="2" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="E622" s="2"/>
     </row>
     <row r="623" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A623" s="5" t="s">
-        <v>665</v>
-      </c>
-      <c r="B623" s="2" t="s">
-        <v>23</v>
-      </c>
+        <v>674</v>
+      </c>
+      <c r="B623" s="2"/>
       <c r="C623" s="3" t="s">
-        <v>670</v>
-      </c>
-      <c r="D623" s="2" t="s">
-        <v>670</v>
+        <v>676</v>
+      </c>
+      <c r="D623" s="11" t="s">
+        <v>812</v>
       </c>
       <c r="E623" s="2"/>
     </row>
     <row r="624" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A624" s="5" t="s">
-        <v>665</v>
-      </c>
-      <c r="B624" s="2" t="s">
-        <v>23</v>
-      </c>
+        <v>674</v>
+      </c>
+      <c r="B624" s="2"/>
       <c r="C624" s="3" t="s">
-        <v>671</v>
-      </c>
-      <c r="D624" s="2" t="s">
-        <v>671</v>
+        <v>677</v>
+      </c>
+      <c r="D624" s="11" t="s">
+        <v>813</v>
       </c>
       <c r="E624" s="2"/>
     </row>
     <row r="625" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A625" s="5" t="s">
-        <v>665</v>
-      </c>
-      <c r="B625" s="2" t="s">
-        <v>23</v>
-      </c>
+        <v>674</v>
+      </c>
+      <c r="B625" s="2"/>
       <c r="C625" s="3" t="s">
-        <v>672</v>
-      </c>
-      <c r="D625" s="2" t="s">
-        <v>672</v>
+        <v>678</v>
+      </c>
+      <c r="D625" s="29" t="s">
+        <v>814</v>
       </c>
       <c r="E625" s="2"/>
     </row>
     <row r="626" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A626" s="5" t="s">
-        <v>665</v>
-      </c>
-      <c r="B626" s="2" t="s">
-        <v>24</v>
+        <v>674</v>
       </c>
       <c r="C626" s="3" t="s">
-        <v>666</v>
-      </c>
-      <c r="D626" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="E626" s="2"/>
+        <v>679</v>
+      </c>
+      <c r="D626" s="30" t="s">
+        <v>679</v>
+      </c>
     </row>
     <row r="627" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A627" s="5" t="s">
-        <v>674</v>
-      </c>
-      <c r="B627" s="2"/>
+        <v>683</v>
+      </c>
+      <c r="B627" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="C627" s="3" t="s">
-        <v>676</v>
-      </c>
-      <c r="D627" s="11" t="s">
-        <v>812</v>
-      </c>
+        <v>703</v>
+      </c>
+      <c r="D627" s="11"/>
       <c r="E627" s="2"/>
     </row>
     <row r="628" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A628" s="5" t="s">
-        <v>674</v>
-      </c>
-      <c r="B628" s="2"/>
+        <v>683</v>
+      </c>
+      <c r="B628" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="C628" s="3" t="s">
-        <v>677</v>
+        <v>701</v>
       </c>
       <c r="D628" s="11" t="s">
-        <v>813</v>
+        <v>827</v>
       </c>
       <c r="E628" s="2"/>
     </row>
     <row r="629" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A629" s="5" t="s">
-        <v>674</v>
-      </c>
-      <c r="B629" s="2"/>
+        <v>683</v>
+      </c>
+      <c r="B629" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="C629" s="3" t="s">
-        <v>678</v>
-      </c>
-      <c r="D629" s="34" t="s">
-        <v>814</v>
+        <v>702</v>
+      </c>
+      <c r="D629" s="11" t="s">
+        <v>826</v>
       </c>
       <c r="E629" s="2"/>
     </row>
     <row r="630" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A630" s="5" t="s">
-        <v>674</v>
+        <v>683</v>
+      </c>
+      <c r="B630" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="C630" s="3" t="s">
-        <v>679</v>
-      </c>
-      <c r="D630" s="35" t="s">
-        <v>679</v>
-      </c>
+        <v>706</v>
+      </c>
+      <c r="E630" s="2"/>
     </row>
     <row r="631" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A631" s="5" t="s">
@@ -13476,7 +13366,7 @@
         <v>24</v>
       </c>
       <c r="C631" s="3" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D631" s="11"/>
       <c r="E631" s="2"/>
@@ -13489,25 +13379,21 @@
         <v>24</v>
       </c>
       <c r="C632" s="3" t="s">
-        <v>701</v>
-      </c>
-      <c r="D632" s="11" t="s">
-        <v>827</v>
-      </c>
+        <v>705</v>
+      </c>
+      <c r="D632" s="11"/>
       <c r="E632" s="2"/>
     </row>
     <row r="633" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A633" s="5" t="s">
         <v>683</v>
       </c>
-      <c r="B633" s="2" t="s">
-        <v>24</v>
-      </c>
+      <c r="B633" s="2"/>
       <c r="C633" s="3" t="s">
-        <v>702</v>
-      </c>
-      <c r="D633" s="11" t="s">
-        <v>826</v>
+        <v>689</v>
+      </c>
+      <c r="D633" s="2" t="s">
+        <v>689</v>
       </c>
       <c r="E633" s="2"/>
     </row>
@@ -13515,11 +13401,12 @@
       <c r="A634" s="5" t="s">
         <v>683</v>
       </c>
-      <c r="B634" s="2" t="s">
-        <v>24</v>
-      </c>
+      <c r="B634" s="2"/>
       <c r="C634" s="3" t="s">
-        <v>706</v>
+        <v>690</v>
+      </c>
+      <c r="D634" s="2" t="s">
+        <v>690</v>
       </c>
       <c r="E634" s="2"/>
     </row>
@@ -13527,26 +13414,26 @@
       <c r="A635" s="5" t="s">
         <v>683</v>
       </c>
-      <c r="B635" s="2" t="s">
-        <v>24</v>
-      </c>
+      <c r="B635" s="2"/>
       <c r="C635" s="3" t="s">
-        <v>704</v>
-      </c>
-      <c r="D635" s="11"/>
+        <v>691</v>
+      </c>
+      <c r="D635" s="2" t="s">
+        <v>691</v>
+      </c>
       <c r="E635" s="2"/>
     </row>
     <row r="636" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A636" s="5" t="s">
         <v>683</v>
       </c>
-      <c r="B636" s="2" t="s">
-        <v>24</v>
-      </c>
+      <c r="B636" s="2"/>
       <c r="C636" s="3" t="s">
-        <v>705</v>
-      </c>
-      <c r="D636" s="11"/>
+        <v>692</v>
+      </c>
+      <c r="D636" s="2" t="s">
+        <v>692</v>
+      </c>
       <c r="E636" s="2"/>
     </row>
     <row r="637" spans="1:5" x14ac:dyDescent="0.45">
@@ -13555,10 +13442,10 @@
       </c>
       <c r="B637" s="2"/>
       <c r="C637" s="3" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="D637" s="2" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="E637" s="2"/>
     </row>
@@ -13568,10 +13455,10 @@
       </c>
       <c r="B638" s="2"/>
       <c r="C638" s="3" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="D638" s="2" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="E638" s="2"/>
     </row>
@@ -13581,10 +13468,10 @@
       </c>
       <c r="B639" s="2"/>
       <c r="C639" s="3" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="D639" s="2" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="E639" s="2"/>
     </row>
@@ -13594,10 +13481,10 @@
       </c>
       <c r="B640" s="2"/>
       <c r="C640" s="3" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="D640" s="2" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="E640" s="2"/>
     </row>
@@ -13607,11 +13494,9 @@
       </c>
       <c r="B641" s="2"/>
       <c r="C641" s="3" t="s">
-        <v>693</v>
-      </c>
-      <c r="D641" s="2" t="s">
-        <v>693</v>
-      </c>
+        <v>707</v>
+      </c>
+      <c r="D641" s="11"/>
       <c r="E641" s="2"/>
     </row>
     <row r="642" spans="1:5" x14ac:dyDescent="0.45">
@@ -13620,10 +13505,10 @@
       </c>
       <c r="B642" s="2"/>
       <c r="C642" s="3" t="s">
-        <v>694</v>
-      </c>
-      <c r="D642" s="2" t="s">
-        <v>694</v>
+        <v>685</v>
+      </c>
+      <c r="D642" s="11" t="s">
+        <v>828</v>
       </c>
       <c r="E642" s="2"/>
     </row>
@@ -13633,10 +13518,10 @@
       </c>
       <c r="B643" s="2"/>
       <c r="C643" s="3" t="s">
-        <v>699</v>
-      </c>
-      <c r="D643" s="2" t="s">
-        <v>699</v>
+        <v>686</v>
+      </c>
+      <c r="D643" s="11" t="s">
+        <v>829</v>
       </c>
       <c r="E643" s="2"/>
     </row>
@@ -13646,10 +13531,10 @@
       </c>
       <c r="B644" s="2"/>
       <c r="C644" s="3" t="s">
-        <v>700</v>
-      </c>
-      <c r="D644" s="2" t="s">
-        <v>700</v>
+        <v>687</v>
+      </c>
+      <c r="D644" s="11" t="s">
+        <v>830</v>
       </c>
       <c r="E644" s="2"/>
     </row>
@@ -13659,7 +13544,7 @@
       </c>
       <c r="B645" s="2"/>
       <c r="C645" s="3" t="s">
-        <v>707</v>
+        <v>688</v>
       </c>
       <c r="D645" s="11"/>
       <c r="E645" s="2"/>
@@ -13670,10 +13555,10 @@
       </c>
       <c r="B646" s="2"/>
       <c r="C646" s="3" t="s">
-        <v>685</v>
-      </c>
-      <c r="D646" s="11" t="s">
-        <v>828</v>
+        <v>695</v>
+      </c>
+      <c r="D646" s="2" t="s">
+        <v>695</v>
       </c>
       <c r="E646" s="2"/>
     </row>
@@ -13683,10 +13568,10 @@
       </c>
       <c r="B647" s="2"/>
       <c r="C647" s="3" t="s">
-        <v>686</v>
-      </c>
-      <c r="D647" s="11" t="s">
-        <v>829</v>
+        <v>696</v>
+      </c>
+      <c r="D647" s="2" t="s">
+        <v>696</v>
       </c>
       <c r="E647" s="2"/>
     </row>
@@ -13696,10 +13581,10 @@
       </c>
       <c r="B648" s="2"/>
       <c r="C648" s="3" t="s">
-        <v>687</v>
-      </c>
-      <c r="D648" s="11" t="s">
-        <v>830</v>
+        <v>697</v>
+      </c>
+      <c r="D648" s="2" t="s">
+        <v>697</v>
       </c>
       <c r="E648" s="2"/>
     </row>
@@ -13709,60 +13594,62 @@
       </c>
       <c r="B649" s="2"/>
       <c r="C649" s="3" t="s">
-        <v>688</v>
-      </c>
-      <c r="D649" s="11"/>
+        <v>698</v>
+      </c>
+      <c r="D649" s="2" t="s">
+        <v>698</v>
+      </c>
       <c r="E649" s="2"/>
     </row>
     <row r="650" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A650" s="5" t="s">
-        <v>683</v>
+      <c r="A650" s="2" t="s">
+        <v>734</v>
       </c>
       <c r="B650" s="2"/>
       <c r="C650" s="3" t="s">
-        <v>695</v>
+        <v>708</v>
       </c>
       <c r="D650" s="2" t="s">
-        <v>695</v>
+        <v>708</v>
       </c>
       <c r="E650" s="2"/>
     </row>
     <row r="651" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A651" s="5" t="s">
-        <v>683</v>
+      <c r="A651" s="2" t="s">
+        <v>734</v>
       </c>
       <c r="B651" s="2"/>
       <c r="C651" s="3" t="s">
-        <v>696</v>
+        <v>709</v>
       </c>
       <c r="D651" s="2" t="s">
-        <v>696</v>
+        <v>709</v>
       </c>
       <c r="E651" s="2"/>
     </row>
     <row r="652" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A652" s="5" t="s">
-        <v>683</v>
+      <c r="A652" s="2" t="s">
+        <v>734</v>
       </c>
       <c r="B652" s="2"/>
       <c r="C652" s="3" t="s">
-        <v>697</v>
+        <v>710</v>
       </c>
       <c r="D652" s="2" t="s">
-        <v>697</v>
+        <v>710</v>
       </c>
       <c r="E652" s="2"/>
     </row>
     <row r="653" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A653" s="5" t="s">
-        <v>683</v>
+      <c r="A653" s="2" t="s">
+        <v>734</v>
       </c>
       <c r="B653" s="2"/>
       <c r="C653" s="3" t="s">
-        <v>698</v>
+        <v>711</v>
       </c>
       <c r="D653" s="2" t="s">
-        <v>698</v>
+        <v>711</v>
       </c>
       <c r="E653" s="2"/>
     </row>
@@ -13772,10 +13659,10 @@
       </c>
       <c r="B654" s="2"/>
       <c r="C654" s="3" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="D654" s="2" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="E654" s="2"/>
     </row>
@@ -13785,10 +13672,10 @@
       </c>
       <c r="B655" s="2"/>
       <c r="C655" s="3" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="D655" s="2" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="E655" s="2"/>
     </row>
@@ -13798,10 +13685,10 @@
       </c>
       <c r="B656" s="2"/>
       <c r="C656" s="3" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="D656" s="2" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="E656" s="2"/>
     </row>
@@ -13811,10 +13698,10 @@
       </c>
       <c r="B657" s="2"/>
       <c r="C657" s="3" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="D657" s="2" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="E657" s="2"/>
     </row>
@@ -13824,10 +13711,10 @@
       </c>
       <c r="B658" s="2"/>
       <c r="C658" s="3" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="D658" s="2" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="E658" s="2"/>
     </row>
@@ -13837,10 +13724,10 @@
       </c>
       <c r="B659" s="2"/>
       <c r="C659" s="3" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="D659" s="2" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="E659" s="2"/>
     </row>
@@ -13850,10 +13737,10 @@
       </c>
       <c r="B660" s="2"/>
       <c r="C660" s="3" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="D660" s="2" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="E660" s="2"/>
     </row>
@@ -13863,10 +13750,10 @@
       </c>
       <c r="B661" s="2"/>
       <c r="C661" s="3" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D661" s="2" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="E661" s="2"/>
     </row>
@@ -13876,10 +13763,10 @@
       </c>
       <c r="B662" s="2"/>
       <c r="C662" s="3" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D662" s="2" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="E662" s="2"/>
     </row>
@@ -13889,10 +13776,10 @@
       </c>
       <c r="B663" s="2"/>
       <c r="C663" s="3" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="D663" s="2" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="E663" s="2"/>
     </row>
@@ -13902,10 +13789,10 @@
       </c>
       <c r="B664" s="2"/>
       <c r="C664" s="3" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="D664" s="2" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="E664" s="2"/>
     </row>
@@ -13915,10 +13802,10 @@
       </c>
       <c r="B665" s="2"/>
       <c r="C665" s="3" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="D665" s="2" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="E665" s="2"/>
     </row>
@@ -13928,10 +13815,10 @@
       </c>
       <c r="B666" s="2"/>
       <c r="C666" s="3" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="D666" s="2" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="E666" s="2"/>
     </row>
@@ -13941,10 +13828,10 @@
       </c>
       <c r="B667" s="2"/>
       <c r="C667" s="3" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="D667" s="2" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="E667" s="2"/>
     </row>
@@ -13954,10 +13841,10 @@
       </c>
       <c r="B668" s="2"/>
       <c r="C668" s="3" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="D668" s="2" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="E668" s="2"/>
     </row>
@@ -13967,10 +13854,10 @@
       </c>
       <c r="B669" s="2"/>
       <c r="C669" s="3" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="D669" s="2" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="E669" s="2"/>
     </row>
@@ -13980,10 +13867,10 @@
       </c>
       <c r="B670" s="2"/>
       <c r="C670" s="3" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="D670" s="2" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="E670" s="2"/>
     </row>
@@ -13993,10 +13880,10 @@
       </c>
       <c r="B671" s="2"/>
       <c r="C671" s="3" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="D671" s="2" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="E671" s="2"/>
     </row>
@@ -14006,10 +13893,10 @@
       </c>
       <c r="B672" s="2"/>
       <c r="C672" s="3" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="D672" s="2" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="E672" s="2"/>
     </row>
@@ -14019,10 +13906,10 @@
       </c>
       <c r="B673" s="2"/>
       <c r="C673" s="3" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="D673" s="2" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="E673" s="2"/>
     </row>
@@ -14032,10 +13919,10 @@
       </c>
       <c r="B674" s="2"/>
       <c r="C674" s="3" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="D674" s="2" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="E674" s="2"/>
     </row>
@@ -14045,10 +13932,10 @@
       </c>
       <c r="B675" s="2"/>
       <c r="C675" s="3" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="D675" s="2" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="E675" s="2"/>
     </row>
@@ -14057,762 +13944,680 @@
         <v>734</v>
       </c>
       <c r="B676" s="2"/>
-      <c r="C676" s="3" t="s">
-        <v>730</v>
+      <c r="C676" s="5" t="s">
+        <v>809</v>
       </c>
       <c r="D676" s="2" t="s">
-        <v>730</v>
+        <v>809</v>
       </c>
       <c r="E676" s="2"/>
     </row>
     <row r="677" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A677" s="2" t="s">
-        <v>734</v>
+        <v>751</v>
       </c>
       <c r="B677" s="2"/>
       <c r="C677" s="3" t="s">
-        <v>731</v>
+        <v>750</v>
       </c>
       <c r="D677" s="2" t="s">
-        <v>731</v>
+        <v>750</v>
       </c>
       <c r="E677" s="2"/>
     </row>
     <row r="678" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A678" s="2" t="s">
-        <v>734</v>
+        <v>751</v>
       </c>
       <c r="B678" s="2"/>
       <c r="C678" s="3" t="s">
-        <v>732</v>
-      </c>
-      <c r="D678" s="2" t="s">
-        <v>732</v>
+        <v>747</v>
+      </c>
+      <c r="D678" s="11" t="s">
+        <v>905</v>
       </c>
       <c r="E678" s="2"/>
     </row>
     <row r="679" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A679" s="2" t="s">
-        <v>734</v>
+        <v>751</v>
       </c>
       <c r="B679" s="2"/>
       <c r="C679" s="3" t="s">
-        <v>733</v>
+        <v>748</v>
       </c>
       <c r="D679" s="2" t="s">
-        <v>733</v>
+        <v>748</v>
       </c>
       <c r="E679" s="2"/>
     </row>
     <row r="680" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A680" s="2" t="s">
-        <v>734</v>
+        <v>751</v>
       </c>
       <c r="B680" s="2"/>
-      <c r="C680" s="5" t="s">
-        <v>809</v>
+      <c r="C680" s="3" t="s">
+        <v>749</v>
       </c>
       <c r="D680" s="2" t="s">
-        <v>809</v>
+        <v>749</v>
       </c>
       <c r="E680" s="2"/>
     </row>
     <row r="681" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A681" s="2" t="s">
-        <v>736</v>
+      <c r="A681" s="5" t="s">
+        <v>752</v>
       </c>
       <c r="B681" s="2"/>
-      <c r="C681" s="3" t="s">
-        <v>739</v>
-      </c>
-      <c r="D681" s="11" t="s">
-        <v>905</v>
-      </c>
-      <c r="E681" s="2"/>
+      <c r="C681" s="8" t="s">
+        <v>754</v>
+      </c>
+      <c r="D681" s="20" t="s">
+        <v>754</v>
+      </c>
+      <c r="E681" s="20"/>
     </row>
     <row r="682" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A682" s="2" t="s">
-        <v>736</v>
+      <c r="A682" s="22" t="s">
+        <v>752</v>
       </c>
       <c r="B682" s="2"/>
-      <c r="C682" s="3" t="s">
-        <v>740</v>
-      </c>
-      <c r="D682" s="11" t="s">
-        <v>906</v>
-      </c>
-      <c r="E682" s="2"/>
+      <c r="C682" s="31" t="s">
+        <v>755</v>
+      </c>
+      <c r="D682" s="24" t="s">
+        <v>755</v>
+      </c>
+      <c r="E682" s="24"/>
     </row>
     <row r="683" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A683" s="2" t="s">
-        <v>736</v>
+      <c r="A683" s="22" t="s">
+        <v>752</v>
       </c>
       <c r="B683" s="2"/>
-      <c r="C683" s="3" t="s">
-        <v>738</v>
-      </c>
-      <c r="D683" s="11" t="s">
-        <v>907</v>
-      </c>
-      <c r="E683" s="2"/>
+      <c r="C683" s="31" t="s">
+        <v>756</v>
+      </c>
+      <c r="D683" s="24" t="s">
+        <v>756</v>
+      </c>
+      <c r="E683" s="24"/>
     </row>
     <row r="684" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A684" s="2" t="s">
-        <v>741</v>
+      <c r="A684" s="22" t="s">
+        <v>752</v>
       </c>
       <c r="B684" s="2"/>
-      <c r="C684" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="D684" s="11" t="s">
-        <v>908</v>
-      </c>
-      <c r="E684" s="2"/>
+      <c r="C684" s="31" t="s">
+        <v>757</v>
+      </c>
+      <c r="D684" s="24" t="s">
+        <v>757</v>
+      </c>
+      <c r="E684" s="24"/>
     </row>
     <row r="685" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A685" s="2" t="s">
-        <v>741</v>
+      <c r="A685" s="22" t="s">
+        <v>752</v>
       </c>
       <c r="B685" s="2"/>
-      <c r="C685" s="3" t="s">
-        <v>744</v>
-      </c>
-      <c r="D685" s="11" t="s">
-        <v>909</v>
-      </c>
-      <c r="E685" s="2"/>
+      <c r="C685" s="31" t="s">
+        <v>758</v>
+      </c>
+      <c r="D685" s="24" t="s">
+        <v>758</v>
+      </c>
+      <c r="E685" s="24"/>
     </row>
     <row r="686" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A686" s="2" t="s">
-        <v>741</v>
+      <c r="A686" s="22" t="s">
+        <v>752</v>
       </c>
       <c r="B686" s="2"/>
-      <c r="C686" s="3" t="s">
-        <v>743</v>
-      </c>
-      <c r="D686" s="11" t="s">
-        <v>910</v>
-      </c>
-      <c r="E686" s="2"/>
+      <c r="C686" s="31" t="s">
+        <v>759</v>
+      </c>
+      <c r="D686" s="24" t="s">
+        <v>759</v>
+      </c>
+      <c r="E686" s="24"/>
     </row>
     <row r="687" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A687" s="2" t="s">
-        <v>751</v>
+      <c r="A687" s="22" t="s">
+        <v>752</v>
       </c>
       <c r="B687" s="2"/>
-      <c r="C687" s="3" t="s">
-        <v>750</v>
-      </c>
-      <c r="D687" s="2" t="s">
-        <v>750</v>
-      </c>
-      <c r="E687" s="2"/>
+      <c r="C687" s="31" t="s">
+        <v>760</v>
+      </c>
+      <c r="D687" s="24" t="s">
+        <v>760</v>
+      </c>
+      <c r="E687" s="24"/>
     </row>
     <row r="688" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A688" s="2" t="s">
-        <v>751</v>
+        <v>761</v>
       </c>
       <c r="B688" s="2"/>
       <c r="C688" s="3" t="s">
-        <v>747</v>
-      </c>
-      <c r="D688" s="11" t="s">
-        <v>911</v>
-      </c>
+        <v>765</v>
+      </c>
+      <c r="D688" s="11"/>
       <c r="E688" s="2"/>
     </row>
     <row r="689" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A689" s="2" t="s">
-        <v>751</v>
+        <v>761</v>
       </c>
       <c r="B689" s="2"/>
       <c r="C689" s="3" t="s">
-        <v>748</v>
-      </c>
-      <c r="D689" s="2" t="s">
-        <v>748</v>
-      </c>
+        <v>764</v>
+      </c>
+      <c r="D689" s="11"/>
       <c r="E689" s="2"/>
     </row>
     <row r="690" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A690" s="2" t="s">
-        <v>751</v>
+        <v>761</v>
       </c>
       <c r="B690" s="2"/>
       <c r="C690" s="3" t="s">
-        <v>749</v>
-      </c>
-      <c r="D690" s="2" t="s">
-        <v>749</v>
-      </c>
+        <v>763</v>
+      </c>
+      <c r="D690" s="11"/>
       <c r="E690" s="2"/>
     </row>
     <row r="691" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A691" s="5" t="s">
-        <v>752</v>
+      <c r="A691" s="2" t="s">
+        <v>766</v>
       </c>
       <c r="B691" s="2"/>
-      <c r="C691" s="8" t="s">
-        <v>754</v>
-      </c>
-      <c r="D691" s="20" t="s">
-        <v>754</v>
-      </c>
-      <c r="E691" s="20"/>
+      <c r="C691" s="3" t="s">
+        <v>768</v>
+      </c>
+      <c r="D691" s="11" t="s">
+        <v>821</v>
+      </c>
+      <c r="E691" s="2"/>
     </row>
     <row r="692" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A692" s="24" t="s">
-        <v>752</v>
+      <c r="A692" s="2" t="s">
+        <v>766</v>
       </c>
       <c r="B692" s="2"/>
-      <c r="C692" s="36" t="s">
-        <v>755</v>
-      </c>
-      <c r="D692" s="27" t="s">
-        <v>755</v>
-      </c>
-      <c r="E692" s="27"/>
+      <c r="C692" s="3" t="s">
+        <v>774</v>
+      </c>
+      <c r="D692" s="11"/>
+      <c r="E692" s="2"/>
     </row>
     <row r="693" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A693" s="24" t="s">
-        <v>752</v>
+      <c r="A693" s="2" t="s">
+        <v>766</v>
       </c>
       <c r="B693" s="2"/>
-      <c r="C693" s="36" t="s">
-        <v>756</v>
-      </c>
-      <c r="D693" s="27" t="s">
-        <v>756</v>
-      </c>
-      <c r="E693" s="27"/>
+      <c r="C693" s="3" t="s">
+        <v>771</v>
+      </c>
+      <c r="D693" s="11" t="s">
+        <v>822</v>
+      </c>
+      <c r="E693" s="2"/>
     </row>
     <row r="694" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A694" s="24" t="s">
-        <v>752</v>
+      <c r="A694" s="2" t="s">
+        <v>766</v>
       </c>
       <c r="B694" s="2"/>
-      <c r="C694" s="36" t="s">
-        <v>757</v>
-      </c>
-      <c r="D694" s="27" t="s">
-        <v>757</v>
-      </c>
-      <c r="E694" s="27"/>
+      <c r="C694" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="D694" s="11" t="s">
+        <v>823</v>
+      </c>
+      <c r="E694" s="2"/>
     </row>
     <row r="695" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A695" s="24" t="s">
-        <v>752</v>
+      <c r="A695" s="2" t="s">
+        <v>766</v>
       </c>
       <c r="B695" s="2"/>
-      <c r="C695" s="36" t="s">
-        <v>758</v>
-      </c>
-      <c r="D695" s="27" t="s">
-        <v>758</v>
-      </c>
-      <c r="E695" s="27"/>
+      <c r="C695" s="3" t="s">
+        <v>773</v>
+      </c>
+      <c r="D695" s="11"/>
+      <c r="E695" s="2"/>
     </row>
     <row r="696" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A696" s="24" t="s">
-        <v>752</v>
+      <c r="A696" s="2" t="s">
+        <v>766</v>
       </c>
       <c r="B696" s="2"/>
-      <c r="C696" s="36" t="s">
-        <v>759</v>
-      </c>
-      <c r="D696" s="27" t="s">
-        <v>759</v>
-      </c>
-      <c r="E696" s="27"/>
+      <c r="C696" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="D696" s="11"/>
+      <c r="E696" s="2"/>
     </row>
     <row r="697" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A697" s="24" t="s">
-        <v>752</v>
+      <c r="A697" s="2" t="s">
+        <v>766</v>
       </c>
       <c r="B697" s="2"/>
-      <c r="C697" s="36" t="s">
-        <v>760</v>
-      </c>
-      <c r="D697" s="27" t="s">
-        <v>760</v>
-      </c>
-      <c r="E697" s="27"/>
+      <c r="C697" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="D697" s="11" t="s">
+        <v>824</v>
+      </c>
+      <c r="E697" s="2"/>
     </row>
     <row r="698" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A698" s="2" t="s">
-        <v>761</v>
+        <v>775</v>
       </c>
       <c r="B698" s="2"/>
       <c r="C698" s="3" t="s">
-        <v>765</v>
-      </c>
-      <c r="D698" s="11"/>
+        <v>777</v>
+      </c>
+      <c r="D698" s="11" t="s">
+        <v>896</v>
+      </c>
       <c r="E698" s="2"/>
     </row>
     <row r="699" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A699" s="2" t="s">
-        <v>761</v>
+        <v>775</v>
       </c>
       <c r="B699" s="2"/>
       <c r="C699" s="3" t="s">
-        <v>764</v>
-      </c>
-      <c r="D699" s="11"/>
+        <v>782</v>
+      </c>
+      <c r="D699" s="11" t="s">
+        <v>897</v>
+      </c>
       <c r="E699" s="2"/>
     </row>
     <row r="700" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A700" s="2" t="s">
-        <v>761</v>
+        <v>775</v>
       </c>
       <c r="B700" s="2"/>
       <c r="C700" s="3" t="s">
-        <v>763</v>
-      </c>
-      <c r="D700" s="11"/>
+        <v>918</v>
+      </c>
+      <c r="D700" s="11" t="s">
+        <v>898</v>
+      </c>
       <c r="E700" s="2"/>
     </row>
     <row r="701" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A701" s="2" t="s">
-        <v>766</v>
+        <v>775</v>
       </c>
       <c r="B701" s="2"/>
       <c r="C701" s="3" t="s">
-        <v>768</v>
+        <v>784</v>
       </c>
       <c r="D701" s="11" t="s">
-        <v>821</v>
+        <v>899</v>
       </c>
       <c r="E701" s="2"/>
     </row>
     <row r="702" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A702" s="2" t="s">
-        <v>766</v>
+        <v>775</v>
       </c>
       <c r="B702" s="2"/>
       <c r="C702" s="3" t="s">
-        <v>774</v>
-      </c>
-      <c r="D702" s="11"/>
+        <v>778</v>
+      </c>
+      <c r="D702" s="11" t="s">
+        <v>900</v>
+      </c>
       <c r="E702" s="2"/>
     </row>
     <row r="703" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A703" s="2" t="s">
-        <v>766</v>
+        <v>775</v>
       </c>
       <c r="B703" s="2"/>
       <c r="C703" s="3" t="s">
-        <v>771</v>
+        <v>783</v>
       </c>
       <c r="D703" s="11" t="s">
-        <v>822</v>
+        <v>901</v>
       </c>
       <c r="E703" s="2"/>
     </row>
     <row r="704" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A704" s="2" t="s">
-        <v>766</v>
+        <v>775</v>
       </c>
       <c r="B704" s="2"/>
       <c r="C704" s="3" t="s">
-        <v>770</v>
+        <v>781</v>
       </c>
       <c r="D704" s="11" t="s">
-        <v>823</v>
+        <v>902</v>
       </c>
       <c r="E704" s="2"/>
     </row>
     <row r="705" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A705" s="2" t="s">
-        <v>766</v>
+        <v>775</v>
       </c>
       <c r="B705" s="2"/>
       <c r="C705" s="3" t="s">
-        <v>773</v>
-      </c>
-      <c r="D705" s="11"/>
+        <v>780</v>
+      </c>
+      <c r="D705" s="11" t="s">
+        <v>903</v>
+      </c>
       <c r="E705" s="2"/>
     </row>
     <row r="706" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A706" s="2" t="s">
-        <v>766</v>
+        <v>775</v>
       </c>
       <c r="B706" s="2"/>
       <c r="C706" s="3" t="s">
-        <v>772</v>
-      </c>
-      <c r="D706" s="11"/>
+        <v>785</v>
+      </c>
+      <c r="D706" s="11" t="s">
+        <v>904</v>
+      </c>
       <c r="E706" s="2"/>
     </row>
     <row r="707" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A707" s="2" t="s">
-        <v>766</v>
+        <v>786</v>
       </c>
       <c r="B707" s="2"/>
       <c r="C707" s="3" t="s">
-        <v>769</v>
+        <v>788</v>
       </c>
       <c r="D707" s="11" t="s">
-        <v>824</v>
+        <v>788</v>
       </c>
       <c r="E707" s="2"/>
     </row>
     <row r="708" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A708" s="2" t="s">
-        <v>775</v>
+        <v>786</v>
       </c>
       <c r="B708" s="2"/>
       <c r="C708" s="3" t="s">
-        <v>777</v>
+        <v>793</v>
       </c>
       <c r="D708" s="11" t="s">
-        <v>896</v>
+        <v>890</v>
       </c>
       <c r="E708" s="2"/>
     </row>
     <row r="709" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A709" s="2" t="s">
-        <v>775</v>
+        <v>786</v>
       </c>
       <c r="B709" s="2"/>
       <c r="C709" s="3" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="D709" s="11" t="s">
-        <v>897</v>
+        <v>790</v>
       </c>
       <c r="E709" s="2"/>
     </row>
     <row r="710" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A710" s="2" t="s">
-        <v>775</v>
+        <v>786</v>
       </c>
       <c r="B710" s="2"/>
       <c r="C710" s="3" t="s">
-        <v>926</v>
+        <v>792</v>
       </c>
       <c r="D710" s="11" t="s">
-        <v>898</v>
+        <v>891</v>
       </c>
       <c r="E710" s="2"/>
     </row>
     <row r="711" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A711" s="2" t="s">
-        <v>775</v>
+        <v>786</v>
       </c>
       <c r="B711" s="2"/>
       <c r="C711" s="3" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="D711" s="11" t="s">
-        <v>899</v>
+        <v>892</v>
       </c>
       <c r="E711" s="2"/>
     </row>
     <row r="712" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A712" s="2" t="s">
-        <v>775</v>
+        <v>786</v>
       </c>
       <c r="B712" s="2"/>
       <c r="C712" s="3" t="s">
-        <v>778</v>
+        <v>789</v>
       </c>
       <c r="D712" s="11" t="s">
-        <v>900</v>
+        <v>789</v>
       </c>
       <c r="E712" s="2"/>
     </row>
     <row r="713" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A713" s="2" t="s">
-        <v>775</v>
+      <c r="A713" s="5" t="s">
+        <v>794</v>
       </c>
       <c r="B713" s="2"/>
       <c r="C713" s="3" t="s">
-        <v>783</v>
+        <v>796</v>
       </c>
       <c r="D713" s="11" t="s">
-        <v>901</v>
+        <v>831</v>
       </c>
       <c r="E713" s="2"/>
     </row>
     <row r="714" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A714" s="2" t="s">
-        <v>775</v>
+      <c r="A714" s="5" t="s">
+        <v>794</v>
       </c>
       <c r="B714" s="2"/>
       <c r="C714" s="3" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="D714" s="11" t="s">
-        <v>902</v>
+        <v>832</v>
       </c>
       <c r="E714" s="2"/>
     </row>
     <row r="715" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A715" s="2" t="s">
-        <v>775</v>
+      <c r="A715" s="5" t="s">
+        <v>794</v>
       </c>
       <c r="B715" s="2"/>
       <c r="C715" s="3" t="s">
-        <v>780</v>
+        <v>793</v>
       </c>
       <c r="D715" s="11" t="s">
-        <v>903</v>
+        <v>833</v>
       </c>
       <c r="E715" s="2"/>
     </row>
     <row r="716" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A716" s="2" t="s">
-        <v>775</v>
+      <c r="A716" s="5" t="s">
+        <v>794</v>
       </c>
       <c r="B716" s="2"/>
       <c r="C716" s="3" t="s">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="D716" s="11" t="s">
-        <v>904</v>
+        <v>834</v>
       </c>
       <c r="E716" s="2"/>
     </row>
     <row r="717" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A717" s="2" t="s">
-        <v>786</v>
+      <c r="A717" s="5" t="s">
+        <v>794</v>
       </c>
       <c r="B717" s="2"/>
       <c r="C717" s="3" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D717" s="11" t="s">
-        <v>788</v>
+        <v>835</v>
       </c>
       <c r="E717" s="2"/>
     </row>
     <row r="718" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A718" s="2" t="s">
-        <v>786</v>
+      <c r="A718" s="5" t="s">
+        <v>797</v>
       </c>
       <c r="B718" s="2"/>
       <c r="C718" s="3" t="s">
-        <v>793</v>
+        <v>799</v>
       </c>
       <c r="D718" s="11" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="E718" s="2"/>
     </row>
     <row r="719" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A719" s="2" t="s">
-        <v>786</v>
+      <c r="A719" s="5" t="s">
+        <v>797</v>
       </c>
       <c r="B719" s="2"/>
       <c r="C719" s="3" t="s">
-        <v>790</v>
+        <v>801</v>
       </c>
       <c r="D719" s="11" t="s">
-        <v>790</v>
+        <v>894</v>
       </c>
       <c r="E719" s="2"/>
     </row>
     <row r="720" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A720" s="2" t="s">
-        <v>786</v>
+      <c r="A720" s="5" t="s">
+        <v>797</v>
       </c>
       <c r="B720" s="2"/>
       <c r="C720" s="3" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="D720" s="11" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="E720" s="2"/>
     </row>
-    <row r="721" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A721" s="2" t="s">
-        <v>786</v>
+    <row r="721" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A721" s="5" t="s">
+        <v>797</v>
       </c>
       <c r="B721" s="2"/>
-      <c r="C721" s="3" t="s">
-        <v>791</v>
+      <c r="C721" s="5" t="s">
+        <v>802</v>
       </c>
       <c r="D721" s="11" t="s">
-        <v>892</v>
+        <v>815</v>
       </c>
       <c r="E721" s="2"/>
     </row>
-    <row r="722" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="722" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A722" s="2" t="s">
-        <v>786</v>
+        <v>919</v>
       </c>
       <c r="B722" s="2"/>
       <c r="C722" s="3" t="s">
-        <v>789</v>
-      </c>
-      <c r="D722" s="11" t="s">
-        <v>789</v>
+        <v>920</v>
+      </c>
+      <c r="D722" s="3" t="s">
+        <v>920</v>
       </c>
       <c r="E722" s="2"/>
     </row>
-    <row r="723" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A723" s="5" t="s">
-        <v>794</v>
+    <row r="723" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A723" s="2" t="s">
+        <v>919</v>
       </c>
       <c r="B723" s="2"/>
       <c r="C723" s="3" t="s">
-        <v>796</v>
-      </c>
-      <c r="D723" s="11" t="s">
-        <v>831</v>
-      </c>
-      <c r="E723" s="2"/>
-    </row>
-    <row r="724" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A724" s="5" t="s">
-        <v>794</v>
+        <v>886</v>
+      </c>
+      <c r="D723" s="10" t="s">
+        <v>886</v>
+      </c>
+      <c r="E723" s="10"/>
+    </row>
+    <row r="724" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A724" s="2" t="s">
+        <v>919</v>
       </c>
       <c r="B724" s="2"/>
       <c r="C724" s="3" t="s">
-        <v>788</v>
-      </c>
-      <c r="D724" s="11" t="s">
-        <v>832</v>
-      </c>
-      <c r="E724" s="2"/>
-    </row>
-    <row r="725" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A725" s="5" t="s">
-        <v>794</v>
+        <v>816</v>
+      </c>
+      <c r="D724" s="10" t="s">
+        <v>816</v>
+      </c>
+      <c r="E724" s="10"/>
+    </row>
+    <row r="725" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A725" s="2" t="s">
+        <v>919</v>
       </c>
       <c r="B725" s="2"/>
       <c r="C725" s="3" t="s">
-        <v>793</v>
-      </c>
-      <c r="D725" s="11" t="s">
-        <v>833</v>
-      </c>
-      <c r="E725" s="2"/>
-    </row>
-    <row r="726" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A726" s="5" t="s">
-        <v>794</v>
+        <v>907</v>
+      </c>
+      <c r="D725" s="17" t="s">
+        <v>907</v>
+      </c>
+      <c r="F725" s="14" t="e">
+        <f>_xlfn.XLOOKUP(#REF!,'[1]Hem Catalogue'!$C$545:$C$643,'[1]Hem Catalogue'!$D$545:$D$643,"")</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="726" spans="1:6" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+      <c r="A726" s="2" t="s">
+        <v>919</v>
       </c>
       <c r="B726" s="2"/>
       <c r="C726" s="3" t="s">
-        <v>790</v>
-      </c>
-      <c r="D726" s="11" t="s">
-        <v>834</v>
-      </c>
-      <c r="E726" s="2"/>
-    </row>
-    <row r="727" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A727" s="5" t="s">
-        <v>794</v>
+        <v>889</v>
+      </c>
+      <c r="D726" s="23" t="s">
+        <v>889</v>
+      </c>
+      <c r="E726" s="24"/>
+    </row>
+    <row r="727" spans="1:6" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+      <c r="A727" s="2" t="s">
+        <v>919</v>
       </c>
       <c r="B727" s="2"/>
       <c r="C727" s="3" t="s">
-        <v>789</v>
-      </c>
-      <c r="D727" s="11" t="s">
-        <v>835</v>
-      </c>
-      <c r="E727" s="2"/>
-    </row>
-    <row r="728" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A728" s="5" t="s">
-        <v>797</v>
-      </c>
+        <v>887</v>
+      </c>
+      <c r="D727" s="23" t="s">
+        <v>887</v>
+      </c>
+      <c r="E727" s="24"/>
+    </row>
+    <row r="728" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B728" s="2"/>
-      <c r="C728" s="3" t="s">
-        <v>799</v>
-      </c>
-      <c r="D728" s="11" t="s">
-        <v>893</v>
-      </c>
-      <c r="E728" s="2"/>
-    </row>
-    <row r="729" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A729" s="5" t="s">
-        <v>797</v>
-      </c>
-      <c r="B729" s="2"/>
-      <c r="C729" s="3" t="s">
-        <v>801</v>
-      </c>
-      <c r="D729" s="11" t="s">
-        <v>894</v>
-      </c>
-      <c r="E729" s="2"/>
-    </row>
-    <row r="730" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A730" s="5" t="s">
-        <v>797</v>
-      </c>
-      <c r="B730" s="2"/>
-      <c r="C730" s="3" t="s">
-        <v>800</v>
-      </c>
-      <c r="D730" s="11" t="s">
-        <v>895</v>
-      </c>
-      <c r="E730" s="2"/>
-    </row>
-    <row r="731" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A731" s="5" t="s">
-        <v>797</v>
-      </c>
-      <c r="B731" s="2"/>
-      <c r="C731" s="5" t="s">
-        <v>802</v>
-      </c>
-      <c r="D731" s="11" t="s">
-        <v>815</v>
-      </c>
-      <c r="E731" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G731" xr:uid="{DBBB3535-4F14-43E5-BD0D-3890A33AED12}"/>
+  <autoFilter ref="A1:G721" xr:uid="{DBBB3535-4F14-43E5-BD0D-3890A33AED12}"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E116452D-696E-4938-8369-72AAE054873C}">
-  <dimension ref="A284:E286"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="63.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="57.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="58.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="48" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="284" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A284" s="14"/>
-      <c r="B284" s="14"/>
-      <c r="C284" s="14"/>
-      <c r="D284" s="14"/>
-      <c r="E284" s="19"/>
-    </row>
-    <row r="285" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A285" s="14"/>
-      <c r="B285" s="14"/>
-      <c r="C285" s="14"/>
-      <c r="D285" s="14"/>
-      <c r="E285" s="19"/>
-    </row>
-    <row r="286" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A286" s="14"/>
-      <c r="B286" s="14"/>
-      <c r="C286" s="14"/>
-      <c r="D286" s="14"/>
-      <c r="E286" s="19"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:CX733"/>
   <sheetFormatPr defaultColWidth="30.08984375" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.35"/>

--- a/Hem catalogue.xlsx
+++ b/Hem catalogue.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Jitesh\Desktop\hem-catalogue-app_final-1\hem-catalogue-app-1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa00\product catalogue\product catalogue app v2\.claude\worktrees\youthful-dhawan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{637A14A9-03BF-4B14-BE5D-93A8CBC102AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B2585C-5A77-4F52-B18B-83449EF44DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hem catalogue'!$A$1:$G$721</definedName>
   </definedNames>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5365" uniqueCount="922">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5365" uniqueCount="927">
   <si>
     <t>Category</t>
   </si>
@@ -2812,6 +2812,21 @@
   </si>
   <si>
     <t>7 Chakras Stone</t>
+  </si>
+  <si>
+    <t>SMC - Smudge Tin Candle Palo Santo</t>
+  </si>
+  <si>
+    <t>SMC - Smudge Tin Candle Patchouli</t>
+  </si>
+  <si>
+    <t>SMC - Smudge Tin  Candle Rosemary</t>
+  </si>
+  <si>
+    <t>SMC - Smudge Tin Candle Vanilla</t>
+  </si>
+  <si>
+    <t>SMC - Smudge Tin  Candle White Sage</t>
   </si>
 </sst>
 </file>
@@ -14336,7 +14351,7 @@
       </c>
       <c r="B707" s="2"/>
       <c r="C707" s="3" t="s">
-        <v>788</v>
+        <v>922</v>
       </c>
       <c r="D707" s="11" t="s">
         <v>788</v>
@@ -14349,7 +14364,7 @@
       </c>
       <c r="B708" s="2"/>
       <c r="C708" s="3" t="s">
-        <v>793</v>
+        <v>923</v>
       </c>
       <c r="D708" s="11" t="s">
         <v>890</v>
@@ -14362,7 +14377,7 @@
       </c>
       <c r="B709" s="2"/>
       <c r="C709" s="3" t="s">
-        <v>790</v>
+        <v>924</v>
       </c>
       <c r="D709" s="11" t="s">
         <v>790</v>
@@ -14388,7 +14403,7 @@
       </c>
       <c r="B711" s="2"/>
       <c r="C711" s="3" t="s">
-        <v>791</v>
+        <v>925</v>
       </c>
       <c r="D711" s="11" t="s">
         <v>892</v>
@@ -14401,7 +14416,7 @@
       </c>
       <c r="B712" s="2"/>
       <c r="C712" s="3" t="s">
-        <v>789</v>
+        <v>926</v>
       </c>
       <c r="D712" s="11" t="s">
         <v>789</v>

--- a/Hem catalogue.xlsx
+++ b/Hem catalogue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa00\product catalogue\product catalogue app v2\.claude\worktrees\youthful-dhawan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B2585C-5A77-4F52-B18B-83449EF44DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0D179E1-2BDC-462C-8536-3DC9AF2455B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5365" uniqueCount="927">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5365" uniqueCount="933">
   <si>
     <t>Category</t>
   </si>
@@ -2827,6 +2827,24 @@
   </si>
   <si>
     <t>SMC - Smudge Tin  Candle White Sage</t>
+  </si>
+  <si>
+    <t>Black Current Car Freshner</t>
+  </si>
+  <si>
+    <t>Citrus Breeze Car Freshner</t>
+  </si>
+  <si>
+    <t>Dreamy Rose Car Freshner</t>
+  </si>
+  <si>
+    <t>Fresh Bergamote Car Freshner</t>
+  </si>
+  <si>
+    <t>Ocean Drive Car Freshner</t>
+  </si>
+  <si>
+    <t>Peach Blossom Car Freshner</t>
   </si>
 </sst>
 </file>
@@ -14162,7 +14180,7 @@
       </c>
       <c r="B692" s="2"/>
       <c r="C692" s="3" t="s">
-        <v>774</v>
+        <v>927</v>
       </c>
       <c r="D692" s="11"/>
       <c r="E692" s="2"/>
@@ -14173,7 +14191,7 @@
       </c>
       <c r="B693" s="2"/>
       <c r="C693" s="3" t="s">
-        <v>771</v>
+        <v>928</v>
       </c>
       <c r="D693" s="11" t="s">
         <v>822</v>
@@ -14186,7 +14204,7 @@
       </c>
       <c r="B694" s="2"/>
       <c r="C694" s="3" t="s">
-        <v>770</v>
+        <v>929</v>
       </c>
       <c r="D694" s="11" t="s">
         <v>823</v>
@@ -14199,7 +14217,7 @@
       </c>
       <c r="B695" s="2"/>
       <c r="C695" s="3" t="s">
-        <v>773</v>
+        <v>930</v>
       </c>
       <c r="D695" s="11"/>
       <c r="E695" s="2"/>
@@ -14210,7 +14228,7 @@
       </c>
       <c r="B696" s="2"/>
       <c r="C696" s="3" t="s">
-        <v>772</v>
+        <v>931</v>
       </c>
       <c r="D696" s="11"/>
       <c r="E696" s="2"/>
@@ -14221,7 +14239,7 @@
       </c>
       <c r="B697" s="2"/>
       <c r="C697" s="3" t="s">
-        <v>769</v>
+        <v>932</v>
       </c>
       <c r="D697" s="11" t="s">
         <v>824</v>

--- a/Hem catalogue.xlsx
+++ b/Hem catalogue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa00\product catalogue\product catalogue app v2\.claude\worktrees\youthful-dhawan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0D179E1-2BDC-462C-8536-3DC9AF2455B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13ED7A0F-A19F-41A4-9C28-BE1A7A91E4E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hem catalogue'!$A$1:$G$721</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hem catalogue'!$A$1:$G$717</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -4272,7 +4272,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBBB3535-4F14-43E5-BD0D-3890A33AED12}">
-  <dimension ref="A1:G728"/>
+  <dimension ref="A1:G724"/>
   <sheetFormatPr defaultColWidth="48.7265625" defaultRowHeight="18.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="63.6328125" style="14" bestFit="1" customWidth="1"/>
@@ -10745,22 +10745,36 @@
         <v>560</v>
       </c>
     </row>
+    <row r="436" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A436" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B436" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C436" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="D436" s="17" t="s">
+        <v>908</v>
+      </c>
+      <c r="F436" s="14" t="e">
+        <f>_xlfn.XLOOKUP(#REF!,'[1]Hem Catalogue'!$C$545:$C$643,'[1]Hem Catalogue'!$D$545:$D$643,"")</f>
+        <v>#REF!</v>
+      </c>
+    </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A437" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B437" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C437" s="2" t="s">
-        <v>807</v>
-      </c>
-      <c r="D437" s="17" t="s">
-        <v>908</v>
-      </c>
-      <c r="F437" s="14" t="e">
-        <f>_xlfn.XLOOKUP(#REF!,'[1]Hem Catalogue'!$C$545:$C$643,'[1]Hem Catalogue'!$D$545:$D$643,"")</f>
-        <v>#REF!</v>
+        <v>23</v>
+      </c>
+      <c r="C437" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="D437" s="14" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.45">
@@ -10771,10 +10785,10 @@
         <v>23</v>
       </c>
       <c r="C438" s="3" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D438" s="14" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.45">
@@ -10785,10 +10799,10 @@
         <v>23</v>
       </c>
       <c r="C439" s="3" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D439" s="14" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.45">
@@ -10799,10 +10813,10 @@
         <v>23</v>
       </c>
       <c r="C440" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D440" s="14" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.45">
@@ -10813,10 +10827,10 @@
         <v>23</v>
       </c>
       <c r="C441" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D441" s="14" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.45">
@@ -10827,10 +10841,10 @@
         <v>23</v>
       </c>
       <c r="C442" s="3" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D442" s="14" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.45">
@@ -10841,25 +10855,25 @@
         <v>23</v>
       </c>
       <c r="C443" s="3" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D443" s="14" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A444" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B444" s="14" t="s">
-        <v>23</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="B444"/>
       <c r="C444" s="3" t="s">
-        <v>532</v>
-      </c>
-      <c r="D444" s="14" t="s">
-        <v>532</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="D444" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="E444" s="2"/>
+      <c r="F444"/>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A445" s="2" t="s">
@@ -10867,10 +10881,10 @@
       </c>
       <c r="B445"/>
       <c r="C445" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D445" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E445" s="2"/>
       <c r="F445"/>
@@ -10881,10 +10895,10 @@
       </c>
       <c r="B446"/>
       <c r="C446" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D446" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E446" s="2"/>
       <c r="F446"/>
@@ -10895,10 +10909,10 @@
       </c>
       <c r="B447"/>
       <c r="C447" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D447" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E447" s="2"/>
       <c r="F447"/>
@@ -10909,40 +10923,40 @@
       </c>
       <c r="B448"/>
       <c r="C448" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E448" s="2"/>
       <c r="F448"/>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A449" s="2" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="B449"/>
       <c r="C449" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="D449" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="E449" s="2"/>
+        <v>418</v>
+      </c>
+      <c r="D449" s="11" t="s">
+        <v>848</v>
+      </c>
+      <c r="E449"/>
       <c r="F449"/>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A450" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="B450"/>
+      <c r="B450" s="2"/>
       <c r="C450" s="3" t="s">
-        <v>418</v>
+        <v>454</v>
       </c>
       <c r="D450" s="11" t="s">
-        <v>848</v>
-      </c>
-      <c r="E450"/>
+        <v>847</v>
+      </c>
+      <c r="E450" s="2"/>
       <c r="F450"/>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.45">
@@ -10951,10 +10965,10 @@
       </c>
       <c r="B451" s="2"/>
       <c r="C451" s="3" t="s">
-        <v>454</v>
+        <v>419</v>
       </c>
       <c r="D451" s="11" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="E451" s="2"/>
       <c r="F451"/>
@@ -10965,13 +10979,12 @@
       </c>
       <c r="B452" s="2"/>
       <c r="C452" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D452" s="11" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="E452" s="2"/>
-      <c r="F452"/>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A453" s="2" t="s">
@@ -10979,10 +10992,10 @@
       </c>
       <c r="B453" s="2"/>
       <c r="C453" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D453" s="11" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="E453" s="2"/>
     </row>
@@ -10992,10 +11005,10 @@
       </c>
       <c r="B454" s="2"/>
       <c r="C454" s="3" t="s">
-        <v>421</v>
+        <v>455</v>
       </c>
       <c r="D454" s="11" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="E454" s="2"/>
     </row>
@@ -11005,10 +11018,10 @@
       </c>
       <c r="B455" s="2"/>
       <c r="C455" s="3" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="D455" s="11" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="E455" s="2"/>
     </row>
@@ -11018,10 +11031,10 @@
       </c>
       <c r="B456" s="2"/>
       <c r="C456" s="3" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="D456" s="11" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="E456" s="2"/>
     </row>
@@ -11031,10 +11044,10 @@
       </c>
       <c r="B457" s="2"/>
       <c r="C457" s="3" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="D457" s="11" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="E457" s="2"/>
     </row>
@@ -11044,10 +11057,10 @@
       </c>
       <c r="B458" s="2"/>
       <c r="C458" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D458" s="11" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="E458" s="2"/>
     </row>
@@ -11057,10 +11070,10 @@
       </c>
       <c r="B459" s="2"/>
       <c r="C459" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D459" s="11" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="E459" s="2"/>
     </row>
@@ -11070,10 +11083,10 @@
       </c>
       <c r="B460" s="2"/>
       <c r="C460" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D460" s="11" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="E460" s="2"/>
     </row>
@@ -11083,10 +11096,10 @@
       </c>
       <c r="B461" s="2"/>
       <c r="C461" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D461" s="11" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="E461" s="2"/>
     </row>
@@ -11096,10 +11109,10 @@
       </c>
       <c r="B462" s="2"/>
       <c r="C462" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D462" s="11" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="E462" s="2"/>
     </row>
@@ -11109,10 +11122,10 @@
       </c>
       <c r="B463" s="2"/>
       <c r="C463" s="3" t="s">
-        <v>429</v>
+        <v>452</v>
       </c>
       <c r="D463" s="11" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="E463" s="2"/>
     </row>
@@ -11122,10 +11135,10 @@
       </c>
       <c r="B464" s="2"/>
       <c r="C464" s="3" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D464" s="11" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="E464" s="2"/>
     </row>
@@ -11135,10 +11148,10 @@
       </c>
       <c r="B465" s="2"/>
       <c r="C465" s="3" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="D465" s="11" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="E465" s="2"/>
     </row>
@@ -11148,10 +11161,10 @@
       </c>
       <c r="B466" s="2"/>
       <c r="C466" s="3" t="s">
-        <v>458</v>
+        <v>444</v>
       </c>
       <c r="D466" s="11" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="E466" s="2"/>
     </row>
@@ -11161,10 +11174,10 @@
       </c>
       <c r="B467" s="2"/>
       <c r="C467" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D467" s="11" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="E467" s="2"/>
     </row>
@@ -11174,10 +11187,10 @@
       </c>
       <c r="B468" s="2"/>
       <c r="C468" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D468" s="11" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="E468" s="2"/>
     </row>
@@ -11187,49 +11200,49 @@
       </c>
       <c r="B469" s="2"/>
       <c r="C469" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D469" s="11" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="E469" s="2"/>
     </row>
-    <row r="470" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="470" spans="1:5" s="25" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A470" s="2" t="s">
         <v>416</v>
       </c>
       <c r="B470" s="2"/>
       <c r="C470" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D470" s="11" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="E470" s="2"/>
     </row>
-    <row r="471" spans="1:5" s="25" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:5" s="28" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A471" s="2" t="s">
         <v>416</v>
       </c>
       <c r="B471" s="2"/>
       <c r="C471" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D471" s="11" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="E471" s="2"/>
     </row>
-    <row r="472" spans="1:5" s="28" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A472" s="2" t="s">
         <v>416</v>
       </c>
       <c r="B472" s="2"/>
       <c r="C472" s="3" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="D472" s="11" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="E472" s="2"/>
     </row>
@@ -11239,10 +11252,10 @@
       </c>
       <c r="B473" s="2"/>
       <c r="C473" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D473" s="11" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="E473" s="2"/>
     </row>
@@ -11252,10 +11265,10 @@
       </c>
       <c r="B474" s="2"/>
       <c r="C474" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D474" s="11" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="E474" s="2"/>
     </row>
@@ -11265,10 +11278,10 @@
       </c>
       <c r="B475" s="2"/>
       <c r="C475" s="3" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D475" s="11" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="E475" s="2"/>
     </row>
@@ -11278,10 +11291,10 @@
       </c>
       <c r="B476" s="2"/>
       <c r="C476" s="3" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="D476" s="11" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E476" s="2"/>
     </row>
@@ -11291,10 +11304,10 @@
       </c>
       <c r="B477" s="2"/>
       <c r="C477" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D477" s="11" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="E477" s="2"/>
     </row>
@@ -11304,10 +11317,10 @@
       </c>
       <c r="B478" s="2"/>
       <c r="C478" s="3" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="D478" s="11" t="s">
-        <v>875</v>
+        <v>456</v>
       </c>
       <c r="E478" s="2"/>
     </row>
@@ -11317,10 +11330,10 @@
       </c>
       <c r="B479" s="2"/>
       <c r="C479" s="3" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="D479" s="11" t="s">
-        <v>456</v>
+        <v>876</v>
       </c>
       <c r="E479" s="2"/>
     </row>
@@ -11330,36 +11343,36 @@
       </c>
       <c r="B480" s="2"/>
       <c r="C480" s="3" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D480" s="11" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="E480" s="2"/>
     </row>
-    <row r="481" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:5" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A481" s="2" t="s">
         <v>416</v>
       </c>
       <c r="B481" s="2"/>
       <c r="C481" s="3" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="D481" s="11" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="E481" s="2"/>
     </row>
-    <row r="482" spans="1:5" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A482" s="2" t="s">
         <v>416</v>
       </c>
       <c r="B482" s="2"/>
       <c r="C482" s="3" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="D482" s="11" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="E482" s="2"/>
     </row>
@@ -11369,10 +11382,10 @@
       </c>
       <c r="B483" s="2"/>
       <c r="C483" s="3" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="D483" s="11" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="E483" s="2"/>
     </row>
@@ -11382,10 +11395,10 @@
       </c>
       <c r="B484" s="2"/>
       <c r="C484" s="3" t="s">
-        <v>433</v>
+        <v>457</v>
       </c>
       <c r="D484" s="11" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="E484" s="2"/>
     </row>
@@ -11395,10 +11408,10 @@
       </c>
       <c r="B485" s="2"/>
       <c r="C485" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="D485" s="11" t="s">
-        <v>881</v>
+        <v>422</v>
+      </c>
+      <c r="D485" s="2" t="s">
+        <v>422</v>
       </c>
       <c r="E485" s="2"/>
     </row>
@@ -11408,10 +11421,10 @@
       </c>
       <c r="B486" s="2"/>
       <c r="C486" s="3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D486" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E486" s="2"/>
     </row>
@@ -11421,10 +11434,10 @@
       </c>
       <c r="B487" s="2"/>
       <c r="C487" s="3" t="s">
-        <v>423</v>
+        <v>450</v>
       </c>
       <c r="D487" s="2" t="s">
-        <v>423</v>
+        <v>450</v>
       </c>
       <c r="E487" s="2"/>
     </row>
@@ -11434,10 +11447,10 @@
       </c>
       <c r="B488" s="2"/>
       <c r="C488" s="3" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="D488" s="2" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="E488" s="2"/>
     </row>
@@ -11447,25 +11460,64 @@
       </c>
       <c r="B489" s="2"/>
       <c r="C489" s="3" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="D489" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="E489" s="2"/>
     </row>
     <row r="490" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A490" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="B490" s="2"/>
+      <c r="A490" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="B490" s="32"/>
       <c r="C490" s="3" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="D490" s="2" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="E490" s="2"/>
+    </row>
+    <row r="491" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+      <c r="A491" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="B491" s="32"/>
+      <c r="C491" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="D491" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E491" s="2"/>
+    </row>
+    <row r="492" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+      <c r="A492" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="B492" s="32"/>
+      <c r="C492" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="D492" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="E492" s="2"/>
+    </row>
+    <row r="493" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+      <c r="A493" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="B493" s="32"/>
+      <c r="C493" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="D493" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="E493" s="2"/>
     </row>
     <row r="494" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A494" s="5" t="s">
@@ -11473,62 +11525,70 @@
       </c>
       <c r="B494" s="32"/>
       <c r="C494" s="3" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="D494" s="2" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E494" s="2"/>
     </row>
     <row r="495" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A495" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="B495" s="32"/>
+        <v>565</v>
+      </c>
+      <c r="B495" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="C495" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="D495" s="2" t="s">
-        <v>462</v>
+        <v>825</v>
+      </c>
+      <c r="D495" s="11" t="s">
+        <v>825</v>
       </c>
       <c r="E495" s="2"/>
     </row>
     <row r="496" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A496" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="B496" s="32"/>
+        <v>565</v>
+      </c>
+      <c r="B496" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="C496" s="3" t="s">
-        <v>463</v>
+        <v>67</v>
       </c>
       <c r="D496" s="2" t="s">
-        <v>463</v>
+        <v>67</v>
       </c>
       <c r="E496" s="2"/>
     </row>
     <row r="497" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A497" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="B497" s="32"/>
+        <v>565</v>
+      </c>
+      <c r="B497" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="C497" s="3" t="s">
-        <v>464</v>
+        <v>68</v>
       </c>
       <c r="D497" s="2" t="s">
-        <v>464</v>
+        <v>68</v>
       </c>
       <c r="E497" s="2"/>
     </row>
     <row r="498" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A498" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="B498" s="32"/>
+        <v>565</v>
+      </c>
+      <c r="B498" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="C498" s="3" t="s">
-        <v>465</v>
+        <v>69</v>
       </c>
       <c r="D498" s="2" t="s">
-        <v>465</v>
+        <v>69</v>
       </c>
       <c r="E498" s="2"/>
     </row>
@@ -11540,10 +11600,10 @@
         <v>24</v>
       </c>
       <c r="C499" s="3" t="s">
-        <v>825</v>
-      </c>
-      <c r="D499" s="11" t="s">
-        <v>825</v>
+        <v>70</v>
+      </c>
+      <c r="D499" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="E499" s="2"/>
     </row>
@@ -11555,10 +11615,10 @@
         <v>24</v>
       </c>
       <c r="C500" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D500" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E500" s="2"/>
     </row>
@@ -11570,10 +11630,10 @@
         <v>24</v>
       </c>
       <c r="C501" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D501" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E501" s="2"/>
     </row>
@@ -11585,10 +11645,10 @@
         <v>24</v>
       </c>
       <c r="C502" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D502" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E502" s="2"/>
     </row>
@@ -11600,10 +11660,10 @@
         <v>24</v>
       </c>
       <c r="C503" s="3" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D503" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E503" s="2"/>
     </row>
@@ -11615,10 +11675,10 @@
         <v>24</v>
       </c>
       <c r="C504" s="3" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D504" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E504" s="2"/>
     </row>
@@ -11630,10 +11690,10 @@
         <v>24</v>
       </c>
       <c r="C505" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D505" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E505" s="2"/>
     </row>
@@ -11645,10 +11705,10 @@
         <v>24</v>
       </c>
       <c r="C506" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D506" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E506" s="2"/>
     </row>
@@ -11660,10 +11720,10 @@
         <v>24</v>
       </c>
       <c r="C507" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D507" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E507" s="2"/>
     </row>
@@ -11675,10 +11735,10 @@
         <v>24</v>
       </c>
       <c r="C508" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D508" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E508" s="2"/>
     </row>
@@ -11690,10 +11750,10 @@
         <v>24</v>
       </c>
       <c r="C509" s="3" t="s">
-        <v>76</v>
+        <v>566</v>
       </c>
       <c r="D509" s="2" t="s">
-        <v>76</v>
+        <v>566</v>
       </c>
       <c r="E509" s="2"/>
     </row>
@@ -11705,10 +11765,10 @@
         <v>24</v>
       </c>
       <c r="C510" s="3" t="s">
-        <v>77</v>
+        <v>567</v>
       </c>
       <c r="D510" s="2" t="s">
-        <v>77</v>
+        <v>567</v>
       </c>
       <c r="E510" s="2"/>
     </row>
@@ -11720,10 +11780,10 @@
         <v>24</v>
       </c>
       <c r="C511" s="3" t="s">
-        <v>78</v>
+        <v>568</v>
       </c>
       <c r="D511" s="2" t="s">
-        <v>78</v>
+        <v>568</v>
       </c>
       <c r="E511" s="2"/>
     </row>
@@ -11735,10 +11795,10 @@
         <v>24</v>
       </c>
       <c r="C512" s="3" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="D512" s="2" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="E512" s="2"/>
     </row>
@@ -11750,10 +11810,10 @@
         <v>24</v>
       </c>
       <c r="C513" s="3" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="D513" s="2" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="E513" s="2"/>
     </row>
@@ -11765,10 +11825,10 @@
         <v>24</v>
       </c>
       <c r="C514" s="3" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="D514" s="2" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="E514" s="2"/>
     </row>
@@ -11780,10 +11840,10 @@
         <v>24</v>
       </c>
       <c r="C515" s="3" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="D515" s="2" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="E515" s="2"/>
     </row>
@@ -11795,10 +11855,10 @@
         <v>24</v>
       </c>
       <c r="C516" s="3" t="s">
-        <v>101</v>
+        <v>572</v>
       </c>
       <c r="D516" s="2" t="s">
-        <v>101</v>
+        <v>572</v>
       </c>
       <c r="E516" s="2"/>
     </row>
@@ -11810,10 +11870,10 @@
         <v>24</v>
       </c>
       <c r="C517" s="3" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="D517" s="2" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="E517" s="2"/>
     </row>
@@ -11825,10 +11885,10 @@
         <v>24</v>
       </c>
       <c r="C518" s="3" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="D518" s="2" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="E518" s="2"/>
     </row>
@@ -11840,10 +11900,10 @@
         <v>24</v>
       </c>
       <c r="C519" s="3" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="D519" s="2" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="E519" s="2"/>
     </row>
@@ -11855,10 +11915,10 @@
         <v>24</v>
       </c>
       <c r="C520" s="3" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="D520" s="2" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="E520" s="2"/>
     </row>
@@ -11870,10 +11930,10 @@
         <v>24</v>
       </c>
       <c r="C521" s="3" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="D521" s="2" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="E521" s="2"/>
     </row>
@@ -11885,10 +11945,10 @@
         <v>24</v>
       </c>
       <c r="C522" s="3" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="D522" s="2" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="E522" s="2"/>
     </row>
@@ -11897,28 +11957,28 @@
         <v>565</v>
       </c>
       <c r="B523" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C523" s="3" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="D523" s="2" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="E523" s="2"/>
     </row>
-    <row r="524" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A524" s="5" t="s">
         <v>565</v>
       </c>
       <c r="B524" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C524" s="3" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="D524" s="2" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="E524" s="2"/>
     </row>
@@ -11927,13 +11987,13 @@
         <v>565</v>
       </c>
       <c r="B525" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C525" s="3" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="D525" s="2" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="E525" s="2"/>
     </row>
@@ -11942,13 +12002,13 @@
         <v>565</v>
       </c>
       <c r="B526" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C526" s="3" t="s">
-        <v>578</v>
+        <v>100</v>
       </c>
       <c r="D526" s="2" t="s">
-        <v>578</v>
+        <v>100</v>
       </c>
       <c r="E526" s="2"/>
     </row>
@@ -11960,14 +12020,14 @@
         <v>23</v>
       </c>
       <c r="C527" s="3" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="D527" s="2" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="E527" s="2"/>
     </row>
-    <row r="528" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="528" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A528" s="5" t="s">
         <v>565</v>
       </c>
@@ -11975,10 +12035,10 @@
         <v>23</v>
       </c>
       <c r="C528" s="3" t="s">
-        <v>581</v>
+        <v>102</v>
       </c>
       <c r="D528" s="2" t="s">
-        <v>581</v>
+        <v>102</v>
       </c>
       <c r="E528" s="2"/>
     </row>
@@ -11990,10 +12050,10 @@
         <v>23</v>
       </c>
       <c r="C529" s="3" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="D529" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E529" s="2"/>
     </row>
@@ -12002,13 +12062,13 @@
         <v>565</v>
       </c>
       <c r="B530" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C530" s="3" t="s">
-        <v>100</v>
+        <v>585</v>
       </c>
       <c r="D530" s="2" t="s">
-        <v>100</v>
+        <v>585</v>
       </c>
       <c r="E530" s="2"/>
     </row>
@@ -12017,13 +12077,13 @@
         <v>565</v>
       </c>
       <c r="B531" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C531" s="3" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="D531" s="2" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="E531" s="2"/>
     </row>
@@ -12032,13 +12092,13 @@
         <v>565</v>
       </c>
       <c r="B532" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C532" s="3" t="s">
-        <v>102</v>
+        <v>587</v>
       </c>
       <c r="D532" s="2" t="s">
-        <v>102</v>
+        <v>587</v>
       </c>
       <c r="E532" s="2"/>
     </row>
@@ -12047,13 +12107,13 @@
         <v>565</v>
       </c>
       <c r="B533" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C533" s="3" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="D533" s="2" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="E533" s="2"/>
     </row>
@@ -12065,10 +12125,10 @@
         <v>24</v>
       </c>
       <c r="C534" s="3" t="s">
-        <v>585</v>
+        <v>104</v>
       </c>
       <c r="D534" s="2" t="s">
-        <v>585</v>
+        <v>104</v>
       </c>
       <c r="E534" s="2"/>
     </row>
@@ -12080,10 +12140,10 @@
         <v>24</v>
       </c>
       <c r="C535" s="3" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="D535" s="2" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E535" s="2"/>
     </row>
@@ -12095,10 +12155,10 @@
         <v>24</v>
       </c>
       <c r="C536" s="3" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="D536" s="2" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="E536" s="2"/>
     </row>
@@ -12110,10 +12170,10 @@
         <v>24</v>
       </c>
       <c r="C537" s="3" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="D537" s="2" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="E537" s="2"/>
     </row>
@@ -12125,10 +12185,10 @@
         <v>24</v>
       </c>
       <c r="C538" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D538" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E538" s="2"/>
     </row>
@@ -12140,10 +12200,10 @@
         <v>24</v>
       </c>
       <c r="C539" s="3" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="D539" s="2" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="E539" s="2"/>
     </row>
@@ -12155,10 +12215,10 @@
         <v>24</v>
       </c>
       <c r="C540" s="3" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="D540" s="2" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="E540" s="2"/>
     </row>
@@ -12167,13 +12227,13 @@
         <v>565</v>
       </c>
       <c r="B541" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C541" s="3" t="s">
-        <v>591</v>
+        <v>811</v>
+      </c>
+      <c r="C541" s="5" t="s">
+        <v>811</v>
       </c>
       <c r="D541" s="2" t="s">
-        <v>591</v>
+        <v>811</v>
       </c>
       <c r="E541" s="2"/>
     </row>
@@ -12181,14 +12241,14 @@
       <c r="A542" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="B542" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C542" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D542" s="2" t="s">
-        <v>103</v>
+      <c r="B542" s="9" t="s">
+        <v>595</v>
+      </c>
+      <c r="C542" s="9" t="s">
+        <v>595</v>
+      </c>
+      <c r="D542" s="11" t="s">
+        <v>819</v>
       </c>
       <c r="E542" s="2"/>
     </row>
@@ -12196,113 +12256,105 @@
       <c r="A543" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="B543" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C543" s="3" t="s">
-        <v>592</v>
-      </c>
-      <c r="D543" s="2" t="s">
-        <v>592</v>
+      <c r="B543" s="9" t="s">
+        <v>596</v>
+      </c>
+      <c r="C543" s="9" t="s">
+        <v>596</v>
+      </c>
+      <c r="D543" s="11" t="s">
+        <v>820</v>
       </c>
       <c r="E543" s="2"/>
     </row>
     <row r="544" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A544" s="5" t="s">
-        <v>565</v>
-      </c>
-      <c r="B544" s="5" t="s">
-        <v>24</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="B544" s="2"/>
       <c r="C544" s="3" t="s">
-        <v>593</v>
-      </c>
-      <c r="D544" s="2" t="s">
-        <v>593</v>
+        <v>84</v>
+      </c>
+      <c r="D544" s="11" t="s">
+        <v>882</v>
       </c>
       <c r="E544" s="2"/>
     </row>
     <row r="545" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A545" s="5" t="s">
-        <v>565</v>
-      </c>
-      <c r="B545" s="5" t="s">
-        <v>811</v>
-      </c>
-      <c r="C545" s="5" t="s">
-        <v>811</v>
-      </c>
-      <c r="D545" s="2" t="s">
-        <v>811</v>
+        <v>85</v>
+      </c>
+      <c r="B545" s="2"/>
+      <c r="C545" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D545" s="11" t="s">
+        <v>883</v>
       </c>
       <c r="E545" s="2"/>
     </row>
     <row r="546" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A546" s="5" t="s">
-        <v>565</v>
-      </c>
-      <c r="B546" s="9" t="s">
-        <v>595</v>
-      </c>
-      <c r="C546" s="9" t="s">
-        <v>595</v>
+        <v>85</v>
+      </c>
+      <c r="B546" s="2"/>
+      <c r="C546" s="3" t="s">
+        <v>83</v>
       </c>
       <c r="D546" s="11" t="s">
-        <v>819</v>
+        <v>884</v>
       </c>
       <c r="E546" s="2"/>
     </row>
     <row r="547" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A547" s="5" t="s">
-        <v>565</v>
-      </c>
-      <c r="B547" s="9" t="s">
-        <v>596</v>
-      </c>
-      <c r="C547" s="9" t="s">
-        <v>596</v>
-      </c>
-      <c r="D547" s="11" t="s">
-        <v>820</v>
+        <v>86</v>
+      </c>
+      <c r="B547" s="2"/>
+      <c r="C547" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D547" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="E547" s="2"/>
     </row>
     <row r="548" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A548" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B548" s="2"/>
       <c r="C548" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D548" s="11" t="s">
-        <v>882</v>
+        <v>88</v>
+      </c>
+      <c r="D548" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="E548" s="2"/>
     </row>
     <row r="549" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A549" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B549" s="2"/>
       <c r="C549" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D549" s="11" t="s">
-        <v>883</v>
+        <v>89</v>
+      </c>
+      <c r="D549" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="E549" s="2"/>
     </row>
-    <row r="550" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:5" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A550" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B550" s="2"/>
       <c r="C550" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D550" s="11" t="s">
-        <v>884</v>
+        <v>90</v>
+      </c>
+      <c r="D550" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="E550" s="2"/>
     </row>
@@ -12312,10 +12364,10 @@
       </c>
       <c r="B551" s="2"/>
       <c r="C551" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D551" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E551" s="2"/>
     </row>
@@ -12325,10 +12377,10 @@
       </c>
       <c r="B552" s="2"/>
       <c r="C552" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D552" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E552" s="2"/>
     </row>
@@ -12338,23 +12390,23 @@
       </c>
       <c r="B553" s="2"/>
       <c r="C553" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D553" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E553" s="2"/>
     </row>
-    <row r="554" spans="1:5" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A554" s="5" t="s">
         <v>86</v>
       </c>
       <c r="B554" s="2"/>
       <c r="C554" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D554" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E554" s="2"/>
     </row>
@@ -12364,10 +12416,10 @@
       </c>
       <c r="B555" s="2"/>
       <c r="C555" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D555" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E555" s="2"/>
     </row>
@@ -12377,10 +12429,10 @@
       </c>
       <c r="B556" s="2"/>
       <c r="C556" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D556" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E556" s="2"/>
     </row>
@@ -12390,10 +12442,10 @@
       </c>
       <c r="B557" s="2"/>
       <c r="C557" s="3" t="s">
-        <v>93</v>
+        <v>599</v>
       </c>
       <c r="D557" s="2" t="s">
-        <v>93</v>
+        <v>599</v>
       </c>
       <c r="E557" s="2"/>
     </row>
@@ -12403,10 +12455,10 @@
       </c>
       <c r="B558" s="2"/>
       <c r="C558" s="3" t="s">
-        <v>94</v>
+        <v>600</v>
       </c>
       <c r="D558" s="2" t="s">
-        <v>94</v>
+        <v>600</v>
       </c>
       <c r="E558" s="2"/>
     </row>
@@ -12416,10 +12468,10 @@
       </c>
       <c r="B559" s="2"/>
       <c r="C559" s="3" t="s">
-        <v>95</v>
+        <v>601</v>
       </c>
       <c r="D559" s="2" t="s">
-        <v>95</v>
+        <v>601</v>
       </c>
       <c r="E559" s="2"/>
     </row>
@@ -12429,10 +12481,10 @@
       </c>
       <c r="B560" s="2"/>
       <c r="C560" s="3" t="s">
-        <v>96</v>
+        <v>602</v>
       </c>
       <c r="D560" s="2" t="s">
-        <v>96</v>
+        <v>602</v>
       </c>
       <c r="E560" s="2"/>
     </row>
@@ -12442,10 +12494,10 @@
       </c>
       <c r="B561" s="2"/>
       <c r="C561" s="3" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="D561" s="2" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="E561" s="2"/>
     </row>
@@ -12455,10 +12507,10 @@
       </c>
       <c r="B562" s="2"/>
       <c r="C562" s="3" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="D562" s="2" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="E562" s="2"/>
     </row>
@@ -12468,10 +12520,10 @@
       </c>
       <c r="B563" s="2"/>
       <c r="C563" s="3" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="D563" s="2" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="E563" s="2"/>
     </row>
@@ -12481,194 +12533,194 @@
       </c>
       <c r="B564" s="2"/>
       <c r="C564" s="3" t="s">
-        <v>602</v>
-      </c>
-      <c r="D564" s="2" t="s">
-        <v>602</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="D564" s="11"/>
       <c r="E564" s="2"/>
     </row>
     <row r="565" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A565" s="5" t="s">
+      <c r="A565" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="B565" s="2"/>
-      <c r="C565" s="3" t="s">
-        <v>603</v>
-      </c>
-      <c r="D565" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="E565" s="2"/>
+      <c r="B565" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="C565" s="7" t="s">
+        <v>606</v>
+      </c>
+      <c r="D565" s="10" t="s">
+        <v>817</v>
+      </c>
+      <c r="E565" s="10"/>
     </row>
     <row r="566" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A566" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B566" s="2"/>
+      <c r="A566" s="26" t="s">
+        <v>906</v>
+      </c>
+      <c r="B566" s="26" t="s">
+        <v>612</v>
+      </c>
       <c r="C566" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="D566" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="E566" s="2"/>
+        <v>921</v>
+      </c>
+      <c r="D566" s="27" t="s">
+        <v>818</v>
+      </c>
+      <c r="E566" s="27"/>
     </row>
     <row r="567" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A567" s="5" t="s">
-        <v>86</v>
+      <c r="A567" s="2" t="s">
+        <v>614</v>
       </c>
       <c r="B567" s="2"/>
       <c r="C567" s="3" t="s">
-        <v>605</v>
+        <v>617</v>
       </c>
       <c r="D567" s="2" t="s">
-        <v>605</v>
+        <v>617</v>
       </c>
       <c r="E567" s="2"/>
     </row>
     <row r="568" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A568" s="5" t="s">
-        <v>86</v>
+      <c r="A568" s="2" t="s">
+        <v>614</v>
       </c>
       <c r="B568" s="2"/>
       <c r="C568" s="3" t="s">
-        <v>607</v>
-      </c>
-      <c r="D568" s="11"/>
+        <v>618</v>
+      </c>
+      <c r="D568" s="2" t="s">
+        <v>618</v>
+      </c>
       <c r="E568" s="2"/>
     </row>
     <row r="569" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A569" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="B569" s="6" t="s">
-        <v>608</v>
-      </c>
-      <c r="C569" s="7" t="s">
-        <v>606</v>
-      </c>
-      <c r="D569" s="10" t="s">
-        <v>817</v>
-      </c>
-      <c r="E569" s="10"/>
+      <c r="A569" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="B569" s="2"/>
+      <c r="C569" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="D569" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="E569" s="2"/>
     </row>
     <row r="570" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A570" s="26" t="s">
-        <v>906</v>
-      </c>
-      <c r="B570" s="26" t="s">
-        <v>612</v>
-      </c>
+      <c r="A570" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="B570" s="2"/>
       <c r="C570" s="3" t="s">
-        <v>921</v>
-      </c>
-      <c r="D570" s="27" t="s">
-        <v>818</v>
-      </c>
-      <c r="E570" s="27"/>
+        <v>620</v>
+      </c>
+      <c r="D570" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="E570" s="2"/>
     </row>
     <row r="571" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A571" s="2" t="s">
-        <v>614</v>
+      <c r="A571" s="5" t="s">
+        <v>616</v>
       </c>
       <c r="B571" s="2"/>
-      <c r="C571" s="3" t="s">
-        <v>617</v>
-      </c>
-      <c r="D571" s="2" t="s">
-        <v>617</v>
+      <c r="C571" s="11" t="s">
+        <v>885</v>
+      </c>
+      <c r="D571" s="11" t="s">
+        <v>885</v>
       </c>
       <c r="E571" s="2"/>
     </row>
     <row r="572" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A572" s="2" t="s">
-        <v>614</v>
+      <c r="A572" s="5" t="s">
+        <v>616</v>
       </c>
       <c r="B572" s="2"/>
       <c r="C572" s="3" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="D572" s="2" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="E572" s="2"/>
     </row>
     <row r="573" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A573" s="2" t="s">
-        <v>614</v>
+      <c r="A573" s="5" t="s">
+        <v>616</v>
       </c>
       <c r="B573" s="2"/>
       <c r="C573" s="3" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="D573" s="2" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="E573" s="2"/>
     </row>
     <row r="574" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A574" s="2" t="s">
-        <v>614</v>
+      <c r="A574" s="5" t="s">
+        <v>616</v>
       </c>
       <c r="B574" s="2"/>
       <c r="C574" s="3" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="D574" s="2" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="E574" s="2"/>
     </row>
-    <row r="575" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A575" s="5" t="s">
         <v>616</v>
       </c>
       <c r="B575" s="2"/>
-      <c r="C575" s="11" t="s">
-        <v>885</v>
-      </c>
-      <c r="D575" s="11" t="s">
-        <v>885</v>
+      <c r="C575" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="D575" s="2" t="s">
+        <v>625</v>
       </c>
       <c r="E575" s="2"/>
     </row>
-    <row r="576" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A576" s="5" t="s">
         <v>616</v>
       </c>
       <c r="B576" s="2"/>
       <c r="C576" s="3" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="D576" s="2" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="E576" s="2"/>
     </row>
-    <row r="577" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A577" s="5" t="s">
         <v>616</v>
       </c>
       <c r="B577" s="2"/>
       <c r="C577" s="3" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="D577" s="2" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="E577" s="2"/>
     </row>
-    <row r="578" spans="1:5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A578" s="5" t="s">
         <v>616</v>
       </c>
       <c r="B578" s="2"/>
       <c r="C578" s="3" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D578" s="2" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="E578" s="2"/>
     </row>
@@ -12678,10 +12730,10 @@
       </c>
       <c r="B579" s="2"/>
       <c r="C579" s="3" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D579" s="2" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="E579" s="2"/>
     </row>
@@ -12691,10 +12743,10 @@
       </c>
       <c r="B580" s="2"/>
       <c r="C580" s="3" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="D580" s="2" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="E580" s="2"/>
     </row>
@@ -12704,10 +12756,10 @@
       </c>
       <c r="B581" s="2"/>
       <c r="C581" s="3" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="D581" s="2" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="E581" s="2"/>
     </row>
@@ -12717,10 +12769,10 @@
       </c>
       <c r="B582" s="2"/>
       <c r="C582" s="3" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D582" s="2" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="E582" s="2"/>
     </row>
@@ -12730,10 +12782,10 @@
       </c>
       <c r="B583" s="2"/>
       <c r="C583" s="3" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="D583" s="2" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="E583" s="2"/>
     </row>
@@ -12743,10 +12795,10 @@
       </c>
       <c r="B584" s="2"/>
       <c r="C584" s="3" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="D584" s="2" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="E584" s="2"/>
     </row>
@@ -12756,10 +12808,10 @@
       </c>
       <c r="B585" s="2"/>
       <c r="C585" s="3" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="D585" s="2" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="E585" s="2"/>
     </row>
@@ -12769,10 +12821,10 @@
       </c>
       <c r="B586" s="2"/>
       <c r="C586" s="3" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="D586" s="2" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="E586" s="2"/>
     </row>
@@ -12782,10 +12834,10 @@
       </c>
       <c r="B587" s="2"/>
       <c r="C587" s="3" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="D587" s="2" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="E587" s="2"/>
     </row>
@@ -12795,10 +12847,10 @@
       </c>
       <c r="B588" s="2"/>
       <c r="C588" s="3" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="D588" s="2" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="E588" s="2"/>
     </row>
@@ -12808,10 +12860,10 @@
       </c>
       <c r="B589" s="2"/>
       <c r="C589" s="3" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="D589" s="2" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="E589" s="2"/>
     </row>
@@ -12821,10 +12873,10 @@
       </c>
       <c r="B590" s="2"/>
       <c r="C590" s="3" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="D590" s="2" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="E590" s="2"/>
     </row>
@@ -12834,10 +12886,10 @@
       </c>
       <c r="B591" s="2"/>
       <c r="C591" s="3" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D591" s="2" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="E591" s="2"/>
     </row>
@@ -12847,10 +12899,10 @@
       </c>
       <c r="B592" s="2"/>
       <c r="C592" s="3" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="D592" s="2" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="E592" s="2"/>
     </row>
@@ -12860,10 +12912,10 @@
       </c>
       <c r="B593" s="2"/>
       <c r="C593" s="3" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="D593" s="2" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E593" s="2"/>
     </row>
@@ -12873,10 +12925,10 @@
       </c>
       <c r="B594" s="2"/>
       <c r="C594" s="3" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="D594" s="2" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="E594" s="2"/>
     </row>
@@ -12886,10 +12938,10 @@
       </c>
       <c r="B595" s="2"/>
       <c r="C595" s="3" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="D595" s="2" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="E595" s="2"/>
     </row>
@@ -12899,10 +12951,10 @@
       </c>
       <c r="B596" s="2"/>
       <c r="C596" s="3" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="D596" s="2" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="E596" s="2"/>
     </row>
@@ -12910,64 +12962,72 @@
       <c r="A597" s="5" t="s">
         <v>616</v>
       </c>
-      <c r="B597" s="2"/>
+      <c r="B597"/>
       <c r="C597" s="3" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="D597" s="2" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E597" s="2"/>
     </row>
     <row r="598" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A598" s="5" t="s">
-        <v>616</v>
-      </c>
-      <c r="B598" s="2"/>
+        <v>649</v>
+      </c>
+      <c r="B598" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="C598" s="3" t="s">
-        <v>644</v>
-      </c>
-      <c r="D598" s="2" t="s">
-        <v>644</v>
+        <v>650</v>
+      </c>
+      <c r="D598" s="11" t="s">
+        <v>650</v>
       </c>
       <c r="E598" s="2"/>
     </row>
     <row r="599" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A599" s="5" t="s">
-        <v>616</v>
-      </c>
-      <c r="B599" s="2"/>
+        <v>649</v>
+      </c>
+      <c r="B599" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="C599" s="3" t="s">
-        <v>645</v>
-      </c>
-      <c r="D599" s="2" t="s">
-        <v>645</v>
+        <v>651</v>
+      </c>
+      <c r="D599" s="11" t="s">
+        <v>651</v>
       </c>
       <c r="E599" s="2"/>
     </row>
     <row r="600" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A600" s="5" t="s">
-        <v>616</v>
-      </c>
-      <c r="B600" s="2"/>
+        <v>649</v>
+      </c>
+      <c r="B600" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="C600" s="3" t="s">
-        <v>646</v>
-      </c>
-      <c r="D600" s="2" t="s">
-        <v>646</v>
+        <v>652</v>
+      </c>
+      <c r="D600" s="11" t="s">
+        <v>652</v>
       </c>
       <c r="E600" s="2"/>
     </row>
     <row r="601" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A601" s="5" t="s">
-        <v>616</v>
-      </c>
-      <c r="B601"/>
+        <v>649</v>
+      </c>
+      <c r="B601" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="C601" s="3" t="s">
-        <v>647</v>
-      </c>
-      <c r="D601" s="2" t="s">
-        <v>647</v>
+        <v>653</v>
+      </c>
+      <c r="D601" s="11" t="s">
+        <v>653</v>
       </c>
       <c r="E601" s="2"/>
     </row>
@@ -12976,13 +13036,13 @@
         <v>649</v>
       </c>
       <c r="B602" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C602" s="3" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="D602" s="11" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="E602" s="2"/>
     </row>
@@ -12994,10 +13054,10 @@
         <v>23</v>
       </c>
       <c r="C603" s="3" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="D603" s="11" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="E603" s="2"/>
     </row>
@@ -13009,10 +13069,10 @@
         <v>23</v>
       </c>
       <c r="C604" s="3" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="D604" s="11" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="E604" s="2"/>
     </row>
@@ -13024,10 +13084,10 @@
         <v>23</v>
       </c>
       <c r="C605" s="3" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="D605" s="11" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="E605" s="2"/>
     </row>
@@ -13039,10 +13099,10 @@
         <v>23</v>
       </c>
       <c r="C606" s="3" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="D606" s="11" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="E606" s="2"/>
     </row>
@@ -13054,10 +13114,10 @@
         <v>23</v>
       </c>
       <c r="C607" s="3" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="D607" s="11" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="E607" s="2"/>
     </row>
@@ -13069,10 +13129,10 @@
         <v>23</v>
       </c>
       <c r="C608" s="3" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="D608" s="11" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="E608" s="2"/>
     </row>
@@ -13084,10 +13144,10 @@
         <v>23</v>
       </c>
       <c r="C609" s="3" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="D609" s="11" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="E609" s="2"/>
     </row>
@@ -13099,10 +13159,10 @@
         <v>23</v>
       </c>
       <c r="C610" s="3" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="D610" s="11" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="E610" s="2"/>
     </row>
@@ -13113,73 +13173,73 @@
       <c r="B611" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C611" s="3" t="s">
-        <v>659</v>
-      </c>
-      <c r="D611" s="11" t="s">
-        <v>659</v>
-      </c>
-      <c r="E611" s="2"/>
+      <c r="C611" s="5" t="s">
+        <v>663</v>
+      </c>
+      <c r="D611" s="5" t="s">
+        <v>663</v>
+      </c>
+      <c r="E611" s="5"/>
     </row>
     <row r="612" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A612" s="5" t="s">
-        <v>649</v>
-      </c>
-      <c r="B612" s="5" t="s">
+        <v>665</v>
+      </c>
+      <c r="B612" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C612" s="3" t="s">
-        <v>660</v>
-      </c>
-      <c r="D612" s="11" t="s">
-        <v>660</v>
+        <v>667</v>
+      </c>
+      <c r="D612" s="2" t="s">
+        <v>667</v>
       </c>
       <c r="E612" s="2"/>
     </row>
     <row r="613" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A613" s="5" t="s">
-        <v>649</v>
-      </c>
-      <c r="B613" s="5" t="s">
+        <v>665</v>
+      </c>
+      <c r="B613" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C613" s="3" t="s">
-        <v>661</v>
-      </c>
-      <c r="D613" s="11" t="s">
-        <v>661</v>
+        <v>668</v>
+      </c>
+      <c r="D613" s="2" t="s">
+        <v>668</v>
       </c>
       <c r="E613" s="2"/>
     </row>
     <row r="614" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A614" s="5" t="s">
-        <v>649</v>
-      </c>
-      <c r="B614" s="5" t="s">
+        <v>665</v>
+      </c>
+      <c r="B614" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C614" s="3" t="s">
-        <v>662</v>
-      </c>
-      <c r="D614" s="11" t="s">
-        <v>662</v>
+        <v>669</v>
+      </c>
+      <c r="D614" s="2" t="s">
+        <v>669</v>
       </c>
       <c r="E614" s="2"/>
     </row>
     <row r="615" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A615" s="5" t="s">
-        <v>649</v>
-      </c>
-      <c r="B615" s="5" t="s">
+        <v>665</v>
+      </c>
+      <c r="B615" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C615" s="5" t="s">
-        <v>663</v>
-      </c>
-      <c r="D615" s="5" t="s">
-        <v>663</v>
-      </c>
-      <c r="E615" s="5"/>
+      <c r="C615" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="D615" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="E615" s="2"/>
     </row>
     <row r="616" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A616" s="5" t="s">
@@ -13189,10 +13249,10 @@
         <v>23</v>
       </c>
       <c r="C616" s="3" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="D616" s="2" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="E616" s="2"/>
     </row>
@@ -13204,10 +13264,10 @@
         <v>23</v>
       </c>
       <c r="C617" s="3" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="D617" s="2" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="E617" s="2"/>
     </row>
@@ -13216,125 +13276,120 @@
         <v>665</v>
       </c>
       <c r="B618" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C618" s="3" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="D618" s="2" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="E618" s="2"/>
     </row>
     <row r="619" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A619" s="5" t="s">
-        <v>665</v>
-      </c>
-      <c r="B619" s="2" t="s">
-        <v>23</v>
-      </c>
+        <v>674</v>
+      </c>
+      <c r="B619" s="2"/>
       <c r="C619" s="3" t="s">
-        <v>670</v>
-      </c>
-      <c r="D619" s="2" t="s">
-        <v>670</v>
+        <v>676</v>
+      </c>
+      <c r="D619" s="11" t="s">
+        <v>812</v>
       </c>
       <c r="E619" s="2"/>
     </row>
     <row r="620" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A620" s="5" t="s">
-        <v>665</v>
-      </c>
-      <c r="B620" s="2" t="s">
-        <v>23</v>
-      </c>
+        <v>674</v>
+      </c>
+      <c r="B620" s="2"/>
       <c r="C620" s="3" t="s">
-        <v>671</v>
-      </c>
-      <c r="D620" s="2" t="s">
-        <v>671</v>
+        <v>677</v>
+      </c>
+      <c r="D620" s="11" t="s">
+        <v>813</v>
       </c>
       <c r="E620" s="2"/>
     </row>
     <row r="621" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A621" s="5" t="s">
-        <v>665</v>
-      </c>
-      <c r="B621" s="2" t="s">
-        <v>23</v>
-      </c>
+        <v>674</v>
+      </c>
+      <c r="B621" s="2"/>
       <c r="C621" s="3" t="s">
-        <v>672</v>
-      </c>
-      <c r="D621" s="2" t="s">
-        <v>672</v>
+        <v>678</v>
+      </c>
+      <c r="D621" s="29" t="s">
+        <v>814</v>
       </c>
       <c r="E621" s="2"/>
     </row>
     <row r="622" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A622" s="5" t="s">
-        <v>665</v>
-      </c>
-      <c r="B622" s="2" t="s">
-        <v>24</v>
+        <v>674</v>
       </c>
       <c r="C622" s="3" t="s">
-        <v>666</v>
-      </c>
-      <c r="D622" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="E622" s="2"/>
+        <v>679</v>
+      </c>
+      <c r="D622" s="30" t="s">
+        <v>679</v>
+      </c>
     </row>
     <row r="623" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A623" s="5" t="s">
-        <v>674</v>
-      </c>
-      <c r="B623" s="2"/>
+        <v>683</v>
+      </c>
+      <c r="B623" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="C623" s="3" t="s">
-        <v>676</v>
-      </c>
-      <c r="D623" s="11" t="s">
-        <v>812</v>
-      </c>
+        <v>703</v>
+      </c>
+      <c r="D623" s="11"/>
       <c r="E623" s="2"/>
     </row>
     <row r="624" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A624" s="5" t="s">
-        <v>674</v>
-      </c>
-      <c r="B624" s="2"/>
+        <v>683</v>
+      </c>
+      <c r="B624" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="C624" s="3" t="s">
-        <v>677</v>
+        <v>701</v>
       </c>
       <c r="D624" s="11" t="s">
-        <v>813</v>
+        <v>827</v>
       </c>
       <c r="E624" s="2"/>
     </row>
     <row r="625" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A625" s="5" t="s">
-        <v>674</v>
-      </c>
-      <c r="B625" s="2"/>
+        <v>683</v>
+      </c>
+      <c r="B625" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="C625" s="3" t="s">
-        <v>678</v>
-      </c>
-      <c r="D625" s="29" t="s">
-        <v>814</v>
+        <v>702</v>
+      </c>
+      <c r="D625" s="11" t="s">
+        <v>826</v>
       </c>
       <c r="E625" s="2"/>
     </row>
     <row r="626" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A626" s="5" t="s">
-        <v>674</v>
+        <v>683</v>
+      </c>
+      <c r="B626" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="C626" s="3" t="s">
-        <v>679</v>
-      </c>
-      <c r="D626" s="30" t="s">
-        <v>679</v>
-      </c>
+        <v>706</v>
+      </c>
+      <c r="E626" s="2"/>
     </row>
     <row r="627" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A627" s="5" t="s">
@@ -13344,7 +13399,7 @@
         <v>24</v>
       </c>
       <c r="C627" s="3" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D627" s="11"/>
       <c r="E627" s="2"/>
@@ -13357,25 +13412,21 @@
         <v>24</v>
       </c>
       <c r="C628" s="3" t="s">
-        <v>701</v>
-      </c>
-      <c r="D628" s="11" t="s">
-        <v>827</v>
-      </c>
+        <v>705</v>
+      </c>
+      <c r="D628" s="11"/>
       <c r="E628" s="2"/>
     </row>
     <row r="629" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A629" s="5" t="s">
         <v>683</v>
       </c>
-      <c r="B629" s="2" t="s">
-        <v>24</v>
-      </c>
+      <c r="B629" s="2"/>
       <c r="C629" s="3" t="s">
-        <v>702</v>
-      </c>
-      <c r="D629" s="11" t="s">
-        <v>826</v>
+        <v>689</v>
+      </c>
+      <c r="D629" s="2" t="s">
+        <v>689</v>
       </c>
       <c r="E629" s="2"/>
     </row>
@@ -13383,11 +13434,12 @@
       <c r="A630" s="5" t="s">
         <v>683</v>
       </c>
-      <c r="B630" s="2" t="s">
-        <v>24</v>
-      </c>
+      <c r="B630" s="2"/>
       <c r="C630" s="3" t="s">
-        <v>706</v>
+        <v>690</v>
+      </c>
+      <c r="D630" s="2" t="s">
+        <v>690</v>
       </c>
       <c r="E630" s="2"/>
     </row>
@@ -13395,26 +13447,26 @@
       <c r="A631" s="5" t="s">
         <v>683</v>
       </c>
-      <c r="B631" s="2" t="s">
-        <v>24</v>
-      </c>
+      <c r="B631" s="2"/>
       <c r="C631" s="3" t="s">
-        <v>704</v>
-      </c>
-      <c r="D631" s="11"/>
+        <v>691</v>
+      </c>
+      <c r="D631" s="2" t="s">
+        <v>691</v>
+      </c>
       <c r="E631" s="2"/>
     </row>
     <row r="632" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A632" s="5" t="s">
         <v>683</v>
       </c>
-      <c r="B632" s="2" t="s">
-        <v>24</v>
-      </c>
+      <c r="B632" s="2"/>
       <c r="C632" s="3" t="s">
-        <v>705</v>
-      </c>
-      <c r="D632" s="11"/>
+        <v>692</v>
+      </c>
+      <c r="D632" s="2" t="s">
+        <v>692</v>
+      </c>
       <c r="E632" s="2"/>
     </row>
     <row r="633" spans="1:5" x14ac:dyDescent="0.45">
@@ -13423,10 +13475,10 @@
       </c>
       <c r="B633" s="2"/>
       <c r="C633" s="3" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="D633" s="2" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="E633" s="2"/>
     </row>
@@ -13436,10 +13488,10 @@
       </c>
       <c r="B634" s="2"/>
       <c r="C634" s="3" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="D634" s="2" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="E634" s="2"/>
     </row>
@@ -13449,10 +13501,10 @@
       </c>
       <c r="B635" s="2"/>
       <c r="C635" s="3" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="D635" s="2" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="E635" s="2"/>
     </row>
@@ -13462,10 +13514,10 @@
       </c>
       <c r="B636" s="2"/>
       <c r="C636" s="3" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="D636" s="2" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="E636" s="2"/>
     </row>
@@ -13475,11 +13527,9 @@
       </c>
       <c r="B637" s="2"/>
       <c r="C637" s="3" t="s">
-        <v>693</v>
-      </c>
-      <c r="D637" s="2" t="s">
-        <v>693</v>
-      </c>
+        <v>707</v>
+      </c>
+      <c r="D637" s="11"/>
       <c r="E637" s="2"/>
     </row>
     <row r="638" spans="1:5" x14ac:dyDescent="0.45">
@@ -13488,10 +13538,10 @@
       </c>
       <c r="B638" s="2"/>
       <c r="C638" s="3" t="s">
-        <v>694</v>
-      </c>
-      <c r="D638" s="2" t="s">
-        <v>694</v>
+        <v>685</v>
+      </c>
+      <c r="D638" s="11" t="s">
+        <v>828</v>
       </c>
       <c r="E638" s="2"/>
     </row>
@@ -13501,10 +13551,10 @@
       </c>
       <c r="B639" s="2"/>
       <c r="C639" s="3" t="s">
-        <v>699</v>
-      </c>
-      <c r="D639" s="2" t="s">
-        <v>699</v>
+        <v>686</v>
+      </c>
+      <c r="D639" s="11" t="s">
+        <v>829</v>
       </c>
       <c r="E639" s="2"/>
     </row>
@@ -13514,10 +13564,10 @@
       </c>
       <c r="B640" s="2"/>
       <c r="C640" s="3" t="s">
-        <v>700</v>
-      </c>
-      <c r="D640" s="2" t="s">
-        <v>700</v>
+        <v>687</v>
+      </c>
+      <c r="D640" s="11" t="s">
+        <v>830</v>
       </c>
       <c r="E640" s="2"/>
     </row>
@@ -13527,7 +13577,7 @@
       </c>
       <c r="B641" s="2"/>
       <c r="C641" s="3" t="s">
-        <v>707</v>
+        <v>688</v>
       </c>
       <c r="D641" s="11"/>
       <c r="E641" s="2"/>
@@ -13538,10 +13588,10 @@
       </c>
       <c r="B642" s="2"/>
       <c r="C642" s="3" t="s">
-        <v>685</v>
-      </c>
-      <c r="D642" s="11" t="s">
-        <v>828</v>
+        <v>695</v>
+      </c>
+      <c r="D642" s="2" t="s">
+        <v>695</v>
       </c>
       <c r="E642" s="2"/>
     </row>
@@ -13551,10 +13601,10 @@
       </c>
       <c r="B643" s="2"/>
       <c r="C643" s="3" t="s">
-        <v>686</v>
-      </c>
-      <c r="D643" s="11" t="s">
-        <v>829</v>
+        <v>696</v>
+      </c>
+      <c r="D643" s="2" t="s">
+        <v>696</v>
       </c>
       <c r="E643" s="2"/>
     </row>
@@ -13564,10 +13614,10 @@
       </c>
       <c r="B644" s="2"/>
       <c r="C644" s="3" t="s">
-        <v>687</v>
-      </c>
-      <c r="D644" s="11" t="s">
-        <v>830</v>
+        <v>697</v>
+      </c>
+      <c r="D644" s="2" t="s">
+        <v>697</v>
       </c>
       <c r="E644" s="2"/>
     </row>
@@ -13577,60 +13627,62 @@
       </c>
       <c r="B645" s="2"/>
       <c r="C645" s="3" t="s">
-        <v>688</v>
-      </c>
-      <c r="D645" s="11"/>
+        <v>698</v>
+      </c>
+      <c r="D645" s="2" t="s">
+        <v>698</v>
+      </c>
       <c r="E645" s="2"/>
     </row>
     <row r="646" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A646" s="5" t="s">
-        <v>683</v>
+      <c r="A646" s="2" t="s">
+        <v>734</v>
       </c>
       <c r="B646" s="2"/>
       <c r="C646" s="3" t="s">
-        <v>695</v>
+        <v>708</v>
       </c>
       <c r="D646" s="2" t="s">
-        <v>695</v>
+        <v>708</v>
       </c>
       <c r="E646" s="2"/>
     </row>
     <row r="647" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A647" s="5" t="s">
-        <v>683</v>
+      <c r="A647" s="2" t="s">
+        <v>734</v>
       </c>
       <c r="B647" s="2"/>
       <c r="C647" s="3" t="s">
-        <v>696</v>
+        <v>709</v>
       </c>
       <c r="D647" s="2" t="s">
-        <v>696</v>
+        <v>709</v>
       </c>
       <c r="E647" s="2"/>
     </row>
     <row r="648" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A648" s="5" t="s">
-        <v>683</v>
+      <c r="A648" s="2" t="s">
+        <v>734</v>
       </c>
       <c r="B648" s="2"/>
       <c r="C648" s="3" t="s">
-        <v>697</v>
+        <v>710</v>
       </c>
       <c r="D648" s="2" t="s">
-        <v>697</v>
+        <v>710</v>
       </c>
       <c r="E648" s="2"/>
     </row>
     <row r="649" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A649" s="5" t="s">
-        <v>683</v>
+      <c r="A649" s="2" t="s">
+        <v>734</v>
       </c>
       <c r="B649" s="2"/>
       <c r="C649" s="3" t="s">
-        <v>698</v>
+        <v>711</v>
       </c>
       <c r="D649" s="2" t="s">
-        <v>698</v>
+        <v>711</v>
       </c>
       <c r="E649" s="2"/>
     </row>
@@ -13640,10 +13692,10 @@
       </c>
       <c r="B650" s="2"/>
       <c r="C650" s="3" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="D650" s="2" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="E650" s="2"/>
     </row>
@@ -13653,10 +13705,10 @@
       </c>
       <c r="B651" s="2"/>
       <c r="C651" s="3" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="D651" s="2" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="E651" s="2"/>
     </row>
@@ -13666,10 +13718,10 @@
       </c>
       <c r="B652" s="2"/>
       <c r="C652" s="3" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="D652" s="2" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="E652" s="2"/>
     </row>
@@ -13679,10 +13731,10 @@
       </c>
       <c r="B653" s="2"/>
       <c r="C653" s="3" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="D653" s="2" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="E653" s="2"/>
     </row>
@@ -13692,10 +13744,10 @@
       </c>
       <c r="B654" s="2"/>
       <c r="C654" s="3" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="D654" s="2" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="E654" s="2"/>
     </row>
@@ -13705,10 +13757,10 @@
       </c>
       <c r="B655" s="2"/>
       <c r="C655" s="3" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="D655" s="2" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="E655" s="2"/>
     </row>
@@ -13718,10 +13770,10 @@
       </c>
       <c r="B656" s="2"/>
       <c r="C656" s="3" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="D656" s="2" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="E656" s="2"/>
     </row>
@@ -13731,10 +13783,10 @@
       </c>
       <c r="B657" s="2"/>
       <c r="C657" s="3" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D657" s="2" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="E657" s="2"/>
     </row>
@@ -13744,10 +13796,10 @@
       </c>
       <c r="B658" s="2"/>
       <c r="C658" s="3" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D658" s="2" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="E658" s="2"/>
     </row>
@@ -13757,10 +13809,10 @@
       </c>
       <c r="B659" s="2"/>
       <c r="C659" s="3" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="D659" s="2" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="E659" s="2"/>
     </row>
@@ -13770,10 +13822,10 @@
       </c>
       <c r="B660" s="2"/>
       <c r="C660" s="3" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="D660" s="2" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="E660" s="2"/>
     </row>
@@ -13783,10 +13835,10 @@
       </c>
       <c r="B661" s="2"/>
       <c r="C661" s="3" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="D661" s="2" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="E661" s="2"/>
     </row>
@@ -13796,10 +13848,10 @@
       </c>
       <c r="B662" s="2"/>
       <c r="C662" s="3" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="D662" s="2" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="E662" s="2"/>
     </row>
@@ -13809,10 +13861,10 @@
       </c>
       <c r="B663" s="2"/>
       <c r="C663" s="3" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="D663" s="2" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="E663" s="2"/>
     </row>
@@ -13822,10 +13874,10 @@
       </c>
       <c r="B664" s="2"/>
       <c r="C664" s="3" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="D664" s="2" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="E664" s="2"/>
     </row>
@@ -13835,10 +13887,10 @@
       </c>
       <c r="B665" s="2"/>
       <c r="C665" s="3" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="D665" s="2" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="E665" s="2"/>
     </row>
@@ -13848,10 +13900,10 @@
       </c>
       <c r="B666" s="2"/>
       <c r="C666" s="3" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="D666" s="2" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="E666" s="2"/>
     </row>
@@ -13861,10 +13913,10 @@
       </c>
       <c r="B667" s="2"/>
       <c r="C667" s="3" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="D667" s="2" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="E667" s="2"/>
     </row>
@@ -13874,10 +13926,10 @@
       </c>
       <c r="B668" s="2"/>
       <c r="C668" s="3" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="D668" s="2" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="E668" s="2"/>
     </row>
@@ -13887,10 +13939,10 @@
       </c>
       <c r="B669" s="2"/>
       <c r="C669" s="3" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="D669" s="2" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="E669" s="2"/>
     </row>
@@ -13900,10 +13952,10 @@
       </c>
       <c r="B670" s="2"/>
       <c r="C670" s="3" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="D670" s="2" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="E670" s="2"/>
     </row>
@@ -13913,10 +13965,10 @@
       </c>
       <c r="B671" s="2"/>
       <c r="C671" s="3" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="D671" s="2" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="E671" s="2"/>
     </row>
@@ -13925,130 +13977,130 @@
         <v>734</v>
       </c>
       <c r="B672" s="2"/>
-      <c r="C672" s="3" t="s">
-        <v>730</v>
+      <c r="C672" s="5" t="s">
+        <v>809</v>
       </c>
       <c r="D672" s="2" t="s">
-        <v>730</v>
+        <v>809</v>
       </c>
       <c r="E672" s="2"/>
     </row>
     <row r="673" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A673" s="2" t="s">
-        <v>734</v>
+        <v>751</v>
       </c>
       <c r="B673" s="2"/>
       <c r="C673" s="3" t="s">
-        <v>731</v>
+        <v>750</v>
       </c>
       <c r="D673" s="2" t="s">
-        <v>731</v>
+        <v>750</v>
       </c>
       <c r="E673" s="2"/>
     </row>
     <row r="674" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A674" s="2" t="s">
-        <v>734</v>
+        <v>751</v>
       </c>
       <c r="B674" s="2"/>
       <c r="C674" s="3" t="s">
-        <v>732</v>
-      </c>
-      <c r="D674" s="2" t="s">
-        <v>732</v>
+        <v>747</v>
+      </c>
+      <c r="D674" s="11" t="s">
+        <v>905</v>
       </c>
       <c r="E674" s="2"/>
     </row>
     <row r="675" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A675" s="2" t="s">
-        <v>734</v>
+        <v>751</v>
       </c>
       <c r="B675" s="2"/>
       <c r="C675" s="3" t="s">
-        <v>733</v>
+        <v>748</v>
       </c>
       <c r="D675" s="2" t="s">
-        <v>733</v>
+        <v>748</v>
       </c>
       <c r="E675" s="2"/>
     </row>
     <row r="676" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A676" s="2" t="s">
-        <v>734</v>
+        <v>751</v>
       </c>
       <c r="B676" s="2"/>
-      <c r="C676" s="5" t="s">
-        <v>809</v>
+      <c r="C676" s="3" t="s">
+        <v>749</v>
       </c>
       <c r="D676" s="2" t="s">
-        <v>809</v>
+        <v>749</v>
       </c>
       <c r="E676" s="2"/>
     </row>
     <row r="677" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A677" s="2" t="s">
-        <v>751</v>
+      <c r="A677" s="5" t="s">
+        <v>752</v>
       </c>
       <c r="B677" s="2"/>
-      <c r="C677" s="3" t="s">
-        <v>750</v>
-      </c>
-      <c r="D677" s="2" t="s">
-        <v>750</v>
-      </c>
-      <c r="E677" s="2"/>
+      <c r="C677" s="8" t="s">
+        <v>754</v>
+      </c>
+      <c r="D677" s="20" t="s">
+        <v>754</v>
+      </c>
+      <c r="E677" s="20"/>
     </row>
     <row r="678" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A678" s="2" t="s">
-        <v>751</v>
+      <c r="A678" s="22" t="s">
+        <v>752</v>
       </c>
       <c r="B678" s="2"/>
-      <c r="C678" s="3" t="s">
-        <v>747</v>
-      </c>
-      <c r="D678" s="11" t="s">
-        <v>905</v>
-      </c>
-      <c r="E678" s="2"/>
+      <c r="C678" s="31" t="s">
+        <v>755</v>
+      </c>
+      <c r="D678" s="24" t="s">
+        <v>755</v>
+      </c>
+      <c r="E678" s="24"/>
     </row>
     <row r="679" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A679" s="2" t="s">
-        <v>751</v>
+      <c r="A679" s="22" t="s">
+        <v>752</v>
       </c>
       <c r="B679" s="2"/>
-      <c r="C679" s="3" t="s">
-        <v>748</v>
-      </c>
-      <c r="D679" s="2" t="s">
-        <v>748</v>
-      </c>
-      <c r="E679" s="2"/>
+      <c r="C679" s="31" t="s">
+        <v>756</v>
+      </c>
+      <c r="D679" s="24" t="s">
+        <v>756</v>
+      </c>
+      <c r="E679" s="24"/>
     </row>
     <row r="680" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A680" s="2" t="s">
-        <v>751</v>
+      <c r="A680" s="22" t="s">
+        <v>752</v>
       </c>
       <c r="B680" s="2"/>
-      <c r="C680" s="3" t="s">
-        <v>749</v>
-      </c>
-      <c r="D680" s="2" t="s">
-        <v>749</v>
-      </c>
-      <c r="E680" s="2"/>
+      <c r="C680" s="31" t="s">
+        <v>757</v>
+      </c>
+      <c r="D680" s="24" t="s">
+        <v>757</v>
+      </c>
+      <c r="E680" s="24"/>
     </row>
     <row r="681" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A681" s="5" t="s">
+      <c r="A681" s="22" t="s">
         <v>752</v>
       </c>
       <c r="B681" s="2"/>
-      <c r="C681" s="8" t="s">
-        <v>754</v>
-      </c>
-      <c r="D681" s="20" t="s">
-        <v>754</v>
-      </c>
-      <c r="E681" s="20"/>
+      <c r="C681" s="31" t="s">
+        <v>758</v>
+      </c>
+      <c r="D681" s="24" t="s">
+        <v>758</v>
+      </c>
+      <c r="E681" s="24"/>
     </row>
     <row r="682" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A682" s="22" t="s">
@@ -14056,10 +14108,10 @@
       </c>
       <c r="B682" s="2"/>
       <c r="C682" s="31" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="D682" s="24" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="E682" s="24"/>
     </row>
@@ -14069,96 +14121,94 @@
       </c>
       <c r="B683" s="2"/>
       <c r="C683" s="31" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="D683" s="24" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="E683" s="24"/>
     </row>
     <row r="684" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A684" s="22" t="s">
-        <v>752</v>
+      <c r="A684" s="2" t="s">
+        <v>761</v>
       </c>
       <c r="B684" s="2"/>
-      <c r="C684" s="31" t="s">
-        <v>757</v>
-      </c>
-      <c r="D684" s="24" t="s">
-        <v>757</v>
-      </c>
-      <c r="E684" s="24"/>
+      <c r="C684" s="3" t="s">
+        <v>765</v>
+      </c>
+      <c r="D684" s="11"/>
+      <c r="E684" s="2"/>
     </row>
     <row r="685" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A685" s="22" t="s">
-        <v>752</v>
+      <c r="A685" s="2" t="s">
+        <v>761</v>
       </c>
       <c r="B685" s="2"/>
-      <c r="C685" s="31" t="s">
-        <v>758</v>
-      </c>
-      <c r="D685" s="24" t="s">
-        <v>758</v>
-      </c>
-      <c r="E685" s="24"/>
+      <c r="C685" s="3" t="s">
+        <v>764</v>
+      </c>
+      <c r="D685" s="11"/>
+      <c r="E685" s="2"/>
     </row>
     <row r="686" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A686" s="22" t="s">
-        <v>752</v>
+      <c r="A686" s="2" t="s">
+        <v>761</v>
       </c>
       <c r="B686" s="2"/>
-      <c r="C686" s="31" t="s">
-        <v>759</v>
-      </c>
-      <c r="D686" s="24" t="s">
-        <v>759</v>
-      </c>
-      <c r="E686" s="24"/>
+      <c r="C686" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="D686" s="11"/>
+      <c r="E686" s="2"/>
     </row>
     <row r="687" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A687" s="22" t="s">
-        <v>752</v>
+      <c r="A687" s="2" t="s">
+        <v>766</v>
       </c>
       <c r="B687" s="2"/>
-      <c r="C687" s="31" t="s">
-        <v>760</v>
-      </c>
-      <c r="D687" s="24" t="s">
-        <v>760</v>
-      </c>
-      <c r="E687" s="24"/>
+      <c r="C687" s="3" t="s">
+        <v>768</v>
+      </c>
+      <c r="D687" s="11" t="s">
+        <v>821</v>
+      </c>
+      <c r="E687" s="2"/>
     </row>
     <row r="688" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A688" s="2" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="B688" s="2"/>
       <c r="C688" s="3" t="s">
-        <v>765</v>
+        <v>927</v>
       </c>
       <c r="D688" s="11"/>
       <c r="E688" s="2"/>
     </row>
     <row r="689" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A689" s="2" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="B689" s="2"/>
       <c r="C689" s="3" t="s">
-        <v>764</v>
-      </c>
-      <c r="D689" s="11"/>
+        <v>928</v>
+      </c>
+      <c r="D689" s="11" t="s">
+        <v>822</v>
+      </c>
       <c r="E689" s="2"/>
     </row>
     <row r="690" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A690" s="2" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="B690" s="2"/>
       <c r="C690" s="3" t="s">
-        <v>763</v>
-      </c>
-      <c r="D690" s="11"/>
+        <v>929</v>
+      </c>
+      <c r="D690" s="11" t="s">
+        <v>823</v>
+      </c>
       <c r="E690" s="2"/>
     </row>
     <row r="691" spans="1:5" x14ac:dyDescent="0.45">
@@ -14167,11 +14217,9 @@
       </c>
       <c r="B691" s="2"/>
       <c r="C691" s="3" t="s">
-        <v>768</v>
-      </c>
-      <c r="D691" s="11" t="s">
-        <v>821</v>
-      </c>
+        <v>930</v>
+      </c>
+      <c r="D691" s="11"/>
       <c r="E691" s="2"/>
     </row>
     <row r="692" spans="1:5" x14ac:dyDescent="0.45">
@@ -14180,7 +14228,7 @@
       </c>
       <c r="B692" s="2"/>
       <c r="C692" s="3" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="D692" s="11"/>
       <c r="E692" s="2"/>
@@ -14191,58 +14239,62 @@
       </c>
       <c r="B693" s="2"/>
       <c r="C693" s="3" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="D693" s="11" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="E693" s="2"/>
     </row>
     <row r="694" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A694" s="2" t="s">
-        <v>766</v>
+        <v>775</v>
       </c>
       <c r="B694" s="2"/>
       <c r="C694" s="3" t="s">
-        <v>929</v>
+        <v>777</v>
       </c>
       <c r="D694" s="11" t="s">
-        <v>823</v>
+        <v>896</v>
       </c>
       <c r="E694" s="2"/>
     </row>
     <row r="695" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A695" s="2" t="s">
-        <v>766</v>
+        <v>775</v>
       </c>
       <c r="B695" s="2"/>
       <c r="C695" s="3" t="s">
-        <v>930</v>
-      </c>
-      <c r="D695" s="11"/>
+        <v>782</v>
+      </c>
+      <c r="D695" s="11" t="s">
+        <v>897</v>
+      </c>
       <c r="E695" s="2"/>
     </row>
     <row r="696" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A696" s="2" t="s">
-        <v>766</v>
+        <v>775</v>
       </c>
       <c r="B696" s="2"/>
       <c r="C696" s="3" t="s">
-        <v>931</v>
-      </c>
-      <c r="D696" s="11"/>
+        <v>918</v>
+      </c>
+      <c r="D696" s="11" t="s">
+        <v>898</v>
+      </c>
       <c r="E696" s="2"/>
     </row>
     <row r="697" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A697" s="2" t="s">
-        <v>766</v>
+        <v>775</v>
       </c>
       <c r="B697" s="2"/>
       <c r="C697" s="3" t="s">
-        <v>932</v>
+        <v>784</v>
       </c>
       <c r="D697" s="11" t="s">
-        <v>824</v>
+        <v>899</v>
       </c>
       <c r="E697" s="2"/>
     </row>
@@ -14252,10 +14304,10 @@
       </c>
       <c r="B698" s="2"/>
       <c r="C698" s="3" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="D698" s="11" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="E698" s="2"/>
     </row>
@@ -14265,10 +14317,10 @@
       </c>
       <c r="B699" s="2"/>
       <c r="C699" s="3" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D699" s="11" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="E699" s="2"/>
     </row>
@@ -14278,10 +14330,10 @@
       </c>
       <c r="B700" s="2"/>
       <c r="C700" s="3" t="s">
-        <v>918</v>
+        <v>781</v>
       </c>
       <c r="D700" s="11" t="s">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="E700" s="2"/>
     </row>
@@ -14291,10 +14343,10 @@
       </c>
       <c r="B701" s="2"/>
       <c r="C701" s="3" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="D701" s="11" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="E701" s="2"/>
     </row>
@@ -14304,62 +14356,62 @@
       </c>
       <c r="B702" s="2"/>
       <c r="C702" s="3" t="s">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="D702" s="11" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="E702" s="2"/>
     </row>
     <row r="703" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A703" s="2" t="s">
-        <v>775</v>
+        <v>786</v>
       </c>
       <c r="B703" s="2"/>
       <c r="C703" s="3" t="s">
-        <v>783</v>
+        <v>922</v>
       </c>
       <c r="D703" s="11" t="s">
-        <v>901</v>
+        <v>788</v>
       </c>
       <c r="E703" s="2"/>
     </row>
     <row r="704" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A704" s="2" t="s">
-        <v>775</v>
+        <v>786</v>
       </c>
       <c r="B704" s="2"/>
       <c r="C704" s="3" t="s">
-        <v>781</v>
+        <v>923</v>
       </c>
       <c r="D704" s="11" t="s">
-        <v>902</v>
+        <v>890</v>
       </c>
       <c r="E704" s="2"/>
     </row>
     <row r="705" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A705" s="2" t="s">
-        <v>775</v>
+        <v>786</v>
       </c>
       <c r="B705" s="2"/>
       <c r="C705" s="3" t="s">
-        <v>780</v>
+        <v>924</v>
       </c>
       <c r="D705" s="11" t="s">
-        <v>903</v>
+        <v>790</v>
       </c>
       <c r="E705" s="2"/>
     </row>
     <row r="706" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A706" s="2" t="s">
-        <v>775</v>
+        <v>786</v>
       </c>
       <c r="B706" s="2"/>
       <c r="C706" s="3" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="D706" s="11" t="s">
-        <v>904</v>
+        <v>891</v>
       </c>
       <c r="E706" s="2"/>
     </row>
@@ -14369,10 +14421,10 @@
       </c>
       <c r="B707" s="2"/>
       <c r="C707" s="3" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="D707" s="11" t="s">
-        <v>788</v>
+        <v>892</v>
       </c>
       <c r="E707" s="2"/>
     </row>
@@ -14382,62 +14434,62 @@
       </c>
       <c r="B708" s="2"/>
       <c r="C708" s="3" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="D708" s="11" t="s">
-        <v>890</v>
+        <v>789</v>
       </c>
       <c r="E708" s="2"/>
     </row>
     <row r="709" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A709" s="2" t="s">
-        <v>786</v>
+      <c r="A709" s="5" t="s">
+        <v>794</v>
       </c>
       <c r="B709" s="2"/>
       <c r="C709" s="3" t="s">
-        <v>924</v>
+        <v>796</v>
       </c>
       <c r="D709" s="11" t="s">
-        <v>790</v>
+        <v>831</v>
       </c>
       <c r="E709" s="2"/>
     </row>
     <row r="710" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A710" s="2" t="s">
-        <v>786</v>
+      <c r="A710" s="5" t="s">
+        <v>794</v>
       </c>
       <c r="B710" s="2"/>
       <c r="C710" s="3" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="D710" s="11" t="s">
-        <v>891</v>
+        <v>832</v>
       </c>
       <c r="E710" s="2"/>
     </row>
     <row r="711" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A711" s="2" t="s">
-        <v>786</v>
+      <c r="A711" s="5" t="s">
+        <v>794</v>
       </c>
       <c r="B711" s="2"/>
       <c r="C711" s="3" t="s">
-        <v>925</v>
+        <v>793</v>
       </c>
       <c r="D711" s="11" t="s">
-        <v>892</v>
+        <v>833</v>
       </c>
       <c r="E711" s="2"/>
     </row>
     <row r="712" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A712" s="2" t="s">
-        <v>786</v>
+      <c r="A712" s="5" t="s">
+        <v>794</v>
       </c>
       <c r="B712" s="2"/>
       <c r="C712" s="3" t="s">
-        <v>926</v>
+        <v>790</v>
       </c>
       <c r="D712" s="11" t="s">
-        <v>789</v>
+        <v>834</v>
       </c>
       <c r="E712" s="2"/>
     </row>
@@ -14447,203 +14499,151 @@
       </c>
       <c r="B713" s="2"/>
       <c r="C713" s="3" t="s">
-        <v>796</v>
+        <v>789</v>
       </c>
       <c r="D713" s="11" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="E713" s="2"/>
     </row>
     <row r="714" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A714" s="5" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="B714" s="2"/>
       <c r="C714" s="3" t="s">
-        <v>788</v>
+        <v>799</v>
       </c>
       <c r="D714" s="11" t="s">
-        <v>832</v>
+        <v>893</v>
       </c>
       <c r="E714" s="2"/>
     </row>
     <row r="715" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A715" s="5" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="B715" s="2"/>
       <c r="C715" s="3" t="s">
-        <v>793</v>
+        <v>801</v>
       </c>
       <c r="D715" s="11" t="s">
-        <v>833</v>
+        <v>894</v>
       </c>
       <c r="E715" s="2"/>
     </row>
     <row r="716" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A716" s="5" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="B716" s="2"/>
       <c r="C716" s="3" t="s">
-        <v>790</v>
+        <v>800</v>
       </c>
       <c r="D716" s="11" t="s">
-        <v>834</v>
+        <v>895</v>
       </c>
       <c r="E716" s="2"/>
     </row>
     <row r="717" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A717" s="5" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="B717" s="2"/>
-      <c r="C717" s="3" t="s">
-        <v>789</v>
+      <c r="C717" s="5" t="s">
+        <v>802</v>
       </c>
       <c r="D717" s="11" t="s">
-        <v>835</v>
+        <v>815</v>
       </c>
       <c r="E717" s="2"/>
     </row>
     <row r="718" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A718" s="5" t="s">
-        <v>797</v>
+      <c r="A718" s="2" t="s">
+        <v>919</v>
       </c>
       <c r="B718" s="2"/>
       <c r="C718" s="3" t="s">
-        <v>799</v>
-      </c>
-      <c r="D718" s="11" t="s">
-        <v>893</v>
+        <v>920</v>
+      </c>
+      <c r="D718" s="3" t="s">
+        <v>920</v>
       </c>
       <c r="E718" s="2"/>
     </row>
     <row r="719" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A719" s="5" t="s">
-        <v>797</v>
+      <c r="A719" s="2" t="s">
+        <v>919</v>
       </c>
       <c r="B719" s="2"/>
       <c r="C719" s="3" t="s">
-        <v>801</v>
-      </c>
-      <c r="D719" s="11" t="s">
-        <v>894</v>
-      </c>
-      <c r="E719" s="2"/>
+        <v>886</v>
+      </c>
+      <c r="D719" s="10" t="s">
+        <v>886</v>
+      </c>
+      <c r="E719" s="10"/>
     </row>
     <row r="720" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A720" s="5" t="s">
-        <v>797</v>
+      <c r="A720" s="2" t="s">
+        <v>919</v>
       </c>
       <c r="B720" s="2"/>
       <c r="C720" s="3" t="s">
-        <v>800</v>
-      </c>
-      <c r="D720" s="11" t="s">
-        <v>895</v>
-      </c>
-      <c r="E720" s="2"/>
+        <v>816</v>
+      </c>
+      <c r="D720" s="10" t="s">
+        <v>816</v>
+      </c>
+      <c r="E720" s="10"/>
     </row>
     <row r="721" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A721" s="5" t="s">
-        <v>797</v>
+      <c r="A721" s="2" t="s">
+        <v>919</v>
       </c>
       <c r="B721" s="2"/>
-      <c r="C721" s="5" t="s">
-        <v>802</v>
-      </c>
-      <c r="D721" s="11" t="s">
-        <v>815</v>
-      </c>
-      <c r="E721" s="2"/>
-    </row>
-    <row r="722" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C721" s="3" t="s">
+        <v>907</v>
+      </c>
+      <c r="D721" s="17" t="s">
+        <v>907</v>
+      </c>
+      <c r="F721" s="14" t="e">
+        <f>_xlfn.XLOOKUP(#REF!,'[1]Hem Catalogue'!$C$545:$C$643,'[1]Hem Catalogue'!$D$545:$D$643,"")</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="722" spans="1:6" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A722" s="2" t="s">
         <v>919</v>
       </c>
       <c r="B722" s="2"/>
       <c r="C722" s="3" t="s">
-        <v>920</v>
-      </c>
-      <c r="D722" s="3" t="s">
-        <v>920</v>
-      </c>
-      <c r="E722" s="2"/>
-    </row>
-    <row r="723" spans="1:6" x14ac:dyDescent="0.45">
+        <v>889</v>
+      </c>
+      <c r="D722" s="23" t="s">
+        <v>889</v>
+      </c>
+      <c r="E722" s="24"/>
+    </row>
+    <row r="723" spans="1:6" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A723" s="2" t="s">
         <v>919</v>
       </c>
       <c r="B723" s="2"/>
       <c r="C723" s="3" t="s">
-        <v>886</v>
-      </c>
-      <c r="D723" s="10" t="s">
-        <v>886</v>
-      </c>
-      <c r="E723" s="10"/>
+        <v>887</v>
+      </c>
+      <c r="D723" s="23" t="s">
+        <v>887</v>
+      </c>
+      <c r="E723" s="24"/>
     </row>
     <row r="724" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A724" s="2" t="s">
-        <v>919</v>
-      </c>
       <c r="B724" s="2"/>
-      <c r="C724" s="3" t="s">
-        <v>816</v>
-      </c>
-      <c r="D724" s="10" t="s">
-        <v>816</v>
-      </c>
-      <c r="E724" s="10"/>
-    </row>
-    <row r="725" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A725" s="2" t="s">
-        <v>919</v>
-      </c>
-      <c r="B725" s="2"/>
-      <c r="C725" s="3" t="s">
-        <v>907</v>
-      </c>
-      <c r="D725" s="17" t="s">
-        <v>907</v>
-      </c>
-      <c r="F725" s="14" t="e">
-        <f>_xlfn.XLOOKUP(#REF!,'[1]Hem Catalogue'!$C$545:$C$643,'[1]Hem Catalogue'!$D$545:$D$643,"")</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="726" spans="1:6" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A726" s="2" t="s">
-        <v>919</v>
-      </c>
-      <c r="B726" s="2"/>
-      <c r="C726" s="3" t="s">
-        <v>889</v>
-      </c>
-      <c r="D726" s="23" t="s">
-        <v>889</v>
-      </c>
-      <c r="E726" s="24"/>
-    </row>
-    <row r="727" spans="1:6" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A727" s="2" t="s">
-        <v>919</v>
-      </c>
-      <c r="B727" s="2"/>
-      <c r="C727" s="3" t="s">
-        <v>887</v>
-      </c>
-      <c r="D727" s="23" t="s">
-        <v>887</v>
-      </c>
-      <c r="E727" s="24"/>
-    </row>
-    <row r="728" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B728" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G721" xr:uid="{DBBB3535-4F14-43E5-BD0D-3890A33AED12}"/>
+  <autoFilter ref="A1:G717" xr:uid="{DBBB3535-4F14-43E5-BD0D-3890A33AED12}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
